--- a/research/traditional_assets/database/data/philippines/philippines_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_farming_agriculture.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="pse_ever" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.09759999999999999</v>
+        <v>-0.13345</v>
+      </c>
+      <c r="E2">
+        <v>1.833</v>
       </c>
       <c r="G2">
-        <v>-0.04682981090100111</v>
+        <v>-0.02512998983227385</v>
       </c>
       <c r="H2">
-        <v>-0.04682981090100111</v>
+        <v>-0.02512998983227385</v>
       </c>
       <c r="I2">
-        <v>-0.1568409343715239</v>
+        <v>-0.08904613502409668</v>
       </c>
       <c r="J2">
-        <v>-0.1568409343715239</v>
+        <v>-0.08897801229784874</v>
       </c>
       <c r="K2">
-        <v>-18.3</v>
+        <v>23.1</v>
       </c>
       <c r="L2">
-        <v>-0.203559510567297</v>
+        <v>0.1909548569491862</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.15</v>
+        <v>5.067</v>
       </c>
       <c r="V2">
-        <v>0.03616352201257862</v>
+        <v>0.1146380090497738</v>
       </c>
       <c r="W2">
-        <v>-0.152627189324437</v>
+        <v>2.832860372922437</v>
       </c>
       <c r="X2">
-        <v>0.1566086629824734</v>
+        <v>0.2019053836524513</v>
       </c>
       <c r="Y2">
-        <v>-0.3092358523069104</v>
+        <v>2.630954989269986</v>
       </c>
       <c r="Z2">
-        <v>0.4222639736965712</v>
+        <v>0.5949929911713352</v>
       </c>
       <c r="AA2">
-        <v>-0.06622827618600283</v>
+        <v>-0.02561989487911624</v>
       </c>
       <c r="AB2">
-        <v>0.05953644799875241</v>
+        <v>0.1020884782485728</v>
       </c>
       <c r="AC2">
-        <v>-0.1257647241847552</v>
+        <v>-0.1277083731276891</v>
       </c>
       <c r="AD2">
-        <v>96.90000000000001</v>
+        <v>95.19</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>96.90000000000001</v>
+        <v>95.19</v>
       </c>
       <c r="AG2">
-        <v>95.75</v>
+        <v>90.12299999999999</v>
       </c>
       <c r="AH2">
-        <v>0.7529137529137528</v>
+        <v>0.6829040820718847</v>
       </c>
       <c r="AI2">
-        <v>0.4896412329459323</v>
+        <v>0.4193576809551081</v>
       </c>
       <c r="AJ2">
-        <v>0.7506860054880439</v>
+        <v>0.6709424298147004</v>
       </c>
       <c r="AK2">
-        <v>0.4866581956797967</v>
+        <v>0.4061003140728991</v>
       </c>
       <c r="AL2">
-        <v>6.62</v>
+        <v>5.621</v>
       </c>
       <c r="AM2">
-        <v>6.62</v>
+        <v>5.621</v>
       </c>
       <c r="AN2">
-        <v>-23.0166270783848</v>
+        <v>-31.3125</v>
       </c>
       <c r="AO2">
-        <v>-2.129909365558912</v>
+        <v>-1.916384984878135</v>
       </c>
       <c r="AP2">
-        <v>-22.74346793349169</v>
+        <v>-29.64572368421052</v>
       </c>
       <c r="AQ2">
-        <v>-2.129909365558912</v>
+        <v>-1.916384984878135</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +712,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Roxas Holdings, Inc. (PSE:ROX)</t>
+          <t>Everwoods Green Resources and Holdings, Inc. (PSE:EVER)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.09759999999999999</v>
+        <v>-0.318</v>
+      </c>
+      <c r="E3">
+        <v>1.833</v>
       </c>
       <c r="G3">
-        <v>-0.04682981090100111</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>-0.04682981090100111</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>-0.1568409343715239</v>
+        <v>0.0490367775831874</v>
       </c>
       <c r="J3">
-        <v>-0.1568409343715239</v>
+        <v>0.04896174863387979</v>
       </c>
       <c r="K3">
-        <v>-18.3</v>
+        <v>36.6</v>
       </c>
       <c r="L3">
-        <v>-0.203559510567297</v>
+        <v>64.09807355516638</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8913 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.15</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="V3">
-        <v>0.03616352201257862</v>
+        <v>0.003799126637554585</v>
       </c>
       <c r="W3">
-        <v>-0.152627189324437</v>
+        <v>5.800316957210777</v>
       </c>
       <c r="X3">
-        <v>0.1566086629824734</v>
+        <v>0.1021641848855593</v>
       </c>
       <c r="Y3">
-        <v>-0.3092358523069104</v>
+        <v>5.698152772325217</v>
       </c>
       <c r="Z3">
-        <v>0.4222639736965712</v>
+        <v>0.07859600825877494</v>
       </c>
       <c r="AA3">
-        <v>-0.06622827618600283</v>
+        <v>0.003848197999992479</v>
       </c>
       <c r="AB3">
-        <v>0.05953644799875241</v>
+        <v>0.1005776865111507</v>
       </c>
       <c r="AC3">
-        <v>-0.1257647241847552</v>
+        <v>-0.0967294885111582</v>
       </c>
       <c r="AD3">
-        <v>96.90000000000001</v>
+        <v>1.19</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>96.90000000000001</v>
+        <v>1.19</v>
       </c>
       <c r="AG3">
-        <v>95.75</v>
+        <v>1.103</v>
       </c>
       <c r="AH3">
-        <v>0.7529137529137528</v>
+        <v>0.0493980904939809</v>
       </c>
       <c r="AI3">
-        <v>0.4896412329459323</v>
+        <v>0.02748902748902749</v>
       </c>
       <c r="AJ3">
-        <v>0.7506860054880439</v>
+        <v>0.04595258925967587</v>
       </c>
       <c r="AK3">
-        <v>0.4866581956797967</v>
+        <v>0.02553063444668194</v>
       </c>
       <c r="AL3">
-        <v>6.62</v>
+        <v>0.121</v>
       </c>
       <c r="AM3">
-        <v>6.62</v>
-      </c>
-      <c r="AN3">
-        <v>-23.0166270783848</v>
+        <v>0.121</v>
       </c>
       <c r="AO3">
-        <v>-2.129909365558912</v>
-      </c>
-      <c r="AP3">
-        <v>-22.74346793349169</v>
+        <v>0.231404958677686</v>
       </c>
       <c r="AQ3">
-        <v>-2.129909365558912</v>
+        <v>0.231404958677686</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Roxas Holdings, Inc. (PSE:ROX)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Farming/Agriculture</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.05110000000000001</v>
+      </c>
+      <c r="G4">
+        <v>-0.02524916943521595</v>
+      </c>
+      <c r="H4">
+        <v>-0.02524916943521595</v>
+      </c>
+      <c r="I4">
+        <v>-0.08970099667774087</v>
+      </c>
+      <c r="J4">
+        <v>-0.08970099667774087</v>
+      </c>
+      <c r="K4">
+        <v>-13.5</v>
+      </c>
+      <c r="L4">
+        <v>-0.1121262458471761</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>4.98</v>
+      </c>
+      <c r="V4">
+        <v>0.2338028169014085</v>
+      </c>
+      <c r="W4">
+        <v>-0.1345962113659023</v>
+      </c>
+      <c r="X4">
+        <v>0.3016465824193434</v>
+      </c>
+      <c r="Y4">
+        <v>-0.4362427937852457</v>
+      </c>
+      <c r="Z4">
+        <v>0.6141290487120633</v>
+      </c>
+      <c r="AA4">
+        <v>-0.05508798775822495</v>
+      </c>
+      <c r="AB4">
+        <v>0.103599269985995</v>
+      </c>
+      <c r="AC4">
+        <v>-0.15868725774422</v>
+      </c>
+      <c r="AD4">
+        <v>94</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>94</v>
+      </c>
+      <c r="AG4">
+        <v>89.02</v>
+      </c>
+      <c r="AH4">
+        <v>0.8152645273200347</v>
+      </c>
+      <c r="AI4">
+        <v>0.5117038649972782</v>
+      </c>
+      <c r="AJ4">
+        <v>0.8069253081943437</v>
+      </c>
+      <c r="AK4">
+        <v>0.4980975828111012</v>
+      </c>
+      <c r="AL4">
+        <v>5.5</v>
+      </c>
+      <c r="AM4">
+        <v>5.5</v>
+      </c>
+      <c r="AN4">
+        <v>-30.92105263157895</v>
+      </c>
+      <c r="AO4">
+        <v>-1.963636363636364</v>
+      </c>
+      <c r="AP4">
+        <v>-29.2828947368421</v>
+      </c>
+      <c r="AQ4">
+        <v>-1.963636363636364</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Everwoods Green Resources and Holdings, Inc. (PSE:EVER)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PSE:EVER</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Farming/Agriculture</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0493980904939809</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>22.9</v>
+      </c>
+      <c r="H2">
+        <v>24.4010837795572</v>
+      </c>
+      <c r="I2">
+        <v>24.003</v>
+      </c>
+      <c r="J2">
+        <v>24.3140837795572</v>
+      </c>
+      <c r="K2">
+        <v>1.19</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0.100577686511151</v>
+      </c>
+      <c r="N2">
+        <v>0.099787278927364</v>
+      </c>
+      <c r="O2">
+        <v>0.07004759174311929</v>
+      </c>
+      <c r="P2">
+        <v>0.034275</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.102164184885559</v>
+      </c>
+      <c r="T2">
+        <v>0.099787278927364</v>
+      </c>
+      <c r="U2">
+        <v>0.688700516148315</v>
+      </c>
+      <c r="V2">
+        <v>0.662866105697023</v>
+      </c>
+      <c r="W2">
+        <v>10000000</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>22.9</v>
+      </c>
+      <c r="AB2">
+        <v>0.09200542674185173</v>
+      </c>
+      <c r="AC2">
+        <v>0.09339678899082569</v>
+      </c>
+      <c r="AD2">
+        <v>0.25</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>-0.028</v>
+      </c>
+      <c r="AI2">
+        <v>-0.02800000000000002</v>
+      </c>
+      <c r="AJ2">
+        <v>1.19</v>
+      </c>
+      <c r="AK2">
+        <v>1.19</v>
+      </c>
+      <c r="AL2">
+        <v>0.121</v>
+      </c>
+      <c r="AM2">
+        <v>1.19</v>
+      </c>
+      <c r="AN2">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.099787278927364</v>
+      </c>
+      <c r="C2">
+        <v>24.40108377955717</v>
+      </c>
+      <c r="D2">
+        <v>24.31408377955717</v>
+      </c>
+      <c r="E2">
+        <v>-1.19</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H2">
+        <v>22.9</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>-0.028</v>
+      </c>
+      <c r="L2">
+        <v>0.028</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.028</v>
+      </c>
+      <c r="O2">
+        <v>0.007</v>
+      </c>
+      <c r="P2">
+        <v>0.021</v>
+      </c>
+      <c r="Q2">
+        <v>-0.006999999999999999</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.099787278927364</v>
+      </c>
+      <c r="T2">
+        <v>0.662866105697023</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.25</v>
+      </c>
+      <c r="W2">
+        <v>0.034275</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1011638137077786</v>
+      </c>
+      <c r="C3">
+        <v>23.62350746060553</v>
+      </c>
+      <c r="D3">
+        <v>23.77740746060553</v>
+      </c>
+      <c r="E3">
+        <v>-0.9490999999999999</v>
+      </c>
+      <c r="F3">
+        <v>0.2409</v>
+      </c>
+      <c r="G3">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H3">
+        <v>22.9</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>-0.028</v>
+      </c>
+      <c r="L3">
+        <v>0.028</v>
+      </c>
+      <c r="M3">
+        <v>0.05150442</v>
+      </c>
+      <c r="N3">
+        <v>-0.02350441999999999</v>
+      </c>
+      <c r="O3">
+        <v>-0.005876104999999999</v>
+      </c>
+      <c r="P3">
+        <v>-0.017628315</v>
+      </c>
+      <c r="Q3">
+        <v>-0.045628315</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1003195865764489</v>
+      </c>
+      <c r="T3">
+        <v>0.6686517171325143</v>
+      </c>
+      <c r="U3">
+        <v>0.2138</v>
+      </c>
+      <c r="V3">
+        <v>0.1359106655312302</v>
+      </c>
+      <c r="W3">
+        <v>0.184742299709423</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>0.5436426621249206</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1034224912849017</v>
+      </c>
+      <c r="C4">
+        <v>22.55154236228524</v>
+      </c>
+      <c r="D4">
+        <v>22.94634236228524</v>
+      </c>
+      <c r="E4">
+        <v>-0.7081999999999999</v>
+      </c>
+      <c r="F4">
+        <v>0.4818</v>
+      </c>
+      <c r="G4">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H4">
+        <v>22.9</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>-0.028</v>
+      </c>
+      <c r="L4">
+        <v>0.028</v>
+      </c>
+      <c r="M4">
+        <v>0.11505384</v>
+      </c>
+      <c r="N4">
+        <v>-0.08705384000000001</v>
+      </c>
+      <c r="O4">
+        <v>-0.02176346</v>
+      </c>
+      <c r="P4">
+        <v>-0.06529038000000001</v>
+      </c>
+      <c r="Q4">
+        <v>-0.09329038000000001</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1009561921304158</v>
+      </c>
+      <c r="T4">
+        <v>0.6755709345799056</v>
+      </c>
+      <c r="U4">
+        <v>0.2388</v>
+      </c>
+      <c r="V4">
+        <v>0.06084108101042086</v>
+      </c>
+      <c r="W4">
+        <v>0.2242711498547115</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>0.2433643240416834</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1054224912849017</v>
+      </c>
+      <c r="C5">
+        <v>21.62179564041295</v>
+      </c>
+      <c r="D5">
+        <v>22.25749564041295</v>
+      </c>
+      <c r="E5">
+        <v>-0.4672999999999999</v>
+      </c>
+      <c r="F5">
+        <v>0.7227</v>
+      </c>
+      <c r="G5">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H5">
+        <v>22.9</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>-0.028</v>
+      </c>
+      <c r="L5">
+        <v>0.028</v>
+      </c>
+      <c r="M5">
+        <v>0.17258076</v>
+      </c>
+      <c r="N5">
+        <v>-0.14458076</v>
+      </c>
+      <c r="O5">
+        <v>-0.03614519</v>
+      </c>
+      <c r="P5">
+        <v>-0.10843557</v>
+      </c>
+      <c r="Q5">
+        <v>-0.13643557</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1015969776162964</v>
+      </c>
+      <c r="T5">
+        <v>0.6825355833900076</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>0.04056072067361391</v>
+      </c>
+      <c r="W5">
+        <v>0.229114099903141</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>0.1622428826944556</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1074224912849017</v>
+      </c>
+      <c r="C6">
+        <v>20.73220174359693</v>
+      </c>
+      <c r="D6">
+        <v>21.60880174359693</v>
+      </c>
+      <c r="E6">
+        <v>-0.2263999999999999</v>
+      </c>
+      <c r="F6">
+        <v>0.9636</v>
+      </c>
+      <c r="G6">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H6">
+        <v>22.9</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>-0.028</v>
+      </c>
+      <c r="L6">
+        <v>0.028</v>
+      </c>
+      <c r="M6">
+        <v>0.23010768</v>
+      </c>
+      <c r="N6">
+        <v>-0.20210768</v>
+      </c>
+      <c r="O6">
+        <v>-0.05052692</v>
+      </c>
+      <c r="P6">
+        <v>-0.15158076</v>
+      </c>
+      <c r="Q6">
+        <v>-0.17958076</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1022511127997995</v>
+      </c>
+      <c r="T6">
+        <v>0.6896453290503203</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>0.03042054050521043</v>
+      </c>
+      <c r="W6">
+        <v>0.2315355749273557</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>0.1216821620208417</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1094224912849017</v>
+      </c>
+      <c r="C7">
+        <v>19.87934933720493</v>
+      </c>
+      <c r="D7">
+        <v>20.99684933720493</v>
+      </c>
+      <c r="E7">
+        <v>0.01450000000000018</v>
+      </c>
+      <c r="F7">
+        <v>1.2045</v>
+      </c>
+      <c r="G7">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H7">
+        <v>22.9</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>-0.028</v>
+      </c>
+      <c r="L7">
+        <v>0.028</v>
+      </c>
+      <c r="M7">
+        <v>0.2876346</v>
+      </c>
+      <c r="N7">
+        <v>-0.2596346</v>
+      </c>
+      <c r="O7">
+        <v>-0.06490865</v>
+      </c>
+      <c r="P7">
+        <v>-0.19472595</v>
+      </c>
+      <c r="Q7">
+        <v>-0.22272595</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1029190192503237</v>
+      </c>
+      <c r="T7">
+        <v>0.6969047535666394</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>0.02433643240416834</v>
+      </c>
+      <c r="W7">
+        <v>0.2329884599418846</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>0.09734572961667343</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1114224912849017</v>
+      </c>
+      <c r="C8">
+        <v>19.06020287482915</v>
+      </c>
+      <c r="D8">
+        <v>20.41860287482915</v>
+      </c>
+      <c r="E8">
+        <v>0.2554000000000001</v>
+      </c>
+      <c r="F8">
+        <v>1.4454</v>
+      </c>
+      <c r="G8">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H8">
+        <v>22.9</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>-0.028</v>
+      </c>
+      <c r="L8">
+        <v>0.028</v>
+      </c>
+      <c r="M8">
+        <v>0.34516152</v>
+      </c>
+      <c r="N8">
+        <v>-0.31716152</v>
+      </c>
+      <c r="O8">
+        <v>-0.07929037999999999</v>
+      </c>
+      <c r="P8">
+        <v>-0.23787114</v>
+      </c>
+      <c r="Q8">
+        <v>-0.26587114</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.103601136476391</v>
+      </c>
+      <c r="T8">
+        <v>0.7043186339237314</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>0.02028036033680695</v>
+      </c>
+      <c r="W8">
+        <v>0.2339570499515705</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>0.08112144134722787</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1134224912849017</v>
+      </c>
+      <c r="C9">
+        <v>18.27205223971238</v>
+      </c>
+      <c r="D9">
+        <v>19.87135223971238</v>
+      </c>
+      <c r="E9">
+        <v>0.4963000000000002</v>
+      </c>
+      <c r="F9">
+        <v>1.6863</v>
+      </c>
+      <c r="G9">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H9">
+        <v>22.9</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>-0.028</v>
+      </c>
+      <c r="L9">
+        <v>0.028</v>
+      </c>
+      <c r="M9">
+        <v>0.40268844</v>
+      </c>
+      <c r="N9">
+        <v>-0.37468844</v>
+      </c>
+      <c r="O9">
+        <v>-0.09367211</v>
+      </c>
+      <c r="P9">
+        <v>-0.28101633</v>
+      </c>
+      <c r="Q9">
+        <v>-0.3090163300000001</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1042979228901156</v>
+      </c>
+      <c r="T9">
+        <v>0.7118919525680726</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>0.01738316600297739</v>
+      </c>
+      <c r="W9">
+        <v>0.234648899958489</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>0.06953266401190961</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1154224912849018</v>
+      </c>
+      <c r="C10">
+        <v>17.51247027292992</v>
+      </c>
+      <c r="D10">
+        <v>19.35267027292992</v>
+      </c>
+      <c r="E10">
+        <v>0.7372000000000001</v>
+      </c>
+      <c r="F10">
+        <v>1.9272</v>
+      </c>
+      <c r="G10">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H10">
+        <v>22.9</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>-0.028</v>
+      </c>
+      <c r="L10">
+        <v>0.028</v>
+      </c>
+      <c r="M10">
+        <v>0.46021536</v>
+      </c>
+      <c r="N10">
+        <v>-0.43221536</v>
+      </c>
+      <c r="O10">
+        <v>-0.10805384</v>
+      </c>
+      <c r="P10">
+        <v>-0.32416152</v>
+      </c>
+      <c r="Q10">
+        <v>-0.35216152</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1050098568345734</v>
+      </c>
+      <c r="T10">
+        <v>0.7196299085742474</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>0.01521027025260521</v>
+      </c>
+      <c r="W10">
+        <v>0.2351677874636779</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>0.06084108101042096</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1174224912849017</v>
+      </c>
+      <c r="C11">
+        <v>16.77927678396371</v>
+      </c>
+      <c r="D11">
+        <v>18.86037678396371</v>
+      </c>
+      <c r="E11">
+        <v>0.9781</v>
+      </c>
+      <c r="F11">
+        <v>2.1681</v>
+      </c>
+      <c r="G11">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H11">
+        <v>22.9</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>-0.028</v>
+      </c>
+      <c r="L11">
+        <v>0.028</v>
+      </c>
+      <c r="M11">
+        <v>0.51774228</v>
+      </c>
+      <c r="N11">
+        <v>-0.48974228</v>
+      </c>
+      <c r="O11">
+        <v>-0.12243557</v>
+      </c>
+      <c r="P11">
+        <v>-0.36730671</v>
+      </c>
+      <c r="Q11">
+        <v>-0.39530671</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1057374376789093</v>
+      </c>
+      <c r="T11">
+        <v>0.7275379295475907</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>0.01352024022453797</v>
+      </c>
+      <c r="W11">
+        <v>0.2355713666343803</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>0.05408096089815195</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1194224912849017</v>
+      </c>
+      <c r="C12">
+        <v>16.07050791800879</v>
+      </c>
+      <c r="D12">
+        <v>18.39250791800879</v>
+      </c>
+      <c r="E12">
+        <v>1.219</v>
+      </c>
+      <c r="F12">
+        <v>2.409</v>
+      </c>
+      <c r="G12">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H12">
+        <v>22.9</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>-0.028</v>
+      </c>
+      <c r="L12">
+        <v>0.028</v>
+      </c>
+      <c r="M12">
+        <v>0.5752692</v>
+      </c>
+      <c r="N12">
+        <v>-0.5472692</v>
+      </c>
+      <c r="O12">
+        <v>-0.1368173</v>
+      </c>
+      <c r="P12">
+        <v>-0.4104519</v>
+      </c>
+      <c r="Q12">
+        <v>-0.4384519</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1064811869864528</v>
+      </c>
+      <c r="T12">
+        <v>0.7356216843203417</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>0.01216821620208417</v>
+      </c>
+      <c r="W12">
+        <v>0.2358942299709423</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>0.04867286480833677</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1214224912849017</v>
+      </c>
+      <c r="C13">
+        <v>15.38438997233859</v>
+      </c>
+      <c r="D13">
+        <v>17.9472899723386</v>
+      </c>
+      <c r="E13">
+        <v>1.4599</v>
+      </c>
+      <c r="F13">
+        <v>2.6499</v>
+      </c>
+      <c r="G13">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H13">
+        <v>22.9</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>-0.028</v>
+      </c>
+      <c r="L13">
+        <v>0.028</v>
+      </c>
+      <c r="M13">
+        <v>0.6327961200000001</v>
+      </c>
+      <c r="N13">
+        <v>-0.60479612</v>
+      </c>
+      <c r="O13">
+        <v>-0.15119903</v>
+      </c>
+      <c r="P13">
+        <v>-0.45359709</v>
+      </c>
+      <c r="Q13">
+        <v>-0.4815970900000001</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1072416497615815</v>
+      </c>
+      <c r="T13">
+        <v>0.7438870965037162</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>0.01106201472916743</v>
+      </c>
+      <c r="W13">
+        <v>0.2361583908826748</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.04424805891666972</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1234224912849017</v>
+      </c>
+      <c r="C14">
+        <v>14.71931692567385</v>
+      </c>
+      <c r="D14">
+        <v>17.52311692567385</v>
+      </c>
+      <c r="E14">
+        <v>1.7008</v>
+      </c>
+      <c r="F14">
+        <v>2.8908</v>
+      </c>
+      <c r="G14">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H14">
+        <v>22.9</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>-0.028</v>
+      </c>
+      <c r="L14">
+        <v>0.028</v>
+      </c>
+      <c r="M14">
+        <v>0.69032304</v>
+      </c>
+      <c r="N14">
+        <v>-0.66232304</v>
+      </c>
+      <c r="O14">
+        <v>-0.16558076</v>
+      </c>
+      <c r="P14">
+        <v>-0.49674228</v>
+      </c>
+      <c r="Q14">
+        <v>-0.52474228</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1080193957815994</v>
+      </c>
+      <c r="T14">
+        <v>0.7523403589639858</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>0.01014018016840348</v>
+      </c>
+      <c r="W14">
+        <v>0.2363785249757853</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.04056072067361394</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1254224912849017</v>
+      </c>
+      <c r="C15">
+        <v>14.07383108045635</v>
+      </c>
+      <c r="D15">
+        <v>17.11853108045635</v>
+      </c>
+      <c r="E15">
+        <v>1.9417</v>
+      </c>
+      <c r="F15">
+        <v>3.1317</v>
+      </c>
+      <c r="G15">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H15">
+        <v>22.9</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>-0.028</v>
+      </c>
+      <c r="L15">
+        <v>0.028</v>
+      </c>
+      <c r="M15">
+        <v>0.74784996</v>
+      </c>
+      <c r="N15">
+        <v>-0.71984996</v>
+      </c>
+      <c r="O15">
+        <v>-0.17996249</v>
+      </c>
+      <c r="P15">
+        <v>-0.53988747</v>
+      </c>
+      <c r="Q15">
+        <v>-0.5678874700000001</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1088150210204684</v>
+      </c>
+      <c r="T15">
+        <v>0.7609879492969052</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>0.009360166309295516</v>
+      </c>
+      <c r="W15">
+        <v>0.2365647922853402</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.03744066523718215</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1274224912849017</v>
+      </c>
+      <c r="C16">
+        <v>13.44660632627122</v>
+      </c>
+      <c r="D16">
+        <v>16.73220632627122</v>
+      </c>
+      <c r="E16">
+        <v>2.1826</v>
+      </c>
+      <c r="F16">
+        <v>3.3726</v>
+      </c>
+      <c r="G16">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H16">
+        <v>22.9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>-0.028</v>
+      </c>
+      <c r="L16">
+        <v>0.028</v>
+      </c>
+      <c r="M16">
+        <v>0.8053768800000001</v>
+      </c>
+      <c r="N16">
+        <v>-0.77737688</v>
+      </c>
+      <c r="O16">
+        <v>-0.19434422</v>
+      </c>
+      <c r="P16">
+        <v>-0.58303266</v>
+      </c>
+      <c r="Q16">
+        <v>-0.61103266</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1096291491718692</v>
+      </c>
+      <c r="T16">
+        <v>0.769836646381753</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>0.008691583001488694</v>
+      </c>
+      <c r="W16">
+        <v>0.2367244499792445</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.0347663320059548</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1294224912849017</v>
+      </c>
+      <c r="C17">
+        <v>12.83643361948439</v>
+      </c>
+      <c r="D17">
+        <v>16.36293361948439</v>
+      </c>
+      <c r="E17">
+        <v>2.4235</v>
+      </c>
+      <c r="F17">
+        <v>3.6135</v>
+      </c>
+      <c r="G17">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H17">
+        <v>22.9</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>-0.028</v>
+      </c>
+      <c r="L17">
+        <v>0.028</v>
+      </c>
+      <c r="M17">
+        <v>0.8629038</v>
+      </c>
+      <c r="N17">
+        <v>-0.8349038</v>
+      </c>
+      <c r="O17">
+        <v>-0.20872595</v>
+      </c>
+      <c r="P17">
+        <v>-0.6261778499999999</v>
+      </c>
+      <c r="Q17">
+        <v>-0.6541778499999999</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1104624332797735</v>
+      </c>
+      <c r="T17">
+        <v>0.7788935481038911</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>0.008112144134722781</v>
+      </c>
+      <c r="W17">
+        <v>0.2368628199806282</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.03244857653889111</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1314224912849017</v>
+      </c>
+      <c r="C18">
+        <v>12.24220834411141</v>
+      </c>
+      <c r="D18">
+        <v>16.00960834411141</v>
+      </c>
+      <c r="E18">
+        <v>2.6644</v>
+      </c>
+      <c r="F18">
+        <v>3.8544</v>
+      </c>
+      <c r="G18">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H18">
+        <v>22.9</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>-0.028</v>
+      </c>
+      <c r="L18">
+        <v>0.028</v>
+      </c>
+      <c r="M18">
+        <v>0.92043072</v>
+      </c>
+      <c r="N18">
+        <v>-0.89243072</v>
+      </c>
+      <c r="O18">
+        <v>-0.22310768</v>
+      </c>
+      <c r="P18">
+        <v>-0.66932304</v>
+      </c>
+      <c r="Q18">
+        <v>-0.69732304</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1113155574854851</v>
+      </c>
+      <c r="T18">
+        <v>0.7881660903432233</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>0.007605135126302607</v>
+      </c>
+      <c r="W18">
+        <v>0.236983893731839</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.03042054050521048</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1334224912849017</v>
+      </c>
+      <c r="C19">
+        <v>11.66291927557785</v>
+      </c>
+      <c r="D19">
+        <v>15.67121927557785</v>
+      </c>
+      <c r="E19">
+        <v>2.9053</v>
+      </c>
+      <c r="F19">
+        <v>4.0953</v>
+      </c>
+      <c r="G19">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H19">
+        <v>22.9</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>-0.028</v>
+      </c>
+      <c r="L19">
+        <v>0.028</v>
+      </c>
+      <c r="M19">
+        <v>0.9779576400000001</v>
+      </c>
+      <c r="N19">
+        <v>-0.94995764</v>
+      </c>
+      <c r="O19">
+        <v>-0.23748941</v>
+      </c>
+      <c r="P19">
+        <v>-0.71246823</v>
+      </c>
+      <c r="Q19">
+        <v>-0.7404682300000001</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1121892389009729</v>
+      </c>
+      <c r="T19">
+        <v>0.7976620673353102</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0.007157774236520101</v>
+      </c>
+      <c r="W19">
+        <v>0.237090723512319</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.02863109694608046</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1354224912849017</v>
+      </c>
+      <c r="C20">
+        <v>11.09763891512183</v>
+      </c>
+      <c r="D20">
+        <v>15.34683891512183</v>
+      </c>
+      <c r="E20">
+        <v>3.1462</v>
+      </c>
+      <c r="F20">
+        <v>4.3362</v>
+      </c>
+      <c r="G20">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H20">
+        <v>22.9</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>-0.028</v>
+      </c>
+      <c r="L20">
+        <v>0.028</v>
+      </c>
+      <c r="M20">
+        <v>1.03548456</v>
+      </c>
+      <c r="N20">
+        <v>-1.00748456</v>
+      </c>
+      <c r="O20">
+        <v>-0.25187114</v>
+      </c>
+      <c r="P20">
+        <v>-0.75561342</v>
+      </c>
+      <c r="Q20">
+        <v>-0.78361342</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1130842296192774</v>
+      </c>
+      <c r="T20">
+        <v>0.8073896535223262</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0.006760120112268985</v>
+      </c>
+      <c r="W20">
+        <v>0.2371856833171902</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.02704048044907592</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1374224912849017</v>
+      </c>
+      <c r="C21">
+        <v>10.54551500026882</v>
+      </c>
+      <c r="D21">
+        <v>15.03561500026882</v>
+      </c>
+      <c r="E21">
+        <v>3.3871</v>
+      </c>
+      <c r="F21">
+        <v>4.5771</v>
+      </c>
+      <c r="G21">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H21">
+        <v>22.9</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>-0.028</v>
+      </c>
+      <c r="L21">
+        <v>0.028</v>
+      </c>
+      <c r="M21">
+        <v>1.09301148</v>
+      </c>
+      <c r="N21">
+        <v>-1.06501148</v>
+      </c>
+      <c r="O21">
+        <v>-0.26625287</v>
+      </c>
+      <c r="P21">
+        <v>-0.7987586099999999</v>
+      </c>
+      <c r="Q21">
+        <v>-0.8267586099999999</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1140013188738364</v>
+      </c>
+      <c r="T21">
+        <v>0.8173574270226018</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.006404324316886407</v>
+      </c>
+      <c r="W21">
+        <v>0.2372706473531275</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.02561729726754569</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1394224912849017</v>
+      </c>
+      <c r="C22">
+        <v>10.00576302774715</v>
+      </c>
+      <c r="D22">
+        <v>14.73676302774715</v>
+      </c>
+      <c r="E22">
+        <v>3.628000000000001</v>
+      </c>
+      <c r="F22">
+        <v>4.818000000000001</v>
+      </c>
+      <c r="G22">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H22">
+        <v>22.9</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>-0.028</v>
+      </c>
+      <c r="L22">
+        <v>0.028</v>
+      </c>
+      <c r="M22">
+        <v>1.1505384</v>
+      </c>
+      <c r="N22">
+        <v>-1.1225384</v>
+      </c>
+      <c r="O22">
+        <v>-0.2806346</v>
+      </c>
+      <c r="P22">
+        <v>-0.8419038000000001</v>
+      </c>
+      <c r="Q22">
+        <v>-0.8699038000000001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1149413353597594</v>
+      </c>
+      <c r="T22">
+        <v>0.8275743948603843</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.006084108101042086</v>
+      </c>
+      <c r="W22">
+        <v>0.2373471149854711</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.02433643240416838</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1414224912849017</v>
+      </c>
+      <c r="C23">
+        <v>9.477659650724567</v>
+      </c>
+      <c r="D23">
+        <v>14.44955965072457</v>
+      </c>
+      <c r="E23">
+        <v>3.8689</v>
+      </c>
+      <c r="F23">
+        <v>5.0589</v>
+      </c>
+      <c r="G23">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H23">
+        <v>22.9</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>-0.028</v>
+      </c>
+      <c r="L23">
+        <v>0.028</v>
+      </c>
+      <c r="M23">
+        <v>1.20806532</v>
+      </c>
+      <c r="N23">
+        <v>-1.18006532</v>
+      </c>
+      <c r="O23">
+        <v>-0.29501633</v>
+      </c>
+      <c r="P23">
+        <v>-0.88504899</v>
+      </c>
+      <c r="Q23">
+        <v>-0.9130489900000001</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1159051497314019</v>
+      </c>
+      <c r="T23">
+        <v>0.8380500201117815</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.00579438866765913</v>
+      </c>
+      <c r="W23">
+        <v>0.237416299986163</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.02317755467063654</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1434224912849018</v>
+      </c>
+      <c r="C24">
+        <v>8.960536833369233</v>
+      </c>
+      <c r="D24">
+        <v>14.17333683336923</v>
+      </c>
+      <c r="E24">
+        <v>4.1098</v>
+      </c>
+      <c r="F24">
+        <v>5.2998</v>
+      </c>
+      <c r="G24">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H24">
+        <v>22.9</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>-0.028</v>
+      </c>
+      <c r="L24">
+        <v>0.028</v>
+      </c>
+      <c r="M24">
+        <v>1.26559224</v>
+      </c>
+      <c r="N24">
+        <v>-1.23759224</v>
+      </c>
+      <c r="O24">
+        <v>-0.30939806</v>
+      </c>
+      <c r="P24">
+        <v>-0.9281941800000001</v>
+      </c>
+      <c r="Q24">
+        <v>-0.9561941800000001</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1168936772920609</v>
+      </c>
+      <c r="T24">
+        <v>0.8487942511388558</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.005531007364583714</v>
+      </c>
+      <c r="W24">
+        <v>0.2374791954413374</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.02212402945833492</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1454224912849017</v>
+      </c>
+      <c r="C25">
+        <v>8.453776663295042</v>
+      </c>
+      <c r="D25">
+        <v>13.90747666329504</v>
+      </c>
+      <c r="E25">
+        <v>4.3507</v>
+      </c>
+      <c r="F25">
+        <v>5.5407</v>
+      </c>
+      <c r="G25">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H25">
+        <v>22.9</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>-0.028</v>
+      </c>
+      <c r="L25">
+        <v>0.028</v>
+      </c>
+      <c r="M25">
+        <v>1.32311916</v>
+      </c>
+      <c r="N25">
+        <v>-1.29511916</v>
+      </c>
+      <c r="O25">
+        <v>-0.32377979</v>
+      </c>
+      <c r="P25">
+        <v>-0.97133937</v>
+      </c>
+      <c r="Q25">
+        <v>-0.9993393700000001</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1179078808932565</v>
+      </c>
+      <c r="T25">
+        <v>0.8598175531016979</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.005290528783514857</v>
+      </c>
+      <c r="W25">
+        <v>0.2375366217264967</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.02116211513405941</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1474224912849017</v>
+      </c>
+      <c r="C26">
+        <v>7.956806737098675</v>
+      </c>
+      <c r="D26">
+        <v>13.65140673709868</v>
+      </c>
+      <c r="E26">
+        <v>4.5916</v>
+      </c>
+      <c r="F26">
+        <v>5.7816</v>
+      </c>
+      <c r="G26">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H26">
+        <v>22.9</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>-0.028</v>
+      </c>
+      <c r="L26">
+        <v>0.028</v>
+      </c>
+      <c r="M26">
+        <v>1.38064608</v>
+      </c>
+      <c r="N26">
+        <v>-1.35264608</v>
+      </c>
+      <c r="O26">
+        <v>-0.33816152</v>
+      </c>
+      <c r="P26">
+        <v>-1.01448456</v>
+      </c>
+      <c r="Q26">
+        <v>-1.04248456</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1189487740629046</v>
+      </c>
+      <c r="T26">
+        <v>0.8711309419582993</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.005070090084201739</v>
+      </c>
+      <c r="W26">
+        <v>0.2375892624878926</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.02028036033680702</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1494224912849017</v>
+      </c>
+      <c r="C27">
+        <v>7.469096046460002</v>
+      </c>
+      <c r="D27">
+        <v>13.40459604646</v>
+      </c>
+      <c r="E27">
+        <v>4.8325</v>
+      </c>
+      <c r="F27">
+        <v>6.0225</v>
+      </c>
+      <c r="G27">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H27">
+        <v>22.9</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>-0.028</v>
+      </c>
+      <c r="L27">
+        <v>0.028</v>
+      </c>
+      <c r="M27">
+        <v>1.438173</v>
+      </c>
+      <c r="N27">
+        <v>-1.410173</v>
+      </c>
+      <c r="O27">
+        <v>-0.35254325</v>
+      </c>
+      <c r="P27">
+        <v>-1.05762975</v>
+      </c>
+      <c r="Q27">
+        <v>-1.08562975</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1200174243837433</v>
+      </c>
+      <c r="T27">
+        <v>0.8827460211844099</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.004867286480833668</v>
+      </c>
+      <c r="W27">
+        <v>0.2376376919883769</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.01946914592333471</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1514224912849017</v>
+      </c>
+      <c r="C28">
+        <v>6.990151302581082</v>
+      </c>
+      <c r="D28">
+        <v>13.16655130258108</v>
+      </c>
+      <c r="E28">
+        <v>5.073399999999999</v>
+      </c>
+      <c r="F28">
+        <v>6.2634</v>
+      </c>
+      <c r="G28">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H28">
+        <v>22.9</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>-0.028</v>
+      </c>
+      <c r="L28">
+        <v>0.028</v>
+      </c>
+      <c r="M28">
+        <v>1.49569992</v>
+      </c>
+      <c r="N28">
+        <v>-1.46769992</v>
+      </c>
+      <c r="O28">
+        <v>-0.36692498</v>
+      </c>
+      <c r="P28">
+        <v>-1.10077494</v>
+      </c>
+      <c r="Q28">
+        <v>-1.12877494</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1211149571456858</v>
+      </c>
+      <c r="T28">
+        <v>0.8946750214706858</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.004680083154647758</v>
+      </c>
+      <c r="W28">
+        <v>0.2376823961426701</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.01872033261859107</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1534224912849017</v>
+      </c>
+      <c r="C29">
+        <v>6.519513645425214</v>
+      </c>
+      <c r="D29">
+        <v>12.93681364542521</v>
+      </c>
+      <c r="E29">
+        <v>5.314300000000001</v>
+      </c>
+      <c r="F29">
+        <v>6.504300000000001</v>
+      </c>
+      <c r="G29">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H29">
+        <v>22.9</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>-0.028</v>
+      </c>
+      <c r="L29">
+        <v>0.028</v>
+      </c>
+      <c r="M29">
+        <v>1.55322684</v>
+      </c>
+      <c r="N29">
+        <v>-1.52522684</v>
+      </c>
+      <c r="O29">
+        <v>-0.38130671</v>
+      </c>
+      <c r="P29">
+        <v>-1.14392013</v>
+      </c>
+      <c r="Q29">
+        <v>-1.17192013</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1222425592983664</v>
+      </c>
+      <c r="T29">
+        <v>0.906930843682613</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.004506746741512656</v>
+      </c>
+      <c r="W29">
+        <v>0.2377237888781268</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.01802698696605065</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1554224912849018</v>
+      </c>
+      <c r="C30">
+        <v>6.056755691562413</v>
+      </c>
+      <c r="D30">
+        <v>12.71495569156241</v>
+      </c>
+      <c r="E30">
+        <v>5.555200000000001</v>
+      </c>
+      <c r="F30">
+        <v>6.745200000000001</v>
+      </c>
+      <c r="G30">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H30">
+        <v>22.9</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>-0.028</v>
+      </c>
+      <c r="L30">
+        <v>0.028</v>
+      </c>
+      <c r="M30">
+        <v>1.61075376</v>
+      </c>
+      <c r="N30">
+        <v>-1.58275376</v>
+      </c>
+      <c r="O30">
+        <v>-0.39568844</v>
+      </c>
+      <c r="P30">
+        <v>-1.18706532</v>
+      </c>
+      <c r="Q30">
+        <v>-1.21506532</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.123401483733066</v>
+      </c>
+      <c r="T30">
+        <v>0.9195271054004271</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.004345791500744347</v>
+      </c>
+      <c r="W30">
+        <v>0.2377622249896223</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.0173831660029774</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1574224912849017</v>
+      </c>
+      <c r="C31">
+        <v>5.601478880658589</v>
+      </c>
+      <c r="D31">
+        <v>12.50057888065859</v>
+      </c>
+      <c r="E31">
+        <v>5.796099999999999</v>
+      </c>
+      <c r="F31">
+        <v>6.9861</v>
+      </c>
+      <c r="G31">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H31">
+        <v>22.9</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>-0.028</v>
+      </c>
+      <c r="L31">
+        <v>0.028</v>
+      </c>
+      <c r="M31">
+        <v>1.66828068</v>
+      </c>
+      <c r="N31">
+        <v>-1.64028068</v>
+      </c>
+      <c r="O31">
+        <v>-0.41007017</v>
+      </c>
+      <c r="P31">
+        <v>-1.23021051</v>
+      </c>
+      <c r="Q31">
+        <v>-1.25821051</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1245930539264894</v>
+      </c>
+      <c r="T31">
+        <v>0.9324781913919823</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.004195936621408335</v>
+      </c>
+      <c r="W31">
+        <v>0.2377980103348077</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.0167837464856333</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1594224912849017</v>
+      </c>
+      <c r="C32">
+        <v>5.153311085946354</v>
+      </c>
+      <c r="D32">
+        <v>12.29331108594635</v>
+      </c>
+      <c r="E32">
+        <v>6.036999999999999</v>
+      </c>
+      <c r="F32">
+        <v>7.226999999999999</v>
+      </c>
+      <c r="G32">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H32">
+        <v>22.9</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>-0.028</v>
+      </c>
+      <c r="L32">
+        <v>0.028</v>
+      </c>
+      <c r="M32">
+        <v>1.7258076</v>
+      </c>
+      <c r="N32">
+        <v>-1.6978076</v>
+      </c>
+      <c r="O32">
+        <v>-0.4244519</v>
+      </c>
+      <c r="P32">
+        <v>-1.2733557</v>
+      </c>
+      <c r="Q32">
+        <v>-1.3013557</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1258186689825821</v>
+      </c>
+      <c r="T32">
+        <v>0.9457993084118679</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.004056072067361391</v>
+      </c>
+      <c r="W32">
+        <v>0.2378314099903141</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.01622428826944555</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1614224912849017</v>
+      </c>
+      <c r="C33">
+        <v>4.711904458538434</v>
+      </c>
+      <c r="D33">
+        <v>12.09280445853843</v>
+      </c>
+      <c r="E33">
+        <v>6.277900000000001</v>
+      </c>
+      <c r="F33">
+        <v>7.4679</v>
+      </c>
+      <c r="G33">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H33">
+        <v>22.9</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>-0.028</v>
+      </c>
+      <c r="L33">
+        <v>0.028</v>
+      </c>
+      <c r="M33">
+        <v>1.78333452</v>
+      </c>
+      <c r="N33">
+        <v>-1.75533452</v>
+      </c>
+      <c r="O33">
+        <v>-0.43883363</v>
+      </c>
+      <c r="P33">
+        <v>-1.31650089</v>
+      </c>
+      <c r="Q33">
+        <v>-1.34450089</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1270798091127645</v>
+      </c>
+      <c r="T33">
+        <v>0.959506544765663</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.003925231032930378</v>
+      </c>
+      <c r="W33">
+        <v>0.2378626548293362</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.01570092413172153</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1634224912849017</v>
+      </c>
+      <c r="C34">
+        <v>4.276933479313778</v>
+      </c>
+      <c r="D34">
+        <v>11.89873347931378</v>
+      </c>
+      <c r="E34">
+        <v>6.518800000000001</v>
+      </c>
+      <c r="F34">
+        <v>7.7088</v>
+      </c>
+      <c r="G34">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H34">
+        <v>22.9</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>-0.028</v>
+      </c>
+      <c r="L34">
+        <v>0.028</v>
+      </c>
+      <c r="M34">
+        <v>1.84086144</v>
+      </c>
+      <c r="N34">
+        <v>-1.81286144</v>
+      </c>
+      <c r="O34">
+        <v>-0.45321536</v>
+      </c>
+      <c r="P34">
+        <v>-1.35964608</v>
+      </c>
+      <c r="Q34">
+        <v>-1.38764608</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1283780415997169</v>
+      </c>
+      <c r="T34">
+        <v>0.9736169351298639</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.003802567563151304</v>
+      </c>
+      <c r="W34">
+        <v>0.2378919468659195</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.01521027025260524</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1654224912849017</v>
+      </c>
+      <c r="C35">
+        <v>3.848093195426271</v>
+      </c>
+      <c r="D35">
+        <v>11.71079319542627</v>
+      </c>
+      <c r="E35">
+        <v>6.7597</v>
+      </c>
+      <c r="F35">
+        <v>7.9497</v>
+      </c>
+      <c r="G35">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H35">
+        <v>22.9</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>-0.028</v>
+      </c>
+      <c r="L35">
+        <v>0.028</v>
+      </c>
+      <c r="M35">
+        <v>1.89838836</v>
+      </c>
+      <c r="N35">
+        <v>-1.87038836</v>
+      </c>
+      <c r="O35">
+        <v>-0.46759709</v>
+      </c>
+      <c r="P35">
+        <v>-1.40279127</v>
+      </c>
+      <c r="Q35">
+        <v>-1.43079127</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1297150272952351</v>
+      </c>
+      <c r="T35">
+        <v>0.9881485311765784</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.00368733824305581</v>
+      </c>
+      <c r="W35">
+        <v>0.2379194636275583</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.01474935297222324</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1674224912849017</v>
+      </c>
+      <c r="C36">
+        <v>3.42509762134061</v>
+      </c>
+      <c r="D36">
+        <v>11.52869762134061</v>
+      </c>
+      <c r="E36">
+        <v>7.0006</v>
+      </c>
+      <c r="F36">
+        <v>8.1906</v>
+      </c>
+      <c r="G36">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H36">
+        <v>22.9</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>-0.028</v>
+      </c>
+      <c r="L36">
+        <v>0.028</v>
+      </c>
+      <c r="M36">
+        <v>1.95591528</v>
+      </c>
+      <c r="N36">
+        <v>-1.92791528</v>
+      </c>
+      <c r="O36">
+        <v>-0.48197882</v>
+      </c>
+      <c r="P36">
+        <v>-1.44593646</v>
+      </c>
+      <c r="Q36">
+        <v>-1.47393646</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1310925277087993</v>
+      </c>
+      <c r="T36">
+        <v>1.003120478618648</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.00357888711826005</v>
+      </c>
+      <c r="W36">
+        <v>0.2379453617561595</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.01431554847304017</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1694224912849017</v>
+      </c>
+      <c r="C37">
+        <v>3.007678286761459</v>
+      </c>
+      <c r="D37">
+        <v>11.35217828676146</v>
+      </c>
+      <c r="E37">
+        <v>7.241500000000002</v>
+      </c>
+      <c r="F37">
+        <v>8.431500000000002</v>
+      </c>
+      <c r="G37">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H37">
+        <v>22.9</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>-0.028</v>
+      </c>
+      <c r="L37">
+        <v>0.028</v>
+      </c>
+      <c r="M37">
+        <v>2.013442200000001</v>
+      </c>
+      <c r="N37">
+        <v>-1.9854422</v>
+      </c>
+      <c r="O37">
+        <v>-0.4963605500000001</v>
+      </c>
+      <c r="P37">
+        <v>-1.48908165</v>
+      </c>
+      <c r="Q37">
+        <v>-1.51708165</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1325124127504731</v>
+      </c>
+      <c r="T37">
+        <v>1.018553101366627</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.003476633200595477</v>
+      </c>
+      <c r="W37">
+        <v>0.2379697799916978</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.01390653280238197</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1714224912849017</v>
+      </c>
+      <c r="C38">
+        <v>2.595582915949516</v>
+      </c>
+      <c r="D38">
+        <v>11.18098291594952</v>
+      </c>
+      <c r="E38">
+        <v>7.4824</v>
+      </c>
+      <c r="F38">
+        <v>8.6724</v>
+      </c>
+      <c r="G38">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H38">
+        <v>22.9</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>-0.028</v>
+      </c>
+      <c r="L38">
+        <v>0.028</v>
+      </c>
+      <c r="M38">
+        <v>2.07096912</v>
+      </c>
+      <c r="N38">
+        <v>-2.04296912</v>
+      </c>
+      <c r="O38">
+        <v>-0.51074228</v>
+      </c>
+      <c r="P38">
+        <v>-1.53222684</v>
+      </c>
+      <c r="Q38">
+        <v>-1.56022684</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1339766691996992</v>
+      </c>
+      <c r="T38">
+        <v>1.03446799357548</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.003380060056134492</v>
+      </c>
+      <c r="W38">
+        <v>0.2379928416585951</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.01352024022453802</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1734224912849017</v>
+      </c>
+      <c r="C39">
+        <v>2.188574224760803</v>
+      </c>
+      <c r="D39">
+        <v>11.0148742247608</v>
+      </c>
+      <c r="E39">
+        <v>7.7233</v>
+      </c>
+      <c r="F39">
+        <v>8.9133</v>
+      </c>
+      <c r="G39">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H39">
+        <v>22.9</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>-0.028</v>
+      </c>
+      <c r="L39">
+        <v>0.028</v>
+      </c>
+      <c r="M39">
+        <v>2.12849604</v>
+      </c>
+      <c r="N39">
+        <v>-2.10049604</v>
+      </c>
+      <c r="O39">
+        <v>-0.52512401</v>
+      </c>
+      <c r="P39">
+        <v>-1.57537203</v>
+      </c>
+      <c r="Q39">
+        <v>-1.60337203</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1354874099806468</v>
+      </c>
+      <c r="T39">
+        <v>1.050888120457631</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.003288707081644371</v>
+      </c>
+      <c r="W39">
+        <v>0.2380146567489033</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.01315482832657755</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1754224912849017</v>
+      </c>
+      <c r="C40">
+        <v>1.78642882334602</v>
+      </c>
+      <c r="D40">
+        <v>10.85362882334602</v>
+      </c>
+      <c r="E40">
+        <v>7.9642</v>
+      </c>
+      <c r="F40">
+        <v>9.154199999999999</v>
+      </c>
+      <c r="G40">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H40">
+        <v>22.9</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>-0.028</v>
+      </c>
+      <c r="L40">
+        <v>0.028</v>
+      </c>
+      <c r="M40">
+        <v>2.18602296</v>
+      </c>
+      <c r="N40">
+        <v>-2.15802296</v>
+      </c>
+      <c r="O40">
+        <v>-0.53950574</v>
+      </c>
+      <c r="P40">
+        <v>-1.61851722</v>
+      </c>
+      <c r="Q40">
+        <v>-1.64651722</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1370468843351734</v>
+      </c>
+      <c r="T40">
+        <v>1.067837928852109</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.003202162158443204</v>
+      </c>
+      <c r="W40">
+        <v>0.2380353236765638</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.01280864863377285</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1774224912849017</v>
+      </c>
+      <c r="C41">
+        <v>1.388936213838818</v>
+      </c>
+      <c r="D41">
+        <v>10.69703621383882</v>
+      </c>
+      <c r="E41">
+        <v>8.205100000000002</v>
+      </c>
+      <c r="F41">
+        <v>9.395100000000001</v>
+      </c>
+      <c r="G41">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H41">
+        <v>22.9</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>-0.028</v>
+      </c>
+      <c r="L41">
+        <v>0.028</v>
+      </c>
+      <c r="M41">
+        <v>2.24354988</v>
+      </c>
+      <c r="N41">
+        <v>-2.21554988</v>
+      </c>
+      <c r="O41">
+        <v>-0.55388747</v>
+      </c>
+      <c r="P41">
+        <v>-1.66166241</v>
+      </c>
+      <c r="Q41">
+        <v>-1.68966241</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1386574889964057</v>
+      </c>
+      <c r="T41">
+        <v>1.085343468669357</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.003120055436431839</v>
+      </c>
+      <c r="W41">
+        <v>0.2380549307617801</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.01248022174572738</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1794224912849017</v>
+      </c>
+      <c r="C42">
+        <v>0.9958978735762098</v>
+      </c>
+      <c r="D42">
+        <v>10.54489787357621</v>
+      </c>
+      <c r="E42">
+        <v>8.446000000000002</v>
+      </c>
+      <c r="F42">
+        <v>9.636000000000001</v>
+      </c>
+      <c r="G42">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H42">
+        <v>22.9</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>-0.028</v>
+      </c>
+      <c r="L42">
+        <v>0.028</v>
+      </c>
+      <c r="M42">
+        <v>2.3010768</v>
+      </c>
+      <c r="N42">
+        <v>-2.2730768</v>
+      </c>
+      <c r="O42">
+        <v>-0.5682692</v>
+      </c>
+      <c r="P42">
+        <v>-1.7048076</v>
+      </c>
+      <c r="Q42">
+        <v>-1.7328076</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1403217804796792</v>
+      </c>
+      <c r="T42">
+        <v>1.103432526480512</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.003042054050521043</v>
+      </c>
+      <c r="W42">
+        <v>0.2380735574927356</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.01216821620208419</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1814224912849017</v>
+      </c>
+      <c r="C43">
+        <v>0.6071264154551805</v>
+      </c>
+      <c r="D43">
+        <v>10.39702641545518</v>
+      </c>
+      <c r="E43">
+        <v>8.686900000000001</v>
+      </c>
+      <c r="F43">
+        <v>9.876900000000001</v>
+      </c>
+      <c r="G43">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H43">
+        <v>22.9</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>-0.028</v>
+      </c>
+      <c r="L43">
+        <v>0.028</v>
+      </c>
+      <c r="M43">
+        <v>2.358603720000001</v>
+      </c>
+      <c r="N43">
+        <v>-2.33060372</v>
+      </c>
+      <c r="O43">
+        <v>-0.5826509300000001</v>
+      </c>
+      <c r="P43">
+        <v>-1.74795279</v>
+      </c>
+      <c r="Q43">
+        <v>-1.77595279</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1420424886234025</v>
+      </c>
+      <c r="T43">
+        <v>1.122134772692047</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.002967857610264432</v>
+      </c>
+      <c r="W43">
+        <v>0.2380912756026689</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.01187143044105776</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1834224912849017</v>
+      </c>
+      <c r="C44">
+        <v>0.2224448179583813</v>
+      </c>
+      <c r="D44">
+        <v>10.25324481795838</v>
+      </c>
+      <c r="E44">
+        <v>8.9278</v>
+      </c>
+      <c r="F44">
+        <v>10.1178</v>
+      </c>
+      <c r="G44">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H44">
+        <v>22.9</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>-0.028</v>
+      </c>
+      <c r="L44">
+        <v>0.028</v>
+      </c>
+      <c r="M44">
+        <v>2.41613064</v>
+      </c>
+      <c r="N44">
+        <v>-2.38813064</v>
+      </c>
+      <c r="O44">
+        <v>-0.59703266</v>
+      </c>
+      <c r="P44">
+        <v>-1.79109798</v>
+      </c>
+      <c r="Q44">
+        <v>-1.81909798</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1438225315307026</v>
+      </c>
+      <c r="T44">
+        <v>1.141481923945358</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.002897194333829565</v>
+      </c>
+      <c r="W44">
+        <v>0.2381081499930815</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.01158877733531827</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1854224912849018</v>
+      </c>
+      <c r="C45">
+        <v>-0.158314281803273</v>
+      </c>
+      <c r="D45">
+        <v>10.11338571819673</v>
+      </c>
+      <c r="E45">
+        <v>9.168699999999999</v>
+      </c>
+      <c r="F45">
+        <v>10.3587</v>
+      </c>
+      <c r="G45">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H45">
+        <v>22.9</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>-0.028</v>
+      </c>
+      <c r="L45">
+        <v>0.028</v>
+      </c>
+      <c r="M45">
+        <v>2.47365756</v>
+      </c>
+      <c r="N45">
+        <v>-2.44565756</v>
+      </c>
+      <c r="O45">
+        <v>-0.61141439</v>
+      </c>
+      <c r="P45">
+        <v>-1.83424317</v>
+      </c>
+      <c r="Q45">
+        <v>-1.86224317</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1456650320838728</v>
+      </c>
+      <c r="T45">
+        <v>1.161507922611066</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.002829817721414924</v>
+      </c>
+      <c r="W45">
+        <v>0.2381242395281261</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.01131927088565976</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1874224912849017</v>
+      </c>
+      <c r="C46">
+        <v>-0.5353092379672049</v>
+      </c>
+      <c r="D46">
+        <v>9.977290762032796</v>
+      </c>
+      <c r="E46">
+        <v>9.409600000000001</v>
+      </c>
+      <c r="F46">
+        <v>10.5996</v>
+      </c>
+      <c r="G46">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H46">
+        <v>22.9</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>-0.028</v>
+      </c>
+      <c r="L46">
+        <v>0.028</v>
+      </c>
+      <c r="M46">
+        <v>2.53118448</v>
+      </c>
+      <c r="N46">
+        <v>-2.50318448</v>
+      </c>
+      <c r="O46">
+        <v>-0.6257961200000001</v>
+      </c>
+      <c r="P46">
+        <v>-1.87738836</v>
+      </c>
+      <c r="Q46">
+        <v>-1.90538836</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1475733362282277</v>
+      </c>
+      <c r="T46">
+        <v>1.182249135514835</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.002765503682291857</v>
+      </c>
+      <c r="W46">
+        <v>0.2381395977206687</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.01106201472916746</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1894224912849017</v>
+      </c>
+      <c r="C47">
+        <v>-0.9086899940205733</v>
+      </c>
+      <c r="D47">
+        <v>9.844810005979427</v>
+      </c>
+      <c r="E47">
+        <v>9.650500000000001</v>
+      </c>
+      <c r="F47">
+        <v>10.8405</v>
+      </c>
+      <c r="G47">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H47">
+        <v>22.9</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>-0.028</v>
+      </c>
+      <c r="L47">
+        <v>0.028</v>
+      </c>
+      <c r="M47">
+        <v>2.5887114</v>
+      </c>
+      <c r="N47">
+        <v>-2.5607114</v>
+      </c>
+      <c r="O47">
+        <v>-0.64017785</v>
+      </c>
+      <c r="P47">
+        <v>-1.92053355</v>
+      </c>
+      <c r="Q47">
+        <v>-1.94853355</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1495510332505591</v>
+      </c>
+      <c r="T47">
+        <v>1.203744574342377</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.002704048044907594</v>
+      </c>
+      <c r="W47">
+        <v>0.2381542733268761</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.01081619217963037</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1914224912849017</v>
+      </c>
+      <c r="C48">
+        <v>-1.278598633875653</v>
+      </c>
+      <c r="D48">
+        <v>9.715801366124348</v>
+      </c>
+      <c r="E48">
+        <v>9.891400000000001</v>
+      </c>
+      <c r="F48">
+        <v>11.0814</v>
+      </c>
+      <c r="G48">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H48">
+        <v>22.9</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>-0.028</v>
+      </c>
+      <c r="L48">
+        <v>0.028</v>
+      </c>
+      <c r="M48">
+        <v>2.64623832</v>
+      </c>
+      <c r="N48">
+        <v>-2.61823832</v>
+      </c>
+      <c r="O48">
+        <v>-0.65455958</v>
+      </c>
+      <c r="P48">
+        <v>-1.96367874</v>
+      </c>
+      <c r="Q48">
+        <v>-1.99167874</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1516019783107546</v>
+      </c>
+      <c r="T48">
+        <v>1.226036140533903</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.002645264391757429</v>
+      </c>
+      <c r="W48">
+        <v>0.2381683108632484</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.01058105756702976</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1934224912849018</v>
+      </c>
+      <c r="C49">
+        <v>-1.645169890177202</v>
+      </c>
+      <c r="D49">
+        <v>9.590130109822798</v>
+      </c>
+      <c r="E49">
+        <v>10.1323</v>
+      </c>
+      <c r="F49">
+        <v>11.3223</v>
+      </c>
+      <c r="G49">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H49">
+        <v>22.9</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>-0.028</v>
+      </c>
+      <c r="L49">
+        <v>0.028</v>
+      </c>
+      <c r="M49">
+        <v>2.70376524</v>
+      </c>
+      <c r="N49">
+        <v>-2.67576524</v>
+      </c>
+      <c r="O49">
+        <v>-0.66894131</v>
+      </c>
+      <c r="P49">
+        <v>-2.00682393</v>
+      </c>
+      <c r="Q49">
+        <v>-2.03482393</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1537303175241651</v>
+      </c>
+      <c r="T49">
+        <v>1.249168897902467</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.002588982170656207</v>
+      </c>
+      <c r="W49">
+        <v>0.2381817510576473</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.0103559286826248</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1954224912849017</v>
+      </c>
+      <c r="C50">
+        <v>-2.008531613664641</v>
+      </c>
+      <c r="D50">
+        <v>9.46766838633536</v>
+      </c>
+      <c r="E50">
+        <v>10.3732</v>
+      </c>
+      <c r="F50">
+        <v>11.5632</v>
+      </c>
+      <c r="G50">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H50">
+        <v>22.9</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>-0.028</v>
+      </c>
+      <c r="L50">
+        <v>0.028</v>
+      </c>
+      <c r="M50">
+        <v>2.76129216</v>
+      </c>
+      <c r="N50">
+        <v>-2.73329216</v>
+      </c>
+      <c r="O50">
+        <v>-0.68332304</v>
+      </c>
+      <c r="P50">
+        <v>-2.04996912</v>
+      </c>
+      <c r="Q50">
+        <v>-2.07796912</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1559405159380913</v>
+      </c>
+      <c r="T50">
+        <v>1.273191376708284</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.002535045042100869</v>
+      </c>
+      <c r="W50">
+        <v>0.2381946312439463</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.01014018016840346</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1974224912849017</v>
+      </c>
+      <c r="C51">
+        <v>-2.368805207026384</v>
+      </c>
+      <c r="D51">
+        <v>9.348294792973617</v>
+      </c>
+      <c r="E51">
+        <v>10.6141</v>
+      </c>
+      <c r="F51">
+        <v>11.8041</v>
+      </c>
+      <c r="G51">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H51">
+        <v>22.9</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>-0.028</v>
+      </c>
+      <c r="L51">
+        <v>0.028</v>
+      </c>
+      <c r="M51">
+        <v>2.81881908</v>
+      </c>
+      <c r="N51">
+        <v>-2.79081908</v>
+      </c>
+      <c r="O51">
+        <v>-0.6977047700000001</v>
+      </c>
+      <c r="P51">
+        <v>-2.09311431</v>
+      </c>
+      <c r="Q51">
+        <v>-2.12111431</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1582373887996226</v>
+      </c>
+      <c r="T51">
+        <v>1.298155913506485</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.002483309428996769</v>
+      </c>
+      <c r="W51">
+        <v>0.2382069857083556</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.009933237715987087</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1994224912849017</v>
+      </c>
+      <c r="C52">
+        <v>-2.726106026341185</v>
+      </c>
+      <c r="D52">
+        <v>9.231893973658815</v>
+      </c>
+      <c r="E52">
+        <v>10.855</v>
+      </c>
+      <c r="F52">
+        <v>12.045</v>
+      </c>
+      <c r="G52">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H52">
+        <v>22.9</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>-0.028</v>
+      </c>
+      <c r="L52">
+        <v>0.028</v>
+      </c>
+      <c r="M52">
+        <v>2.876346</v>
+      </c>
+      <c r="N52">
+        <v>-2.848346</v>
+      </c>
+      <c r="O52">
+        <v>-0.7120865000000001</v>
+      </c>
+      <c r="P52">
+        <v>-2.1362595</v>
+      </c>
+      <c r="Q52">
+        <v>-2.1642595</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.160626136575615</v>
+      </c>
+      <c r="T52">
+        <v>1.324119031776615</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.002433643240416834</v>
+      </c>
+      <c r="W52">
+        <v>0.2382188459941885</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.009734572961667354</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2014224912849018</v>
+      </c>
+      <c r="C53">
+        <v>-3.080543752896924</v>
+      </c>
+      <c r="D53">
+        <v>9.118356247103076</v>
+      </c>
+      <c r="E53">
+        <v>11.0959</v>
+      </c>
+      <c r="F53">
+        <v>12.2859</v>
+      </c>
+      <c r="G53">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H53">
+        <v>22.9</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>-0.028</v>
+      </c>
+      <c r="L53">
+        <v>0.028</v>
+      </c>
+      <c r="M53">
+        <v>2.93387292</v>
+      </c>
+      <c r="N53">
+        <v>-2.90587292</v>
+      </c>
+      <c r="O53">
+        <v>-0.72646823</v>
+      </c>
+      <c r="P53">
+        <v>-2.17940469</v>
+      </c>
+      <c r="Q53">
+        <v>-2.20740469</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1631123842608316</v>
+      </c>
+      <c r="T53">
+        <v>1.351141869159811</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.0023859247455067</v>
+      </c>
+      <c r="W53">
+        <v>0.238230241170773</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.009543698982026783</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2034224912849018</v>
+      </c>
+      <c r="C54">
+        <v>-3.432222737905994</v>
+      </c>
+      <c r="D54">
+        <v>9.007577262094006</v>
+      </c>
+      <c r="E54">
+        <v>11.3368</v>
+      </c>
+      <c r="F54">
+        <v>12.5268</v>
+      </c>
+      <c r="G54">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H54">
+        <v>22.9</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>-0.028</v>
+      </c>
+      <c r="L54">
+        <v>0.028</v>
+      </c>
+      <c r="M54">
+        <v>2.99139984</v>
+      </c>
+      <c r="N54">
+        <v>-2.96339984</v>
+      </c>
+      <c r="O54">
+        <v>-0.74084996</v>
+      </c>
+      <c r="P54">
+        <v>-2.22254988</v>
+      </c>
+      <c r="Q54">
+        <v>-2.25054988</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.165702225599599</v>
+      </c>
+      <c r="T54">
+        <v>1.379290658100641</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.002340041577323879</v>
+      </c>
+      <c r="W54">
+        <v>0.2382411980713351</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.009360166309295481</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2054224912849018</v>
+      </c>
+      <c r="C55">
+        <v>-3.78124232239465</v>
+      </c>
+      <c r="D55">
+        <v>8.899457677605351</v>
+      </c>
+      <c r="E55">
+        <v>11.5777</v>
+      </c>
+      <c r="F55">
+        <v>12.7677</v>
+      </c>
+      <c r="G55">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H55">
+        <v>22.9</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>-0.028</v>
+      </c>
+      <c r="L55">
+        <v>0.028</v>
+      </c>
+      <c r="M55">
+        <v>3.048926760000001</v>
+      </c>
+      <c r="N55">
+        <v>-3.02092676</v>
+      </c>
+      <c r="O55">
+        <v>-0.7552316900000001</v>
+      </c>
+      <c r="P55">
+        <v>-2.26569507</v>
+      </c>
+      <c r="Q55">
+        <v>-2.293695070000001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1684022729527819</v>
+      </c>
+      <c r="T55">
+        <v>1.408637267847463</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.002295889849449844</v>
+      </c>
+      <c r="W55">
+        <v>0.2382517415039514</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.009183559397799357</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2074224912849018</v>
+      </c>
+      <c r="C56">
+        <v>-4.127697134327407</v>
+      </c>
+      <c r="D56">
+        <v>8.793902865672594</v>
+      </c>
+      <c r="E56">
+        <v>11.8186</v>
+      </c>
+      <c r="F56">
+        <v>13.0086</v>
+      </c>
+      <c r="G56">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H56">
+        <v>22.9</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>-0.028</v>
+      </c>
+      <c r="L56">
+        <v>0.028</v>
+      </c>
+      <c r="M56">
+        <v>3.10645368</v>
+      </c>
+      <c r="N56">
+        <v>-3.07845368</v>
+      </c>
+      <c r="O56">
+        <v>-0.7696134200000001</v>
+      </c>
+      <c r="P56">
+        <v>-2.30884026</v>
+      </c>
+      <c r="Q56">
+        <v>-2.33684026</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1712197136691468</v>
+      </c>
+      <c r="T56">
+        <v>1.439259817148495</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.002253373370756328</v>
+      </c>
+      <c r="W56">
+        <v>0.2382618944390634</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.00901349348302527</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2094224912849018</v>
+      </c>
+      <c r="C57">
+        <v>-4.471677364834518</v>
+      </c>
+      <c r="D57">
+        <v>8.690822635165484</v>
+      </c>
+      <c r="E57">
+        <v>12.0595</v>
+      </c>
+      <c r="F57">
+        <v>13.2495</v>
+      </c>
+      <c r="G57">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H57">
+        <v>22.9</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>-0.028</v>
+      </c>
+      <c r="L57">
+        <v>0.028</v>
+      </c>
+      <c r="M57">
+        <v>3.1639806</v>
+      </c>
+      <c r="N57">
+        <v>-3.1359806</v>
+      </c>
+      <c r="O57">
+        <v>-0.7839951500000001</v>
+      </c>
+      <c r="P57">
+        <v>-2.35198545</v>
+      </c>
+      <c r="Q57">
+        <v>-2.37998545</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1741623739729056</v>
+      </c>
+      <c r="T57">
+        <v>1.471243368640684</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.002212402945833486</v>
+      </c>
+      <c r="W57">
+        <v>0.238271678176535</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.008849611783333988</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2114224912849018</v>
+      </c>
+      <c r="C58">
+        <v>-4.81326902523724</v>
+      </c>
+      <c r="D58">
+        <v>8.590130974762761</v>
+      </c>
+      <c r="E58">
+        <v>12.3004</v>
+      </c>
+      <c r="F58">
+        <v>13.4904</v>
+      </c>
+      <c r="G58">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H58">
+        <v>22.9</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>-0.028</v>
+      </c>
+      <c r="L58">
+        <v>0.028</v>
+      </c>
+      <c r="M58">
+        <v>3.22150752</v>
+      </c>
+      <c r="N58">
+        <v>-3.19350752</v>
+      </c>
+      <c r="O58">
+        <v>-0.7983768800000001</v>
+      </c>
+      <c r="P58">
+        <v>-2.39513064</v>
+      </c>
+      <c r="Q58">
+        <v>-2.42313064</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1772387915631989</v>
+      </c>
+      <c r="T58">
+        <v>1.504680717927972</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.002172895750372173</v>
+      </c>
+      <c r="W58">
+        <v>0.2382811124948112</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.008691583001488756</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2134224912849017</v>
+      </c>
+      <c r="C59">
+        <v>-5.152554186410407</v>
+      </c>
+      <c r="D59">
+        <v>8.491745813589594</v>
+      </c>
+      <c r="E59">
+        <v>12.5413</v>
+      </c>
+      <c r="F59">
+        <v>13.7313</v>
+      </c>
+      <c r="G59">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H59">
+        <v>22.9</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>-0.028</v>
+      </c>
+      <c r="L59">
+        <v>0.028</v>
+      </c>
+      <c r="M59">
+        <v>3.27903444</v>
+      </c>
+      <c r="N59">
+        <v>-3.25103444</v>
+      </c>
+      <c r="O59">
+        <v>-0.81275861</v>
+      </c>
+      <c r="P59">
+        <v>-2.43827583</v>
+      </c>
+      <c r="Q59">
+        <v>-2.46627583</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1804582983437384</v>
+      </c>
+      <c r="T59">
+        <v>1.539673292763506</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.002134774772295469</v>
+      </c>
+      <c r="W59">
+        <v>0.2382902157843758</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.008539099089181934</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2154224912849017</v>
+      </c>
+      <c r="C60">
+        <v>-5.489611201882369</v>
+      </c>
+      <c r="D60">
+        <v>8.395588798117631</v>
+      </c>
+      <c r="E60">
+        <v>12.7822</v>
+      </c>
+      <c r="F60">
+        <v>13.9722</v>
+      </c>
+      <c r="G60">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H60">
+        <v>22.9</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>-0.028</v>
+      </c>
+      <c r="L60">
+        <v>0.028</v>
+      </c>
+      <c r="M60">
+        <v>3.33656136</v>
+      </c>
+      <c r="N60">
+        <v>-3.30856136</v>
+      </c>
+      <c r="O60">
+        <v>-0.82714034</v>
+      </c>
+      <c r="P60">
+        <v>-2.48142102</v>
+      </c>
+      <c r="Q60">
+        <v>-2.50942102</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1838311149709702</v>
+      </c>
+      <c r="T60">
+        <v>1.576332180686446</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.002097968310704168</v>
+      </c>
+      <c r="W60">
+        <v>0.2382990051674038</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.00839187324281665</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2174224912849017</v>
+      </c>
+      <c r="C61">
+        <v>-5.824514915946875</v>
+      </c>
+      <c r="D61">
+        <v>8.301585084053125</v>
+      </c>
+      <c r="E61">
+        <v>13.0231</v>
+      </c>
+      <c r="F61">
+        <v>14.2131</v>
+      </c>
+      <c r="G61">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H61">
+        <v>22.9</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>-0.028</v>
+      </c>
+      <c r="L61">
+        <v>0.028</v>
+      </c>
+      <c r="M61">
+        <v>3.39408828</v>
+      </c>
+      <c r="N61">
+        <v>-3.36608828</v>
+      </c>
+      <c r="O61">
+        <v>-0.84152207</v>
+      </c>
+      <c r="P61">
+        <v>-2.52456621</v>
+      </c>
+      <c r="Q61">
+        <v>-2.55256621</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1873684592385549</v>
+      </c>
+      <c r="T61">
+        <v>1.614779307044652</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.002062409525776978</v>
+      </c>
+      <c r="W61">
+        <v>0.2383074966052445</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.00824963810310797</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2194224912849017</v>
+      </c>
+      <c r="C62">
+        <v>-6.157336857948643</v>
+      </c>
+      <c r="D62">
+        <v>8.209663142051356</v>
+      </c>
+      <c r="E62">
+        <v>13.264</v>
+      </c>
+      <c r="F62">
+        <v>14.454</v>
+      </c>
+      <c r="G62">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H62">
+        <v>22.9</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>-0.028</v>
+      </c>
+      <c r="L62">
+        <v>0.028</v>
+      </c>
+      <c r="M62">
+        <v>3.4516152</v>
+      </c>
+      <c r="N62">
+        <v>-3.4236152</v>
+      </c>
+      <c r="O62">
+        <v>-0.8559038</v>
+      </c>
+      <c r="P62">
+        <v>-2.5677114</v>
+      </c>
+      <c r="Q62">
+        <v>-2.5957114</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1910826707195187</v>
+      </c>
+      <c r="T62">
+        <v>1.655148789720769</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.002028036033680695</v>
+      </c>
+      <c r="W62">
+        <v>0.2383157049951571</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.008112144134722832</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2214224912849017</v>
+      </c>
+      <c r="C63">
+        <v>-6.488145423802607</v>
+      </c>
+      <c r="D63">
+        <v>8.119754576197392</v>
+      </c>
+      <c r="E63">
+        <v>13.5049</v>
+      </c>
+      <c r="F63">
+        <v>14.6949</v>
+      </c>
+      <c r="G63">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H63">
+        <v>22.9</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>-0.028</v>
+      </c>
+      <c r="L63">
+        <v>0.028</v>
+      </c>
+      <c r="M63">
+        <v>3.50914212</v>
+      </c>
+      <c r="N63">
+        <v>-3.48114212</v>
+      </c>
+      <c r="O63">
+        <v>-0.87028553</v>
+      </c>
+      <c r="P63">
+        <v>-2.61085659</v>
+      </c>
+      <c r="Q63">
+        <v>-2.63885659</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1949873545841218</v>
+      </c>
+      <c r="T63">
+        <v>1.697588502277712</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.001994789541325274</v>
+      </c>
+      <c r="W63">
+        <v>0.2383236442575316</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.007979158165301148</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2234224912849018</v>
+      </c>
+      <c r="C64">
+        <v>-6.817006045714781</v>
+      </c>
+      <c r="D64">
+        <v>8.03179395428522</v>
+      </c>
+      <c r="E64">
+        <v>13.7458</v>
+      </c>
+      <c r="F64">
+        <v>14.9358</v>
+      </c>
+      <c r="G64">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H64">
+        <v>22.9</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>-0.028</v>
+      </c>
+      <c r="L64">
+        <v>0.028</v>
+      </c>
+      <c r="M64">
+        <v>3.56666904</v>
+      </c>
+      <c r="N64">
+        <v>-3.53866904</v>
+      </c>
+      <c r="O64">
+        <v>-0.8846672600000001</v>
+      </c>
+      <c r="P64">
+        <v>-2.65400178</v>
+      </c>
+      <c r="Q64">
+        <v>-2.68200178</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1990975481258092</v>
+      </c>
+      <c r="T64">
+        <v>1.742261883916599</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.001962615516465189</v>
+      </c>
+      <c r="W64">
+        <v>0.2383313274146681</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.007850462065860708</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2254224912849017</v>
+      </c>
+      <c r="C65">
+        <v>-7.143981350990002</v>
+      </c>
+      <c r="D65">
+        <v>7.945718649009999</v>
+      </c>
+      <c r="E65">
+        <v>13.9867</v>
+      </c>
+      <c r="F65">
+        <v>15.1767</v>
+      </c>
+      <c r="G65">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H65">
+        <v>22.9</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>-0.028</v>
+      </c>
+      <c r="L65">
+        <v>0.028</v>
+      </c>
+      <c r="M65">
+        <v>3.62419596</v>
+      </c>
+      <c r="N65">
+        <v>-3.59619596</v>
+      </c>
+      <c r="O65">
+        <v>-0.89904899</v>
+      </c>
+      <c r="P65">
+        <v>-2.69714697</v>
+      </c>
+      <c r="Q65">
+        <v>-2.72514697</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2034299142913716</v>
+      </c>
+      <c r="T65">
+        <v>1.789350042941372</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.00193146288921971</v>
+      </c>
+      <c r="W65">
+        <v>0.2383387666620543</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.007725851556878882</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2274224912849017</v>
+      </c>
+      <c r="C66">
+        <v>-7.469131310736409</v>
+      </c>
+      <c r="D66">
+        <v>7.861468689263591</v>
+      </c>
+      <c r="E66">
+        <v>14.2276</v>
+      </c>
+      <c r="F66">
+        <v>15.4176</v>
+      </c>
+      <c r="G66">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H66">
+        <v>22.9</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>-0.028</v>
+      </c>
+      <c r="L66">
+        <v>0.028</v>
+      </c>
+      <c r="M66">
+        <v>3.68172288</v>
+      </c>
+      <c r="N66">
+        <v>-3.65372288</v>
+      </c>
+      <c r="O66">
+        <v>-0.91343072</v>
+      </c>
+      <c r="P66">
+        <v>-2.74029216</v>
+      </c>
+      <c r="Q66">
+        <v>-2.76829216</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2080029674661319</v>
+      </c>
+      <c r="T66">
+        <v>1.839054210800854</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.001901283781575652</v>
+      </c>
+      <c r="W66">
+        <v>0.2383459734329598</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.007605135126302565</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2294224912849017</v>
+      </c>
+      <c r="C67">
+        <v>-7.792513379208737</v>
+      </c>
+      <c r="D67">
+        <v>7.778986620791263</v>
+      </c>
+      <c r="E67">
+        <v>14.4685</v>
+      </c>
+      <c r="F67">
+        <v>15.6585</v>
+      </c>
+      <c r="G67">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H67">
+        <v>22.9</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>-0.028</v>
+      </c>
+      <c r="L67">
+        <v>0.028</v>
+      </c>
+      <c r="M67">
+        <v>3.7392498</v>
+      </c>
+      <c r="N67">
+        <v>-3.7112498</v>
+      </c>
+      <c r="O67">
+        <v>-0.92781245</v>
+      </c>
+      <c r="P67">
+        <v>-2.78343735</v>
+      </c>
+      <c r="Q67">
+        <v>-2.81143735</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2128373379651643</v>
+      </c>
+      <c r="T67">
+        <v>1.891598616823736</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.001872033261859103</v>
+      </c>
+      <c r="W67">
+        <v>0.2383529584570681</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.007488133047436452</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2314224912849018</v>
+      </c>
+      <c r="C68">
+        <v>-8.114182624470818</v>
+      </c>
+      <c r="D68">
+        <v>7.698217375529183</v>
+      </c>
+      <c r="E68">
+        <v>14.7094</v>
+      </c>
+      <c r="F68">
+        <v>15.8994</v>
+      </c>
+      <c r="G68">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H68">
+        <v>22.9</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>-0.028</v>
+      </c>
+      <c r="L68">
+        <v>0.028</v>
+      </c>
+      <c r="M68">
+        <v>3.79677672</v>
+      </c>
+      <c r="N68">
+        <v>-3.76877672</v>
+      </c>
+      <c r="O68">
+        <v>-0.94219418</v>
+      </c>
+      <c r="P68">
+        <v>-2.82658254</v>
+      </c>
+      <c r="Q68">
+        <v>-2.85458254</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2179560831994339</v>
+      </c>
+      <c r="T68">
+        <v>1.947233870259728</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.001843669121527905</v>
+      </c>
+      <c r="W68">
+        <v>0.2383597318137791</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.007374676486111675</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2334224912849018</v>
+      </c>
+      <c r="C69">
+        <v>-8.434191851001678</v>
+      </c>
+      <c r="D69">
+        <v>7.619108148998322</v>
+      </c>
+      <c r="E69">
+        <v>14.9503</v>
+      </c>
+      <c r="F69">
+        <v>16.1403</v>
+      </c>
+      <c r="G69">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H69">
+        <v>22.9</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>-0.028</v>
+      </c>
+      <c r="L69">
+        <v>0.028</v>
+      </c>
+      <c r="M69">
+        <v>3.85430364</v>
+      </c>
+      <c r="N69">
+        <v>-3.82630364</v>
+      </c>
+      <c r="O69">
+        <v>-0.9565759100000001</v>
+      </c>
+      <c r="P69">
+        <v>-2.86972773</v>
+      </c>
+      <c r="Q69">
+        <v>-2.89772773</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2233850554175985</v>
+      </c>
+      <c r="T69">
+        <v>2.006240957237296</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.001816151671952861</v>
+      </c>
+      <c r="W69">
+        <v>0.2383663029807377</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.007264606687811481</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2354224912849018</v>
+      </c>
+      <c r="C70">
+        <v>-8.752591714818973</v>
+      </c>
+      <c r="D70">
+        <v>7.541608285181027</v>
+      </c>
+      <c r="E70">
+        <v>15.1912</v>
+      </c>
+      <c r="F70">
+        <v>16.3812</v>
+      </c>
+      <c r="G70">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H70">
+        <v>22.9</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>-0.028</v>
+      </c>
+      <c r="L70">
+        <v>0.028</v>
+      </c>
+      <c r="M70">
+        <v>3.91183056</v>
+      </c>
+      <c r="N70">
+        <v>-3.88383056</v>
+      </c>
+      <c r="O70">
+        <v>-0.9709576400000001</v>
+      </c>
+      <c r="P70">
+        <v>-2.91287292</v>
+      </c>
+      <c r="Q70">
+        <v>-2.94087292</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2291533383993985</v>
+      </c>
+      <c r="T70">
+        <v>2.068935987150961</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.001789443559130025</v>
+      </c>
+      <c r="W70">
+        <v>0.2383726808780798</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.007157774236520087</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2374224912849018</v>
+      </c>
+      <c r="C71">
+        <v>-9.069430831647018</v>
+      </c>
+      <c r="D71">
+        <v>7.465669168352981</v>
+      </c>
+      <c r="E71">
+        <v>15.4321</v>
+      </c>
+      <c r="F71">
+        <v>16.6221</v>
+      </c>
+      <c r="G71">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H71">
+        <v>22.9</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>-0.028</v>
+      </c>
+      <c r="L71">
+        <v>0.028</v>
+      </c>
+      <c r="M71">
+        <v>3.96935748</v>
+      </c>
+      <c r="N71">
+        <v>-3.94135748</v>
+      </c>
+      <c r="O71">
+        <v>-0.98533937</v>
+      </c>
+      <c r="P71">
+        <v>-2.95601811</v>
+      </c>
+      <c r="Q71">
+        <v>-2.98401811</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2352937686703468</v>
+      </c>
+      <c r="T71">
+        <v>2.135675857704218</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.001763509594504952</v>
+      </c>
+      <c r="W71">
+        <v>0.2383788739088322</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.007054038378019767</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2394224912849017</v>
+      </c>
+      <c r="C72">
+        <v>-9.384755878614971</v>
+      </c>
+      <c r="D72">
+        <v>7.391244121385033</v>
+      </c>
+      <c r="E72">
+        <v>15.673</v>
+      </c>
+      <c r="F72">
+        <v>16.863</v>
+      </c>
+      <c r="G72">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H72">
+        <v>22.9</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>-0.028</v>
+      </c>
+      <c r="L72">
+        <v>0.028</v>
+      </c>
+      <c r="M72">
+        <v>4.026884400000001</v>
+      </c>
+      <c r="N72">
+        <v>-3.998884400000001</v>
+      </c>
+      <c r="O72">
+        <v>-0.9997211000000003</v>
+      </c>
+      <c r="P72">
+        <v>-2.999163300000001</v>
+      </c>
+      <c r="Q72">
+        <v>-3.027163300000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2418435609593583</v>
+      </c>
+      <c r="T72">
+        <v>2.206865052961025</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.001738316600297739</v>
+      </c>
+      <c r="W72">
+        <v>0.2383848899958489</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.006953266401190983</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2414224912849017</v>
+      </c>
+      <c r="C73">
+        <v>-9.698611689932008</v>
+      </c>
+      <c r="D73">
+        <v>7.318288310067992</v>
+      </c>
+      <c r="E73">
+        <v>15.9139</v>
+      </c>
+      <c r="F73">
+        <v>17.1039</v>
+      </c>
+      <c r="G73">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H73">
+        <v>22.9</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>-0.028</v>
+      </c>
+      <c r="L73">
+        <v>0.028</v>
+      </c>
+      <c r="M73">
+        <v>4.08441132</v>
+      </c>
+      <c r="N73">
+        <v>-4.05641132</v>
+      </c>
+      <c r="O73">
+        <v>-1.01410283</v>
+      </c>
+      <c r="P73">
+        <v>-3.04230849</v>
+      </c>
+      <c r="Q73">
+        <v>-3.07030849</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2488450630614051</v>
+      </c>
+      <c r="T73">
+        <v>2.282963847890715</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.001713833267899179</v>
+      </c>
+      <c r="W73">
+        <v>0.2383907366156257</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.006855333071596581</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2434224912849017</v>
+      </c>
+      <c r="C74">
+        <v>-10.01104134695176</v>
+      </c>
+      <c r="D74">
+        <v>7.246758653048239</v>
+      </c>
+      <c r="E74">
+        <v>16.1548</v>
+      </c>
+      <c r="F74">
+        <v>17.3448</v>
+      </c>
+      <c r="G74">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H74">
+        <v>22.9</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>-0.028</v>
+      </c>
+      <c r="L74">
+        <v>0.028</v>
+      </c>
+      <c r="M74">
+        <v>4.14193824</v>
+      </c>
+      <c r="N74">
+        <v>-4.11393824</v>
+      </c>
+      <c r="O74">
+        <v>-1.02848456</v>
+      </c>
+      <c r="P74">
+        <v>-3.085453680000001</v>
+      </c>
+      <c r="Q74">
+        <v>-3.113453680000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2563466724564554</v>
+      </c>
+      <c r="T74">
+        <v>2.36449827102967</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.001690030028067246</v>
+      </c>
+      <c r="W74">
+        <v>0.2383964208292976</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.006760120112268897</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2454224912849017</v>
+      </c>
+      <c r="C75">
+        <v>-10.322086263006</v>
+      </c>
+      <c r="D75">
+        <v>7.176613736994003</v>
+      </c>
+      <c r="E75">
+        <v>16.3957</v>
+      </c>
+      <c r="F75">
+        <v>17.5857</v>
+      </c>
+      <c r="G75">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H75">
+        <v>22.9</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>-0.028</v>
+      </c>
+      <c r="L75">
+        <v>0.028</v>
+      </c>
+      <c r="M75">
+        <v>4.19946516</v>
+      </c>
+      <c r="N75">
+        <v>-4.17146516</v>
+      </c>
+      <c r="O75">
+        <v>-1.04286629</v>
+      </c>
+      <c r="P75">
+        <v>-3.12859887</v>
+      </c>
+      <c r="Q75">
+        <v>-3.15659887</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2644039566215092</v>
+      </c>
+      <c r="T75">
+        <v>2.452072281067805</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.001666878931792352</v>
+      </c>
+      <c r="W75">
+        <v>0.238401949311088</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.006667515727169282</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2474224912849018</v>
+      </c>
+      <c r="C76">
+        <v>-10.63178626335872</v>
+      </c>
+      <c r="D76">
+        <v>7.107813736641276</v>
+      </c>
+      <c r="E76">
+        <v>16.6366</v>
+      </c>
+      <c r="F76">
+        <v>17.8266</v>
+      </c>
+      <c r="G76">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H76">
+        <v>22.9</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>-0.028</v>
+      </c>
+      <c r="L76">
+        <v>0.028</v>
+      </c>
+      <c r="M76">
+        <v>4.25699208</v>
+      </c>
+      <c r="N76">
+        <v>-4.22899208</v>
+      </c>
+      <c r="O76">
+        <v>-1.05724802</v>
+      </c>
+      <c r="P76">
+        <v>-3.17174406</v>
+      </c>
+      <c r="Q76">
+        <v>-3.19974406</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2730810318761827</v>
+      </c>
+      <c r="T76">
+        <v>2.546382753416567</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.001644353540822186</v>
+      </c>
+      <c r="W76">
+        <v>0.2384073283744517</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.006577414163288609</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2494224912849017</v>
+      </c>
+      <c r="C77">
+        <v>-10.94017966060495</v>
+      </c>
+      <c r="D77">
+        <v>7.040320339395046</v>
+      </c>
+      <c r="E77">
+        <v>16.8775</v>
+      </c>
+      <c r="F77">
+        <v>18.0675</v>
+      </c>
+      <c r="G77">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H77">
+        <v>22.9</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>-0.028</v>
+      </c>
+      <c r="L77">
+        <v>0.028</v>
+      </c>
+      <c r="M77">
+        <v>4.314519</v>
+      </c>
+      <c r="N77">
+        <v>-4.286519</v>
+      </c>
+      <c r="O77">
+        <v>-1.07162975</v>
+      </c>
+      <c r="P77">
+        <v>-3.21488925</v>
+      </c>
+      <c r="Q77">
+        <v>-3.24288925</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.28245227315123</v>
+      </c>
+      <c r="T77">
+        <v>2.64823806355323</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.001622428826944556</v>
+      </c>
+      <c r="W77">
+        <v>0.2384125639961256</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.006489715307778088</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2514224912849017</v>
+      </c>
+      <c r="C78">
+        <v>-11.24730332581412</v>
+      </c>
+      <c r="D78">
+        <v>6.974096674185881</v>
+      </c>
+      <c r="E78">
+        <v>17.1184</v>
+      </c>
+      <c r="F78">
+        <v>18.3084</v>
+      </c>
+      <c r="G78">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H78">
+        <v>22.9</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>-0.028</v>
+      </c>
+      <c r="L78">
+        <v>0.028</v>
+      </c>
+      <c r="M78">
+        <v>4.37204592</v>
+      </c>
+      <c r="N78">
+        <v>-4.34404592</v>
+      </c>
+      <c r="O78">
+        <v>-1.08601148</v>
+      </c>
+      <c r="P78">
+        <v>-3.25803444</v>
+      </c>
+      <c r="Q78">
+        <v>-3.28603444</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2926044511991979</v>
+      </c>
+      <c r="T78">
+        <v>2.758581316201281</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.001601081079221602</v>
+      </c>
+      <c r="W78">
+        <v>0.2384176618382819</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.006404324316886312</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2534224912849017</v>
+      </c>
+      <c r="C79">
+        <v>-11.5531927556957</v>
+      </c>
+      <c r="D79">
+        <v>6.909107244304295</v>
+      </c>
+      <c r="E79">
+        <v>17.3593</v>
+      </c>
+      <c r="F79">
+        <v>18.5493</v>
+      </c>
+      <c r="G79">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H79">
+        <v>22.9</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>-0.028</v>
+      </c>
+      <c r="L79">
+        <v>0.028</v>
+      </c>
+      <c r="M79">
+        <v>4.42957284</v>
+      </c>
+      <c r="N79">
+        <v>-4.40157284</v>
+      </c>
+      <c r="O79">
+        <v>-1.10039321</v>
+      </c>
+      <c r="P79">
+        <v>-3.30117963</v>
+      </c>
+      <c r="Q79">
+        <v>-3.32917963</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3036394273382934</v>
+      </c>
+      <c r="T79">
+        <v>2.878519634296989</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.00158028781845249</v>
+      </c>
+      <c r="W79">
+        <v>0.2384226272689536</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.006321151273809833</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2554224912849017</v>
+      </c>
+      <c r="C80">
+        <v>-11.85788213604419</v>
+      </c>
+      <c r="D80">
+        <v>6.845317863955811</v>
+      </c>
+      <c r="E80">
+        <v>17.6002</v>
+      </c>
+      <c r="F80">
+        <v>18.7902</v>
+      </c>
+      <c r="G80">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H80">
+        <v>22.9</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>-0.028</v>
+      </c>
+      <c r="L80">
+        <v>0.028</v>
+      </c>
+      <c r="M80">
+        <v>4.48709976</v>
+      </c>
+      <c r="N80">
+        <v>-4.459099760000001</v>
+      </c>
+      <c r="O80">
+        <v>-1.11477494</v>
+      </c>
+      <c r="P80">
+        <v>-3.344324820000001</v>
+      </c>
+      <c r="Q80">
+        <v>-3.372324820000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3156775831263977</v>
+      </c>
+      <c r="T80">
+        <v>3.009361435855943</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.001560027718215919</v>
+      </c>
+      <c r="W80">
+        <v>0.23842746538089</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.00624011087286358</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2574224912849018</v>
+      </c>
+      <c r="C81">
+        <v>-12.16140440170153</v>
+      </c>
+      <c r="D81">
+        <v>6.782695598298473</v>
+      </c>
+      <c r="E81">
+        <v>17.8411</v>
+      </c>
+      <c r="F81">
+        <v>19.0311</v>
+      </c>
+      <c r="G81">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H81">
+        <v>22.9</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>-0.028</v>
+      </c>
+      <c r="L81">
+        <v>0.028</v>
+      </c>
+      <c r="M81">
+        <v>4.54462668</v>
+      </c>
+      <c r="N81">
+        <v>-4.516626680000001</v>
+      </c>
+      <c r="O81">
+        <v>-1.12915667</v>
+      </c>
+      <c r="P81">
+        <v>-3.38747001</v>
+      </c>
+      <c r="Q81">
+        <v>-3.41547001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3288622299419405</v>
+      </c>
+      <c r="T81">
+        <v>3.152664361372894</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.001540280531909389</v>
+      </c>
+      <c r="W81">
+        <v>0.2384321810089801</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.00616112212763742</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2594224912849018</v>
+      </c>
+      <c r="C82">
+        <v>-12.4637912932582</v>
+      </c>
+      <c r="D82">
+        <v>6.721208706741804</v>
+      </c>
+      <c r="E82">
+        <v>18.082</v>
+      </c>
+      <c r="F82">
+        <v>19.272</v>
+      </c>
+      <c r="G82">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H82">
+        <v>22.9</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>-0.028</v>
+      </c>
+      <c r="L82">
+        <v>0.028</v>
+      </c>
+      <c r="M82">
+        <v>4.6021536</v>
+      </c>
+      <c r="N82">
+        <v>-4.574153600000001</v>
+      </c>
+      <c r="O82">
+        <v>-1.1435384</v>
+      </c>
+      <c r="P82">
+        <v>-3.430615200000001</v>
+      </c>
+      <c r="Q82">
+        <v>-3.458615200000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3433653414390376</v>
+      </c>
+      <c r="T82">
+        <v>3.310297579441539</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.001521027025260521</v>
+      </c>
+      <c r="W82">
+        <v>0.2384367787463678</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.006084108101041985</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2614224912849017</v>
+      </c>
+      <c r="C83">
+        <v>-12.7650734106979</v>
+      </c>
+      <c r="D83">
+        <v>6.660826589302106</v>
+      </c>
+      <c r="E83">
+        <v>18.3229</v>
+      </c>
+      <c r="F83">
+        <v>19.5129</v>
+      </c>
+      <c r="G83">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H83">
+        <v>22.9</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>-0.028</v>
+      </c>
+      <c r="L83">
+        <v>0.028</v>
+      </c>
+      <c r="M83">
+        <v>4.659680520000001</v>
+      </c>
+      <c r="N83">
+        <v>-4.631680520000002</v>
+      </c>
+      <c r="O83">
+        <v>-1.15792013</v>
+      </c>
+      <c r="P83">
+        <v>-3.473760390000001</v>
+      </c>
+      <c r="Q83">
+        <v>-3.501760390000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3593950962516185</v>
+      </c>
+      <c r="T83">
+        <v>3.484523767833198</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.001502248913837552</v>
+      </c>
+      <c r="W83">
+        <v>0.2384412629593756</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.006008995655350069</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2634224912849017</v>
+      </c>
+      <c r="C84">
+        <v>-13.06528026417637</v>
+      </c>
+      <c r="D84">
+        <v>6.601519735823628</v>
+      </c>
+      <c r="E84">
+        <v>18.5638</v>
+      </c>
+      <c r="F84">
+        <v>19.7538</v>
+      </c>
+      <c r="G84">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H84">
+        <v>22.9</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>-0.028</v>
+      </c>
+      <c r="L84">
+        <v>0.028</v>
+      </c>
+      <c r="M84">
+        <v>4.717207440000001</v>
+      </c>
+      <c r="N84">
+        <v>-4.689207440000001</v>
+      </c>
+      <c r="O84">
+        <v>-1.17230186</v>
+      </c>
+      <c r="P84">
+        <v>-3.516905580000001</v>
+      </c>
+      <c r="Q84">
+        <v>-3.544905580000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.377205934932264</v>
+      </c>
+      <c r="T84">
+        <v>3.678108421601709</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.001483928805132216</v>
+      </c>
+      <c r="W84">
+        <v>0.2384456378013344</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.005935715220528825</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2654224912849018</v>
+      </c>
+      <c r="C85">
+        <v>-13.36444032211144</v>
+      </c>
+      <c r="D85">
+        <v>6.54325967788856</v>
+      </c>
+      <c r="E85">
+        <v>18.8047</v>
+      </c>
+      <c r="F85">
+        <v>19.9947</v>
+      </c>
+      <c r="G85">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H85">
+        <v>22.9</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>-0.028</v>
+      </c>
+      <c r="L85">
+        <v>0.028</v>
+      </c>
+      <c r="M85">
+        <v>4.774734360000001</v>
+      </c>
+      <c r="N85">
+        <v>-4.746734360000001</v>
+      </c>
+      <c r="O85">
+        <v>-1.18668359</v>
+      </c>
+      <c r="P85">
+        <v>-3.560050770000001</v>
+      </c>
+      <c r="Q85">
+        <v>-3.588050770000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3971121663988678</v>
+      </c>
+      <c r="T85">
+        <v>3.894467740519457</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.001466050144829418</v>
+      </c>
+      <c r="W85">
+        <v>0.2384499072254148</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.00586420057931758</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2674224912849017</v>
+      </c>
+      <c r="C86">
+        <v>-13.66258105674882</v>
+      </c>
+      <c r="D86">
+        <v>6.486018943251177</v>
+      </c>
+      <c r="E86">
+        <v>19.0456</v>
+      </c>
+      <c r="F86">
+        <v>20.2356</v>
+      </c>
+      <c r="G86">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H86">
+        <v>22.9</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>-0.028</v>
+      </c>
+      <c r="L86">
+        <v>0.028</v>
+      </c>
+      <c r="M86">
+        <v>4.83226128</v>
+      </c>
+      <c r="N86">
+        <v>-4.80426128</v>
+      </c>
+      <c r="O86">
+        <v>-1.20106532</v>
+      </c>
+      <c r="P86">
+        <v>-3.60319596</v>
+      </c>
+      <c r="Q86">
+        <v>-3.63119596</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4195066767987968</v>
+      </c>
+      <c r="T86">
+        <v>4.137871974301921</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.001448597166914782</v>
+      </c>
+      <c r="W86">
+        <v>0.2384540749965408</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.005794388667659023</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2694224912849017</v>
+      </c>
+      <c r="C87">
+        <v>-13.9597289873571</v>
+      </c>
+      <c r="D87">
+        <v>6.429771012642894</v>
+      </c>
+      <c r="E87">
+        <v>19.2865</v>
+      </c>
+      <c r="F87">
+        <v>20.4765</v>
+      </c>
+      <c r="G87">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H87">
+        <v>22.9</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>-0.028</v>
+      </c>
+      <c r="L87">
+        <v>0.028</v>
+      </c>
+      <c r="M87">
+        <v>4.8897882</v>
+      </c>
+      <c r="N87">
+        <v>-4.8617882</v>
+      </c>
+      <c r="O87">
+        <v>-1.21544705</v>
+      </c>
+      <c r="P87">
+        <v>-3.64634115</v>
+      </c>
+      <c r="Q87">
+        <v>-3.67434115</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4448871219187166</v>
+      </c>
+      <c r="T87">
+        <v>4.413730105922049</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.00143155484730402</v>
+      </c>
+      <c r="W87">
+        <v>0.2384581447024638</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.005726219389216025</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2714224912849017</v>
+      </c>
+      <c r="C88">
+        <v>-14.25590972119438</v>
+      </c>
+      <c r="D88">
+        <v>6.374490278805615</v>
+      </c>
+      <c r="E88">
+        <v>19.5274</v>
+      </c>
+      <c r="F88">
+        <v>20.7174</v>
+      </c>
+      <c r="G88">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H88">
+        <v>22.9</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>-0.028</v>
+      </c>
+      <c r="L88">
+        <v>0.028</v>
+      </c>
+      <c r="M88">
+        <v>4.94731512</v>
+      </c>
+      <c r="N88">
+        <v>-4.91931512</v>
+      </c>
+      <c r="O88">
+        <v>-1.22982878</v>
+      </c>
+      <c r="P88">
+        <v>-3.68948634</v>
+      </c>
+      <c r="Q88">
+        <v>-3.71748634</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4738933449129107</v>
+      </c>
+      <c r="T88">
+        <v>4.728996542059339</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.001414908860707462</v>
+      </c>
+      <c r="W88">
+        <v>0.2384621197640631</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.005659635442829769</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2734224912849017</v>
+      </c>
+      <c r="C89">
+        <v>-14.55114799237969</v>
+      </c>
+      <c r="D89">
+        <v>6.320152007620307</v>
+      </c>
+      <c r="E89">
+        <v>19.7683</v>
+      </c>
+      <c r="F89">
+        <v>20.9583</v>
+      </c>
+      <c r="G89">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H89">
+        <v>22.9</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>-0.028</v>
+      </c>
+      <c r="L89">
+        <v>0.028</v>
+      </c>
+      <c r="M89">
+        <v>5.004842040000001</v>
+      </c>
+      <c r="N89">
+        <v>-4.976842040000001</v>
+      </c>
+      <c r="O89">
+        <v>-1.24421051</v>
+      </c>
+      <c r="P89">
+        <v>-3.732631530000001</v>
+      </c>
+      <c r="Q89">
+        <v>-3.760631530000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5073620637523654</v>
+      </c>
+      <c r="T89">
+        <v>5.092765506833135</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.001398645540469445</v>
+      </c>
+      <c r="W89">
+        <v>0.2384660034449359</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.005594582161877693</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2754224912849018</v>
+      </c>
+      <c r="C90">
+        <v>-14.84546769879307</v>
+      </c>
+      <c r="D90">
+        <v>6.266732301206932</v>
+      </c>
+      <c r="E90">
+        <v>20.0092</v>
+      </c>
+      <c r="F90">
+        <v>21.1992</v>
+      </c>
+      <c r="G90">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H90">
+        <v>22.9</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>-0.028</v>
+      </c>
+      <c r="L90">
+        <v>0.028</v>
+      </c>
+      <c r="M90">
+        <v>5.062368960000001</v>
+      </c>
+      <c r="N90">
+        <v>-5.034368960000001</v>
+      </c>
+      <c r="O90">
+        <v>-1.25859224</v>
+      </c>
+      <c r="P90">
+        <v>-3.775776720000001</v>
+      </c>
+      <c r="Q90">
+        <v>-3.803776720000001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5464089023983958</v>
+      </c>
+      <c r="T90">
+        <v>5.517162632402562</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.001382751841145929</v>
+      </c>
+      <c r="W90">
+        <v>0.2384697988603344</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.005531007364583673</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2774224912849018</v>
+      </c>
+      <c r="C91">
+        <v>-15.13889193712</v>
+      </c>
+      <c r="D91">
+        <v>6.214208062880003</v>
+      </c>
+      <c r="E91">
+        <v>20.2501</v>
+      </c>
+      <c r="F91">
+        <v>21.4401</v>
+      </c>
+      <c r="G91">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H91">
+        <v>22.9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>-0.028</v>
+      </c>
+      <c r="L91">
+        <v>0.028</v>
+      </c>
+      <c r="M91">
+        <v>5.119895880000001</v>
+      </c>
+      <c r="N91">
+        <v>-5.091895880000001</v>
+      </c>
+      <c r="O91">
+        <v>-1.27297397</v>
+      </c>
+      <c r="P91">
+        <v>-3.818921910000001</v>
+      </c>
+      <c r="Q91">
+        <v>-3.846921910000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5925551662527955</v>
+      </c>
+      <c r="T91">
+        <v>6.018722871711886</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.001367215303604963</v>
+      </c>
+      <c r="W91">
+        <v>0.2384735089854992</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.005468861214419807</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2794224912849017</v>
+      </c>
+      <c r="C92">
+        <v>-15.43144303614816</v>
+      </c>
+      <c r="D92">
+        <v>6.162556963851839</v>
+      </c>
+      <c r="E92">
+        <v>20.491</v>
+      </c>
+      <c r="F92">
+        <v>21.681</v>
+      </c>
+      <c r="G92">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H92">
+        <v>22.9</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>-0.028</v>
+      </c>
+      <c r="L92">
+        <v>0.028</v>
+      </c>
+      <c r="M92">
+        <v>5.1774228</v>
+      </c>
+      <c r="N92">
+        <v>-5.149422800000001</v>
+      </c>
+      <c r="O92">
+        <v>-1.2873557</v>
+      </c>
+      <c r="P92">
+        <v>-3.862067100000001</v>
+      </c>
+      <c r="Q92">
+        <v>-3.890067100000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6479306828780751</v>
+      </c>
+      <c r="T92">
+        <v>6.620595158883075</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.001352024022453797</v>
+      </c>
+      <c r="W92">
+        <v>0.238477136663438</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.005408096089815073</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2814224912849017</v>
+      </c>
+      <c r="C93">
+        <v>-15.72314258841733</v>
+      </c>
+      <c r="D93">
+        <v>6.11175741158267</v>
+      </c>
+      <c r="E93">
+        <v>20.7319</v>
+      </c>
+      <c r="F93">
+        <v>21.9219</v>
+      </c>
+      <c r="G93">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H93">
+        <v>22.9</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>-0.028</v>
+      </c>
+      <c r="L93">
+        <v>0.028</v>
+      </c>
+      <c r="M93">
+        <v>5.23494972</v>
+      </c>
+      <c r="N93">
+        <v>-5.206949720000001</v>
+      </c>
+      <c r="O93">
+        <v>-1.30173743</v>
+      </c>
+      <c r="P93">
+        <v>-3.905212290000001</v>
+      </c>
+      <c r="Q93">
+        <v>-3.933212290000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.715611869864528</v>
+      </c>
+      <c r="T93">
+        <v>7.356216843203418</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.001337166615613645</v>
+      </c>
+      <c r="W93">
+        <v>0.2384806846121915</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.005348666462454466</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2834224912849018</v>
+      </c>
+      <c r="C94">
+        <v>-16.01401148031668</v>
+      </c>
+      <c r="D94">
+        <v>6.061788519683317</v>
+      </c>
+      <c r="E94">
+        <v>20.9728</v>
+      </c>
+      <c r="F94">
+        <v>22.1628</v>
+      </c>
+      <c r="G94">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H94">
+        <v>22.9</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>-0.028</v>
+      </c>
+      <c r="L94">
+        <v>0.028</v>
+      </c>
+      <c r="M94">
+        <v>5.29247664</v>
+      </c>
+      <c r="N94">
+        <v>-5.264476640000001</v>
+      </c>
+      <c r="O94">
+        <v>-1.31611916</v>
+      </c>
+      <c r="P94">
+        <v>-3.94835748</v>
+      </c>
+      <c r="Q94">
+        <v>-3.97635748</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8002133535975942</v>
+      </c>
+      <c r="T94">
+        <v>8.275743948603848</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.001322632195878714</v>
+      </c>
+      <c r="W94">
+        <v>0.2384841554316242</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.00529052878351477</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2854224912849018</v>
+      </c>
+      <c r="C95">
+        <v>-16.30406992071765</v>
+      </c>
+      <c r="D95">
+        <v>6.01263007928235</v>
+      </c>
+      <c r="E95">
+        <v>21.2137</v>
+      </c>
+      <c r="F95">
+        <v>22.4037</v>
+      </c>
+      <c r="G95">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H95">
+        <v>22.9</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>-0.028</v>
+      </c>
+      <c r="L95">
+        <v>0.028</v>
+      </c>
+      <c r="M95">
+        <v>5.35000356</v>
+      </c>
+      <c r="N95">
+        <v>-5.322003560000001</v>
+      </c>
+      <c r="O95">
+        <v>-1.33050089</v>
+      </c>
+      <c r="P95">
+        <v>-3.99150267</v>
+      </c>
+      <c r="Q95">
+        <v>-4.01950267</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.9089866898258221</v>
+      </c>
+      <c r="T95">
+        <v>9.457993084118685</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.001308410344310126</v>
+      </c>
+      <c r="W95">
+        <v>0.2384875516097787</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.005233641377240472</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2874224912849017</v>
+      </c>
+      <c r="C96">
+        <v>-16.59333746822478</v>
+      </c>
+      <c r="D96">
+        <v>5.964262531775217</v>
+      </c>
+      <c r="E96">
+        <v>21.4546</v>
+      </c>
+      <c r="F96">
+        <v>22.6446</v>
+      </c>
+      <c r="G96">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H96">
+        <v>22.9</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>-0.028</v>
+      </c>
+      <c r="L96">
+        <v>0.028</v>
+      </c>
+      <c r="M96">
+        <v>5.40753048</v>
+      </c>
+      <c r="N96">
+        <v>-5.379530480000001</v>
+      </c>
+      <c r="O96">
+        <v>-1.34488262</v>
+      </c>
+      <c r="P96">
+        <v>-4.034647860000001</v>
+      </c>
+      <c r="Q96">
+        <v>-4.06264786</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.054017804796792</v>
+      </c>
+      <c r="T96">
+        <v>11.03432526480513</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.001294491085328103</v>
+      </c>
+      <c r="W96">
+        <v>0.2384908755288237</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.005177964341312347</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2894224912849018</v>
+      </c>
+      <c r="C97">
+        <v>-16.88183305712183</v>
+      </c>
+      <c r="D97">
+        <v>5.916666942878167</v>
+      </c>
+      <c r="E97">
+        <v>21.6955</v>
+      </c>
+      <c r="F97">
+        <v>22.8855</v>
+      </c>
+      <c r="G97">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H97">
+        <v>22.9</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>-0.028</v>
+      </c>
+      <c r="L97">
+        <v>0.028</v>
+      </c>
+      <c r="M97">
+        <v>5.4650574</v>
+      </c>
+      <c r="N97">
+        <v>-5.4370574</v>
+      </c>
+      <c r="O97">
+        <v>-1.35926435</v>
+      </c>
+      <c r="P97">
+        <v>-4.07779305</v>
+      </c>
+      <c r="Q97">
+        <v>-4.10579305</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.257061365756152</v>
+      </c>
+      <c r="T97">
+        <v>13.24119031776617</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.001280864863377281</v>
+      </c>
+      <c r="W97">
+        <v>0.2384941294706255</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.005123459453509005</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2914224912849017</v>
+      </c>
+      <c r="C98">
+        <v>-17.16957502208532</v>
+      </c>
+      <c r="D98">
+        <v>5.869824977914679</v>
+      </c>
+      <c r="E98">
+        <v>21.9364</v>
+      </c>
+      <c r="F98">
+        <v>23.1264</v>
+      </c>
+      <c r="G98">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H98">
+        <v>22.9</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>-0.028</v>
+      </c>
+      <c r="L98">
+        <v>0.028</v>
+      </c>
+      <c r="M98">
+        <v>5.52258432</v>
+      </c>
+      <c r="N98">
+        <v>-5.49458432</v>
+      </c>
+      <c r="O98">
+        <v>-1.37364608</v>
+      </c>
+      <c r="P98">
+        <v>-4.12093824</v>
+      </c>
+      <c r="Q98">
+        <v>-4.14893824</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.561626707195186</v>
+      </c>
+      <c r="T98">
+        <v>16.55148789720767</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.001267522521050435</v>
+      </c>
+      <c r="W98">
+        <v>0.2384973156219732</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.005070090084201673</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2934224912849018</v>
+      </c>
+      <c r="C99">
+        <v>-17.45658112173342</v>
+      </c>
+      <c r="D99">
+        <v>5.823718878266579</v>
+      </c>
+      <c r="E99">
+        <v>22.1773</v>
+      </c>
+      <c r="F99">
+        <v>23.3673</v>
+      </c>
+      <c r="G99">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H99">
+        <v>22.9</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>-0.028</v>
+      </c>
+      <c r="L99">
+        <v>0.028</v>
+      </c>
+      <c r="M99">
+        <v>5.58011124</v>
+      </c>
+      <c r="N99">
+        <v>-5.55211124</v>
+      </c>
+      <c r="O99">
+        <v>-1.38802781</v>
+      </c>
+      <c r="P99">
+        <v>-4.16408343</v>
+      </c>
+      <c r="Q99">
+        <v>-4.192083429999999</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.069235609593582</v>
+      </c>
+      <c r="T99">
+        <v>22.06865052961023</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.001254455278565379</v>
+      </c>
+      <c r="W99">
+        <v>0.2385004360794786</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.005017821114261412</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2954224912849018</v>
+      </c>
+      <c r="C100">
+        <v>-17.74286856107366</v>
+      </c>
+      <c r="D100">
+        <v>5.778331438926345</v>
+      </c>
+      <c r="E100">
+        <v>22.4182</v>
+      </c>
+      <c r="F100">
+        <v>23.6082</v>
+      </c>
+      <c r="G100">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H100">
+        <v>22.9</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>-0.028</v>
+      </c>
+      <c r="L100">
+        <v>0.028</v>
+      </c>
+      <c r="M100">
+        <v>5.637638160000001</v>
+      </c>
+      <c r="N100">
+        <v>-5.609638160000001</v>
+      </c>
+      <c r="O100">
+        <v>-1.40240954</v>
+      </c>
+      <c r="P100">
+        <v>-4.20722862</v>
+      </c>
+      <c r="Q100">
+        <v>-4.23522862</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.084453414390373</v>
+      </c>
+      <c r="T100">
+        <v>33.10297579441535</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.001241654714498385</v>
+      </c>
+      <c r="W100">
+        <v>0.2385034928541778</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.004966618857993432</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2974224912849017</v>
+      </c>
+      <c r="C101">
+        <v>-18.02845401290902</v>
+      </c>
+      <c r="D101">
+        <v>5.733645987090985</v>
+      </c>
+      <c r="E101">
+        <v>22.6591</v>
+      </c>
+      <c r="F101">
+        <v>23.8491</v>
+      </c>
+      <c r="G101">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H101">
+        <v>22.9</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>-0.028</v>
+      </c>
+      <c r="L101">
+        <v>0.028</v>
+      </c>
+      <c r="M101">
+        <v>5.695165080000001</v>
+      </c>
+      <c r="N101">
+        <v>-5.667165080000001</v>
+      </c>
+      <c r="O101">
+        <v>-1.41679127</v>
+      </c>
+      <c r="P101">
+        <v>-4.250373810000001</v>
+      </c>
+      <c r="Q101">
+        <v>-4.278373810000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.130106828780746</v>
+      </c>
+      <c r="T101">
+        <v>66.2059515888307</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.00122911274768527</v>
+      </c>
+      <c r="W101">
+        <v>0.2385064878758528</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.004916450990741006</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/philippines/philippines_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_farming_agriculture.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08625793460826361</v>
+        <v>0.08607603977174295</v>
       </c>
       <c r="C2">
-        <v>22.80301220140012</v>
+        <v>22.62872531337002</v>
       </c>
       <c r="D2">
-        <v>22.79001220140012</v>
+        <v>22.84359531337001</v>
       </c>
       <c r="E2">
-        <v>-0.7869999999999999</v>
+        <v>-0.5591299999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.22787</v>
       </c>
       <c r="G2">
         <v>0.013</v>
@@ -1433,28 +1433,28 @@
         <v>2.34</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.011461861</v>
       </c>
       <c r="N2">
-        <v>2.34</v>
+        <v>2.328538139</v>
       </c>
       <c r="O2">
-        <v>0.585</v>
+        <v>0.58213453475</v>
       </c>
       <c r="P2">
-        <v>1.755</v>
+        <v>1.74640360425</v>
       </c>
       <c r="Q2">
-        <v>1.755</v>
+        <v>1.74640360425</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08625793460826361</v>
+        <v>0.08656443411287168</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442503</v>
+        <v>0.5931721862945856</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>204.1553287027299</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08607603977174295</v>
+        <v>0.08589414493522231</v>
       </c>
       <c r="C3">
-        <v>22.62872531337002</v>
+        <v>22.45469098477896</v>
       </c>
       <c r="D3">
-        <v>22.84359531337001</v>
+        <v>22.89743098477895</v>
       </c>
       <c r="E3">
-        <v>-0.5591299999999999</v>
+        <v>-0.3312599999999999</v>
       </c>
       <c r="F3">
-        <v>0.22787</v>
+        <v>0.45574</v>
       </c>
       <c r="G3">
         <v>0.013</v>
@@ -1515,28 +1515,28 @@
         <v>2.34</v>
       </c>
       <c r="M3">
-        <v>0.011461861</v>
+        <v>0.022923722</v>
       </c>
       <c r="N3">
-        <v>2.328538139</v>
+        <v>2.317076278</v>
       </c>
       <c r="O3">
-        <v>0.58213453475</v>
+        <v>0.5792690695</v>
       </c>
       <c r="P3">
-        <v>1.74640360425</v>
+        <v>1.7378072085</v>
       </c>
       <c r="Q3">
-        <v>1.74640360425</v>
+        <v>1.7378072085</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08656443411287168</v>
+        <v>0.08687718870941051</v>
       </c>
       <c r="T3">
-        <v>0.5931721862945856</v>
+        <v>0.5977231467541113</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>204.1553287027299</v>
+        <v>102.0776643513649</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08589414493522231</v>
+        <v>0.08571225009870163</v>
       </c>
       <c r="C4">
-        <v>22.45469098477896</v>
+        <v>22.28091100547122</v>
       </c>
       <c r="D4">
-        <v>22.89743098477895</v>
+        <v>22.95152100547122</v>
       </c>
       <c r="E4">
-        <v>-0.3312599999999999</v>
+        <v>-0.10339</v>
       </c>
       <c r="F4">
-        <v>0.45574</v>
+        <v>0.6836099999999999</v>
       </c>
       <c r="G4">
         <v>0.013</v>
@@ -1597,28 +1597,28 @@
         <v>2.34</v>
       </c>
       <c r="M4">
-        <v>0.022923722</v>
+        <v>0.034385583</v>
       </c>
       <c r="N4">
-        <v>2.317076278</v>
+        <v>2.305614417</v>
       </c>
       <c r="O4">
-        <v>0.5792690695</v>
+        <v>0.5764036042499999</v>
       </c>
       <c r="P4">
-        <v>1.7378072085</v>
+        <v>1.72921081275</v>
       </c>
       <c r="Q4">
-        <v>1.7378072085</v>
+        <v>1.72921081275</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08687718870941051</v>
+        <v>0.08719639185433159</v>
       </c>
       <c r="T4">
-        <v>0.5977231467541113</v>
+        <v>0.6023679414499159</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>102.0776643513649</v>
+        <v>68.05177623424328</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08571225009870163</v>
+        <v>0.08553035526218097</v>
       </c>
       <c r="C5">
-        <v>22.28091100547122</v>
+        <v>22.10738718224356</v>
       </c>
       <c r="D5">
-        <v>22.95152100547122</v>
+        <v>23.00586718224356</v>
       </c>
       <c r="E5">
-        <v>-0.10339</v>
+        <v>0.12448</v>
       </c>
       <c r="F5">
-        <v>0.6836099999999999</v>
+        <v>0.91148</v>
       </c>
       <c r="G5">
         <v>0.013</v>
@@ -1679,28 +1679,28 @@
         <v>2.34</v>
       </c>
       <c r="M5">
-        <v>0.034385583</v>
+        <v>0.04584744399999999</v>
       </c>
       <c r="N5">
-        <v>2.305614417</v>
+        <v>2.294152556</v>
       </c>
       <c r="O5">
-        <v>0.5764036042499999</v>
+        <v>0.5735381389999999</v>
       </c>
       <c r="P5">
-        <v>1.72921081275</v>
+        <v>1.720614417</v>
       </c>
       <c r="Q5">
-        <v>1.72921081275</v>
+        <v>1.720614417</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08719639185433159</v>
+        <v>0.08752224506477185</v>
       </c>
       <c r="T5">
-        <v>0.6023679414499159</v>
+        <v>0.6071095027018831</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>68.05177623424328</v>
+        <v>51.03883217568247</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08553035526218097</v>
+        <v>0.08534846042566033</v>
       </c>
       <c r="C6">
-        <v>22.10738718224356</v>
+        <v>21.93412133904634</v>
       </c>
       <c r="D6">
-        <v>23.00586718224356</v>
+        <v>23.06047133904634</v>
       </c>
       <c r="E6">
-        <v>0.12448</v>
+        <v>0.3523500000000002</v>
       </c>
       <c r="F6">
-        <v>0.91148</v>
+        <v>1.13935</v>
       </c>
       <c r="G6">
         <v>0.013</v>
@@ -1761,28 +1761,28 @@
         <v>2.34</v>
       </c>
       <c r="M6">
-        <v>0.04584744399999999</v>
+        <v>0.057309305</v>
       </c>
       <c r="N6">
-        <v>2.294152556</v>
+        <v>2.282690695</v>
       </c>
       <c r="O6">
-        <v>0.5735381389999999</v>
+        <v>0.57067267375</v>
       </c>
       <c r="P6">
-        <v>1.720614417</v>
+        <v>1.71201802125</v>
       </c>
       <c r="Q6">
-        <v>1.720614417</v>
+        <v>1.71201802125</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08752224506477185</v>
+        <v>0.08785495834280034</v>
       </c>
       <c r="T6">
-        <v>0.6071095027018831</v>
+        <v>0.611950886295997</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>51.03883217568247</v>
+        <v>40.83106574054597</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08534846042566033</v>
+        <v>0.08516656558913967</v>
       </c>
       <c r="C7">
-        <v>21.93412133904634</v>
+        <v>21.76111531718766</v>
       </c>
       <c r="D7">
-        <v>23.06047133904634</v>
+        <v>23.11533531718766</v>
       </c>
       <c r="E7">
-        <v>0.3523500000000002</v>
+        <v>0.5802200000000002</v>
       </c>
       <c r="F7">
-        <v>1.13935</v>
+        <v>1.36722</v>
       </c>
       <c r="G7">
         <v>0.013</v>
@@ -1843,28 +1843,28 @@
         <v>2.34</v>
       </c>
       <c r="M7">
-        <v>0.057309305</v>
+        <v>0.06877116600000001</v>
       </c>
       <c r="N7">
-        <v>2.282690695</v>
+        <v>2.271228834</v>
       </c>
       <c r="O7">
-        <v>0.57067267375</v>
+        <v>0.5678072085</v>
       </c>
       <c r="P7">
-        <v>1.71201802125</v>
+        <v>1.7034216255</v>
       </c>
       <c r="Q7">
-        <v>1.71201802125</v>
+        <v>1.7034216255</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08785495834280034</v>
+        <v>0.08819475062674433</v>
       </c>
       <c r="T7">
-        <v>0.611950886295997</v>
+        <v>0.6168952780516879</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.83106574054597</v>
+        <v>34.02588811712164</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08516656558913967</v>
+        <v>0.08498467075261901</v>
       </c>
       <c r="C8">
-        <v>21.76111531718766</v>
+        <v>21.58837097554026</v>
       </c>
       <c r="D8">
-        <v>23.11533531718766</v>
+        <v>23.17046097554026</v>
       </c>
       <c r="E8">
-        <v>0.58022</v>
+        <v>0.8080899999999998</v>
       </c>
       <c r="F8">
-        <v>1.36722</v>
+        <v>1.59509</v>
       </c>
       <c r="G8">
         <v>0.013</v>
@@ -1925,28 +1925,28 @@
         <v>2.34</v>
       </c>
       <c r="M8">
-        <v>0.06877116599999999</v>
+        <v>0.08023302699999998</v>
       </c>
       <c r="N8">
-        <v>2.271228834</v>
+        <v>2.259766973</v>
       </c>
       <c r="O8">
-        <v>0.5678072085</v>
+        <v>0.56494174325</v>
       </c>
       <c r="P8">
-        <v>1.7034216255</v>
+        <v>1.69482522975</v>
       </c>
       <c r="Q8">
-        <v>1.7034216255</v>
+        <v>1.69482522975</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08819475062674433</v>
+        <v>0.08854185027163333</v>
       </c>
       <c r="T8">
-        <v>0.6168952780516879</v>
+        <v>0.6219460008128773</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.02588811712165</v>
+        <v>29.16504695753284</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08498467075261899</v>
+        <v>0.08480277591609836</v>
       </c>
       <c r="C9">
-        <v>21.58837097554027</v>
+        <v>21.41589019075152</v>
       </c>
       <c r="D9">
-        <v>23.17046097554027</v>
+        <v>23.22585019075152</v>
       </c>
       <c r="E9">
-        <v>0.8080900000000002</v>
+        <v>1.03596</v>
       </c>
       <c r="F9">
-        <v>1.59509</v>
+        <v>1.82296</v>
       </c>
       <c r="G9">
         <v>0.013</v>
@@ -2007,28 +2007,28 @@
         <v>2.34</v>
       </c>
       <c r="M9">
-        <v>0.080233027</v>
+        <v>0.09169488799999999</v>
       </c>
       <c r="N9">
-        <v>2.259766973</v>
+        <v>2.248305112</v>
       </c>
       <c r="O9">
-        <v>0.56494174325</v>
+        <v>0.5620762779999999</v>
       </c>
       <c r="P9">
-        <v>1.69482522975</v>
+        <v>1.686228834</v>
       </c>
       <c r="Q9">
-        <v>1.69482522975</v>
+        <v>1.686228834</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08854185027163333</v>
+        <v>0.08889649556097647</v>
       </c>
       <c r="T9">
-        <v>0.6219460008128773</v>
+        <v>0.6271065218949624</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.16504695753284</v>
+        <v>25.51941608784123</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08480277591609836</v>
+        <v>0.0846208810795777</v>
       </c>
       <c r="C10">
-        <v>21.41589019075152</v>
+        <v>21.24367485745638</v>
       </c>
       <c r="D10">
-        <v>23.22585019075152</v>
+        <v>23.28150485745638</v>
       </c>
       <c r="E10">
-        <v>1.03596</v>
+        <v>1.26383</v>
       </c>
       <c r="F10">
-        <v>1.82296</v>
+        <v>2.05083</v>
       </c>
       <c r="G10">
         <v>0.013</v>
@@ -2089,28 +2089,28 @@
         <v>2.34</v>
       </c>
       <c r="M10">
-        <v>0.09169488799999999</v>
+        <v>0.103156749</v>
       </c>
       <c r="N10">
-        <v>2.248305112</v>
+        <v>2.236843251</v>
       </c>
       <c r="O10">
-        <v>0.5620762779999999</v>
+        <v>0.55921081275</v>
       </c>
       <c r="P10">
-        <v>1.686228834</v>
+        <v>1.67763243825</v>
       </c>
       <c r="Q10">
-        <v>1.686228834</v>
+        <v>1.67763243825</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08889649556097647</v>
+        <v>0.08925893525228318</v>
       </c>
       <c r="T10">
-        <v>0.6271065218949624</v>
+        <v>0.6323804610228073</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.51941608784123</v>
+        <v>22.68392541141443</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0846208810795777</v>
+        <v>0.08443898624305703</v>
       </c>
       <c r="C11">
-        <v>21.24367485745638</v>
+        <v>21.07172688849339</v>
       </c>
       <c r="D11">
-        <v>23.28150485745638</v>
+        <v>23.33742688849339</v>
       </c>
       <c r="E11">
-        <v>1.26383</v>
+        <v>1.4917</v>
       </c>
       <c r="F11">
-        <v>2.05083</v>
+        <v>2.2787</v>
       </c>
       <c r="G11">
         <v>0.013</v>
@@ -2171,28 +2171,28 @@
         <v>2.34</v>
       </c>
       <c r="M11">
-        <v>0.103156749</v>
+        <v>0.11461861</v>
       </c>
       <c r="N11">
-        <v>2.236843251</v>
+        <v>2.22538139</v>
       </c>
       <c r="O11">
-        <v>0.55921081275</v>
+        <v>0.5563453475</v>
       </c>
       <c r="P11">
-        <v>1.67763243825</v>
+        <v>1.6690360425</v>
       </c>
       <c r="Q11">
-        <v>1.67763243825</v>
+        <v>1.6690360425</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08925893525228318</v>
+        <v>0.08962942915895225</v>
       </c>
       <c r="T11">
-        <v>0.6323804610228073</v>
+        <v>0.6377715987979379</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.68392541141443</v>
+        <v>20.41553287027299</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08443898624305703</v>
+        <v>0.08425709140653637</v>
       </c>
       <c r="C12">
-        <v>21.07172688849339</v>
+        <v>20.90004821512386</v>
       </c>
       <c r="D12">
-        <v>23.33742688849339</v>
+        <v>23.39361821512386</v>
       </c>
       <c r="E12">
-        <v>1.4917</v>
+        <v>1.71957</v>
       </c>
       <c r="F12">
-        <v>2.2787</v>
+        <v>2.50657</v>
       </c>
       <c r="G12">
         <v>0.013</v>
@@ -2253,28 +2253,28 @@
         <v>2.34</v>
       </c>
       <c r="M12">
-        <v>0.11461861</v>
+        <v>0.126080471</v>
       </c>
       <c r="N12">
-        <v>2.22538139</v>
+        <v>2.213919529</v>
       </c>
       <c r="O12">
-        <v>0.5563453475</v>
+        <v>0.55347988225</v>
       </c>
       <c r="P12">
-        <v>1.6690360425</v>
+        <v>1.66043964675</v>
       </c>
       <c r="Q12">
-        <v>1.6690360425</v>
+        <v>1.66043964675</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08962942915895225</v>
+        <v>0.09000824877138919</v>
       </c>
       <c r="T12">
-        <v>0.6377715987979379</v>
+        <v>0.6432838857365545</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.41553287027298</v>
+        <v>18.5595753366118</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08425709140653637</v>
+        <v>0.08407519657001572</v>
       </c>
       <c r="C13">
-        <v>20.90004821512386</v>
+        <v>20.72864078725417</v>
       </c>
       <c r="D13">
-        <v>23.39361821512386</v>
+        <v>23.45008078725417</v>
       </c>
       <c r="E13">
-        <v>1.71957</v>
+        <v>1.94744</v>
       </c>
       <c r="F13">
-        <v>2.50657</v>
+        <v>2.73444</v>
       </c>
       <c r="G13">
         <v>0.013</v>
@@ -2335,28 +2335,28 @@
         <v>2.34</v>
       </c>
       <c r="M13">
-        <v>0.126080471</v>
+        <v>0.137542332</v>
       </c>
       <c r="N13">
-        <v>2.213919529</v>
+        <v>2.202457668</v>
       </c>
       <c r="O13">
-        <v>0.55347988225</v>
+        <v>0.550614417</v>
       </c>
       <c r="P13">
-        <v>1.66043964675</v>
+        <v>1.651843251</v>
       </c>
       <c r="Q13">
-        <v>1.66043964675</v>
+        <v>1.651843251</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09000824877138919</v>
+        <v>0.0903956779204724</v>
       </c>
       <c r="T13">
-        <v>0.6432838857365545</v>
+        <v>0.6489214519237759</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.5595753366118</v>
+        <v>17.01294405856082</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08407519657001572</v>
+        <v>0.08389330173349506</v>
       </c>
       <c r="C14">
-        <v>20.72864078725417</v>
+        <v>20.55750657366135</v>
       </c>
       <c r="D14">
-        <v>23.45008078725417</v>
+        <v>23.50681657366134</v>
       </c>
       <c r="E14">
-        <v>1.94744</v>
+        <v>2.17531</v>
       </c>
       <c r="F14">
-        <v>2.73444</v>
+        <v>2.96231</v>
       </c>
       <c r="G14">
         <v>0.013</v>
@@ -2417,28 +2417,28 @@
         <v>2.34</v>
       </c>
       <c r="M14">
-        <v>0.137542332</v>
+        <v>0.149004193</v>
       </c>
       <c r="N14">
-        <v>2.202457668</v>
+        <v>2.190995807</v>
       </c>
       <c r="O14">
-        <v>0.550614417</v>
+        <v>0.5477489517499999</v>
       </c>
       <c r="P14">
-        <v>1.651843251</v>
+        <v>1.64324685525</v>
       </c>
       <c r="Q14">
-        <v>1.651843251</v>
+        <v>1.64324685525</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0903956779204724</v>
+        <v>0.09079201348677593</v>
       </c>
       <c r="T14">
-        <v>0.6489214519237759</v>
+        <v>0.6546886173336922</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.01294405856082</v>
+        <v>15.70425605405614</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08389330173349506</v>
+        <v>0.08371140689697439</v>
       </c>
       <c r="C15">
-        <v>20.55750657366135</v>
+        <v>20.38664756222188</v>
       </c>
       <c r="D15">
-        <v>23.50681657366134</v>
+        <v>23.56382756222188</v>
       </c>
       <c r="E15">
-        <v>2.17531</v>
+        <v>2.40318</v>
       </c>
       <c r="F15">
-        <v>2.96231</v>
+        <v>3.19018</v>
       </c>
       <c r="G15">
         <v>0.013</v>
@@ -2499,28 +2499,28 @@
         <v>2.34</v>
       </c>
       <c r="M15">
-        <v>0.149004193</v>
+        <v>0.160466054</v>
       </c>
       <c r="N15">
-        <v>2.190995807</v>
+        <v>2.179533946</v>
       </c>
       <c r="O15">
-        <v>0.5477489517499999</v>
+        <v>0.5448834865</v>
       </c>
       <c r="P15">
-        <v>1.64324685525</v>
+        <v>1.6346504595</v>
       </c>
       <c r="Q15">
-        <v>1.64324685525</v>
+        <v>1.6346504595</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09079201348677593</v>
+        <v>0.09119756615927255</v>
       </c>
       <c r="T15">
-        <v>0.6546886173336922</v>
+        <v>0.6605899028694204</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.70425605405614</v>
+        <v>14.58252347876642</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08371140689697439</v>
+        <v>0.08352951206045374</v>
       </c>
       <c r="C16">
-        <v>20.38664756222188</v>
+        <v>20.2160657601439</v>
       </c>
       <c r="D16">
-        <v>23.56382756222188</v>
+        <v>23.6211157601439</v>
       </c>
       <c r="E16">
-        <v>2.40318</v>
+        <v>2.631050000000001</v>
       </c>
       <c r="F16">
-        <v>3.19018</v>
+        <v>3.41805</v>
       </c>
       <c r="G16">
         <v>0.013</v>
@@ -2581,28 +2581,28 @@
         <v>2.34</v>
       </c>
       <c r="M16">
-        <v>0.160466054</v>
+        <v>0.171927915</v>
       </c>
       <c r="N16">
-        <v>2.179533946</v>
+        <v>2.168072085</v>
       </c>
       <c r="O16">
-        <v>0.5448834865</v>
+        <v>0.54201802125</v>
       </c>
       <c r="P16">
-        <v>1.6346504595</v>
+        <v>1.62605406375</v>
       </c>
       <c r="Q16">
-        <v>1.6346504595</v>
+        <v>1.62605406375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09119756615927255</v>
+        <v>0.09161266124759262</v>
       </c>
       <c r="T16">
-        <v>0.6605899028694204</v>
+        <v>0.6666300421824599</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.58252347876642</v>
+        <v>13.61035524684866</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08352951206045374</v>
+        <v>0.08352761722393306</v>
       </c>
       <c r="C17">
-        <v>20.2160657601439</v>
+        <v>19.98879400931856</v>
       </c>
       <c r="D17">
-        <v>23.6211157601439</v>
+        <v>23.62171400931856</v>
       </c>
       <c r="E17">
-        <v>2.63105</v>
+        <v>2.85892</v>
       </c>
       <c r="F17">
-        <v>3.41805</v>
+        <v>3.64592</v>
       </c>
       <c r="G17">
         <v>0.013</v>
@@ -2663,45 +2663,45 @@
         <v>2.34</v>
       </c>
       <c r="M17">
-        <v>0.171927915</v>
+        <v>0.188858656</v>
       </c>
       <c r="N17">
-        <v>2.168072085</v>
+        <v>2.151141344</v>
       </c>
       <c r="O17">
-        <v>0.54201802125</v>
+        <v>0.537785336</v>
       </c>
       <c r="P17">
-        <v>1.62605406375</v>
+        <v>1.613356008</v>
       </c>
       <c r="Q17">
-        <v>1.62605406375</v>
+        <v>1.613356008</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09161266124759262</v>
+        <v>0.09203763955230128</v>
       </c>
       <c r="T17">
-        <v>0.6666300421824599</v>
+        <v>0.6728139943362861</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.61035524684866</v>
+        <v>12.39021842874917</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08352761722393306</v>
+        <v>0.08335697238741241</v>
       </c>
       <c r="C18">
-        <v>19.98879400931856</v>
+        <v>19.81492555849432</v>
       </c>
       <c r="D18">
-        <v>23.62171400931856</v>
+        <v>23.67571555849432</v>
       </c>
       <c r="E18">
-        <v>2.85892</v>
+        <v>3.08679</v>
       </c>
       <c r="F18">
-        <v>3.64592</v>
+        <v>3.87379</v>
       </c>
       <c r="G18">
         <v>0.013</v>
@@ -2745,28 +2745,28 @@
         <v>2.34</v>
       </c>
       <c r="M18">
-        <v>0.188858656</v>
+        <v>0.200662322</v>
       </c>
       <c r="N18">
-        <v>2.151141344</v>
+        <v>2.139337678</v>
       </c>
       <c r="O18">
-        <v>0.537785336</v>
+        <v>0.5348344195</v>
       </c>
       <c r="P18">
-        <v>1.613356008</v>
+        <v>1.6045032585</v>
       </c>
       <c r="Q18">
-        <v>1.613356008</v>
+        <v>1.6045032585</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09203763955230128</v>
+        <v>0.09247285829808724</v>
       </c>
       <c r="T18">
-        <v>0.6728139943362861</v>
+        <v>0.6791469573853852</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.39021842874917</v>
+        <v>11.66138205058745</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08335697238741241</v>
+        <v>0.08318632755089175</v>
       </c>
       <c r="C19">
-        <v>19.81492555849432</v>
+        <v>19.64130457906285</v>
       </c>
       <c r="D19">
-        <v>23.67571555849432</v>
+        <v>23.72996457906284</v>
       </c>
       <c r="E19">
-        <v>3.08679</v>
+        <v>3.314660000000001</v>
       </c>
       <c r="F19">
-        <v>3.87379</v>
+        <v>4.101660000000001</v>
       </c>
       <c r="G19">
         <v>0.013</v>
@@ -2827,28 +2827,28 @@
         <v>2.34</v>
       </c>
       <c r="M19">
-        <v>0.200662322</v>
+        <v>0.212465988</v>
       </c>
       <c r="N19">
-        <v>2.139337678</v>
+        <v>2.127534012</v>
       </c>
       <c r="O19">
-        <v>0.5348344195</v>
+        <v>0.531883503</v>
       </c>
       <c r="P19">
-        <v>1.6045032585</v>
+        <v>1.595650509</v>
       </c>
       <c r="Q19">
-        <v>1.6045032585</v>
+        <v>1.595650509</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09247285829808724</v>
+        <v>0.09291869213523385</v>
       </c>
       <c r="T19">
-        <v>0.6791469573853852</v>
+        <v>0.6856343829478769</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.66138205058745</v>
+        <v>11.01352749222148</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08318632755089177</v>
+        <v>0.0830156827143711</v>
       </c>
       <c r="C20">
-        <v>19.64130457906285</v>
+        <v>19.4679327760513</v>
       </c>
       <c r="D20">
-        <v>23.72996457906284</v>
+        <v>23.7844627760513</v>
       </c>
       <c r="E20">
-        <v>3.31466</v>
+        <v>3.54253</v>
       </c>
       <c r="F20">
-        <v>4.10166</v>
+        <v>4.32953</v>
       </c>
       <c r="G20">
         <v>0.013</v>
@@ -2909,28 +2909,28 @@
         <v>2.34</v>
       </c>
       <c r="M20">
-        <v>0.212465988</v>
+        <v>0.224269654</v>
       </c>
       <c r="N20">
-        <v>2.127534012</v>
+        <v>2.115730346</v>
       </c>
       <c r="O20">
-        <v>0.531883503</v>
+        <v>0.5289325865</v>
       </c>
       <c r="P20">
-        <v>1.595650509</v>
+        <v>1.5867977595</v>
       </c>
       <c r="Q20">
-        <v>1.595650509</v>
+        <v>1.5867977595</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09291869213523385</v>
+        <v>0.09337553421527296</v>
       </c>
       <c r="T20">
-        <v>0.6856343829478769</v>
+        <v>0.6922819918575908</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.01352749222148</v>
+        <v>10.43386815052562</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0830156827143711</v>
+        <v>0.08284503787785044</v>
       </c>
       <c r="C21">
-        <v>19.4679327760513</v>
+        <v>19.29481187018594</v>
       </c>
       <c r="D21">
-        <v>23.7844627760513</v>
+        <v>23.83921187018594</v>
       </c>
       <c r="E21">
-        <v>3.54253</v>
+        <v>3.7704</v>
       </c>
       <c r="F21">
-        <v>4.32953</v>
+        <v>4.5574</v>
       </c>
       <c r="G21">
         <v>0.013</v>
@@ -2991,28 +2991,28 @@
         <v>2.34</v>
       </c>
       <c r="M21">
-        <v>0.224269654</v>
+        <v>0.23607332</v>
       </c>
       <c r="N21">
-        <v>2.115730346</v>
+        <v>2.10392668</v>
       </c>
       <c r="O21">
-        <v>0.5289325865</v>
+        <v>0.52598167</v>
       </c>
       <c r="P21">
-        <v>1.5867977595</v>
+        <v>1.57794501</v>
       </c>
       <c r="Q21">
-        <v>1.5867977595</v>
+        <v>1.57794501</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09337553421527296</v>
+        <v>0.09384379734731305</v>
       </c>
       <c r="T21">
-        <v>0.6922819918575908</v>
+        <v>0.6990957909900473</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.43386815052562</v>
+        <v>9.912174742999335</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08284503787785044</v>
+        <v>0.08294214304132978</v>
       </c>
       <c r="C22">
-        <v>19.29481187018594</v>
+        <v>19.03575612299524</v>
       </c>
       <c r="D22">
-        <v>23.83921187018594</v>
+        <v>23.80802612299524</v>
       </c>
       <c r="E22">
-        <v>3.7704</v>
+        <v>3.998270000000001</v>
       </c>
       <c r="F22">
-        <v>4.5574</v>
+        <v>4.785270000000001</v>
       </c>
       <c r="G22">
         <v>0.013</v>
@@ -3073,45 +3073,45 @@
         <v>2.34</v>
       </c>
       <c r="M22">
-        <v>0.23607332</v>
+        <v>0.256011945</v>
       </c>
       <c r="N22">
-        <v>2.10392668</v>
+        <v>2.083988055</v>
       </c>
       <c r="O22">
-        <v>0.52598167</v>
+        <v>0.52099701375</v>
       </c>
       <c r="P22">
-        <v>1.57794501</v>
+        <v>1.56299104125</v>
       </c>
       <c r="Q22">
-        <v>1.57794501</v>
+        <v>1.56299104125</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09384379734731305</v>
+        <v>0.0943239152421896</v>
       </c>
       <c r="T22">
-        <v>0.6990957909900473</v>
+        <v>0.7060820913663636</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>9.912174742999335</v>
+        <v>9.140198516909043</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08294214304132978</v>
+        <v>0.08278424820480912</v>
       </c>
       <c r="C23">
-        <v>19.03575612299524</v>
+        <v>18.85863635488014</v>
       </c>
       <c r="D23">
-        <v>23.80802612299524</v>
+        <v>23.85877635488014</v>
       </c>
       <c r="E23">
-        <v>3.99827</v>
+        <v>4.22614</v>
       </c>
       <c r="F23">
-        <v>4.78527</v>
+        <v>5.01314</v>
       </c>
       <c r="G23">
         <v>0.013</v>
@@ -3155,28 +3155,28 @@
         <v>2.34</v>
       </c>
       <c r="M23">
-        <v>0.256011945</v>
+        <v>0.26820299</v>
       </c>
       <c r="N23">
-        <v>2.083988055</v>
+        <v>2.07179701</v>
       </c>
       <c r="O23">
-        <v>0.52099701375</v>
+        <v>0.5179492525</v>
       </c>
       <c r="P23">
-        <v>1.56299104125</v>
+        <v>1.5538477575</v>
       </c>
       <c r="Q23">
-        <v>1.56299104125</v>
+        <v>1.5538477575</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0943239152421896</v>
+        <v>0.09481634385231938</v>
       </c>
       <c r="T23">
-        <v>0.7060820913663636</v>
+        <v>0.7132475276497648</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.140198516909045</v>
+        <v>8.724734947958634</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08278424820480912</v>
+        <v>0.08262635336828847</v>
       </c>
       <c r="C24">
-        <v>18.85863635488014</v>
+        <v>18.68173341179566</v>
       </c>
       <c r="D24">
-        <v>23.85877635488014</v>
+        <v>23.90974341179566</v>
       </c>
       <c r="E24">
-        <v>4.22614</v>
+        <v>4.45401</v>
       </c>
       <c r="F24">
-        <v>5.01314</v>
+        <v>5.24101</v>
       </c>
       <c r="G24">
         <v>0.013</v>
@@ -3237,28 +3237,28 @@
         <v>2.34</v>
       </c>
       <c r="M24">
-        <v>0.26820299</v>
+        <v>0.280394035</v>
       </c>
       <c r="N24">
-        <v>2.07179701</v>
+        <v>2.059605965</v>
       </c>
       <c r="O24">
-        <v>0.5179492525</v>
+        <v>0.51490149125</v>
       </c>
       <c r="P24">
-        <v>1.5538477575</v>
+        <v>1.54470447375</v>
       </c>
       <c r="Q24">
-        <v>1.5538477575</v>
+        <v>1.54470447375</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09481634385231938</v>
+        <v>0.09532156281595904</v>
       </c>
       <c r="T24">
-        <v>0.7132475276497648</v>
+        <v>0.7205990791613064</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.724734947958634</v>
+        <v>8.345398645873477</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08262635336828847</v>
+        <v>0.0824684585317678</v>
       </c>
       <c r="C25">
-        <v>18.68173341179566</v>
+        <v>18.50504868625973</v>
       </c>
       <c r="D25">
-        <v>23.90974341179566</v>
+        <v>23.96092868625972</v>
       </c>
       <c r="E25">
-        <v>4.45401</v>
+        <v>4.68188</v>
       </c>
       <c r="F25">
-        <v>5.24101</v>
+        <v>5.46888</v>
       </c>
       <c r="G25">
         <v>0.013</v>
@@ -3319,28 +3319,28 @@
         <v>2.34</v>
       </c>
       <c r="M25">
-        <v>0.280394035</v>
+        <v>0.29258508</v>
       </c>
       <c r="N25">
-        <v>2.059605965</v>
+        <v>2.04741492</v>
       </c>
       <c r="O25">
-        <v>0.51490149125</v>
+        <v>0.51185373</v>
       </c>
       <c r="P25">
-        <v>1.54470447375</v>
+        <v>1.53556119</v>
       </c>
       <c r="Q25">
-        <v>1.54470447375</v>
+        <v>1.53556119</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09532156281595904</v>
+        <v>0.09584007701548396</v>
       </c>
       <c r="T25">
-        <v>0.7205990791613064</v>
+        <v>0.7281440925547308</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.345398645873477</v>
+        <v>7.997673702295415</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0824684585317678</v>
+        <v>0.08231056369524715</v>
       </c>
       <c r="C26">
-        <v>18.50504868625973</v>
+        <v>18.32858358274008</v>
       </c>
       <c r="D26">
-        <v>23.96092868625972</v>
+        <v>24.01233358274008</v>
       </c>
       <c r="E26">
-        <v>4.68188</v>
+        <v>4.90975</v>
       </c>
       <c r="F26">
-        <v>5.46888</v>
+        <v>5.69675</v>
       </c>
       <c r="G26">
         <v>0.013</v>
@@ -3401,28 +3401,28 @@
         <v>2.34</v>
       </c>
       <c r="M26">
-        <v>0.2925850799999999</v>
+        <v>0.304776125</v>
       </c>
       <c r="N26">
-        <v>2.04741492</v>
+        <v>2.035223875</v>
       </c>
       <c r="O26">
-        <v>0.51185373</v>
+        <v>0.5088059687499999</v>
       </c>
       <c r="P26">
-        <v>1.53556119</v>
+        <v>1.52641790625</v>
       </c>
       <c r="Q26">
-        <v>1.53556119</v>
+        <v>1.52641790625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09584007701548396</v>
+        <v>0.09637241826032952</v>
       </c>
       <c r="T26">
-        <v>0.7281440925547308</v>
+        <v>0.7358903063053129</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.997673702295416</v>
+        <v>7.677766754203598</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08231056369524715</v>
+        <v>0.08230866885872648</v>
       </c>
       <c r="C27">
-        <v>18.32858358274008</v>
+        <v>18.10133181293187</v>
       </c>
       <c r="D27">
-        <v>24.01233358274008</v>
+        <v>24.01295181293187</v>
       </c>
       <c r="E27">
-        <v>4.90975</v>
+        <v>5.13762</v>
       </c>
       <c r="F27">
-        <v>5.69675</v>
+        <v>5.92462</v>
       </c>
       <c r="G27">
         <v>0.013</v>
@@ -3483,45 +3483,45 @@
         <v>2.34</v>
       </c>
       <c r="M27">
-        <v>0.304776125</v>
+        <v>0.321706866</v>
       </c>
       <c r="N27">
-        <v>2.035223875</v>
+        <v>2.018293134</v>
       </c>
       <c r="O27">
-        <v>0.5088059687499999</v>
+        <v>0.5045732835</v>
       </c>
       <c r="P27">
-        <v>1.52641790625</v>
+        <v>1.5137198505</v>
       </c>
       <c r="Q27">
-        <v>1.52641790625</v>
+        <v>1.5137198505</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09637241826032952</v>
+        <v>0.09691914710638713</v>
       </c>
       <c r="T27">
-        <v>0.7358903063053129</v>
+        <v>0.7438458771842893</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.677766754203598</v>
+        <v>7.273702389677937</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08230866885872648</v>
+        <v>0.08215677402220582</v>
       </c>
       <c r="C28">
-        <v>18.10133181293187</v>
+        <v>17.92312446631065</v>
       </c>
       <c r="D28">
-        <v>24.01295181293187</v>
+        <v>24.06261446631065</v>
       </c>
       <c r="E28">
-        <v>5.13762</v>
+        <v>5.36549</v>
       </c>
       <c r="F28">
-        <v>5.92462</v>
+        <v>6.15249</v>
       </c>
       <c r="G28">
         <v>0.013</v>
@@ -3565,28 +3565,28 @@
         <v>2.34</v>
       </c>
       <c r="M28">
-        <v>0.321706866</v>
+        <v>0.334080207</v>
       </c>
       <c r="N28">
-        <v>2.018293134</v>
+        <v>2.005919793</v>
       </c>
       <c r="O28">
-        <v>0.5045732835</v>
+        <v>0.50147994825</v>
       </c>
       <c r="P28">
-        <v>1.5137198505</v>
+        <v>1.50443984475</v>
       </c>
       <c r="Q28">
-        <v>1.5137198505</v>
+        <v>1.50443984475</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09691914710638713</v>
+        <v>0.09748085482493948</v>
       </c>
       <c r="T28">
-        <v>0.7438458771842893</v>
+        <v>0.7520194089092651</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.273702389677937</v>
+        <v>7.00430600487505</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08215677402220582</v>
+        <v>0.08200487918568516</v>
       </c>
       <c r="C29">
-        <v>17.92312446631065</v>
+        <v>17.74512296615102</v>
       </c>
       <c r="D29">
-        <v>24.06261446631065</v>
+        <v>24.11248296615102</v>
       </c>
       <c r="E29">
-        <v>5.36549</v>
+        <v>5.593360000000001</v>
       </c>
       <c r="F29">
-        <v>6.15249</v>
+        <v>6.38036</v>
       </c>
       <c r="G29">
         <v>0.013</v>
@@ -3647,28 +3647,28 @@
         <v>2.34</v>
       </c>
       <c r="M29">
-        <v>0.334080207</v>
+        <v>0.3464535480000001</v>
       </c>
       <c r="N29">
-        <v>2.005919793</v>
+        <v>1.993546452</v>
       </c>
       <c r="O29">
-        <v>0.50147994825</v>
+        <v>0.498386613</v>
       </c>
       <c r="P29">
-        <v>1.50443984475</v>
+        <v>1.495159839</v>
       </c>
       <c r="Q29">
-        <v>1.50443984475</v>
+        <v>1.495159839</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09748085482493948</v>
+        <v>0.09805816553567384</v>
       </c>
       <c r="T29">
-        <v>0.7520194089092651</v>
+        <v>0.7604199831821568</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.00430600487505</v>
+        <v>6.754152218986655</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08200487918568516</v>
+        <v>0.08185298434916452</v>
       </c>
       <c r="C30">
-        <v>17.74512296615102</v>
+        <v>17.56732859492863</v>
       </c>
       <c r="D30">
-        <v>24.11248296615102</v>
+        <v>24.16255859492863</v>
       </c>
       <c r="E30">
-        <v>5.593360000000001</v>
+        <v>5.821230000000001</v>
       </c>
       <c r="F30">
-        <v>6.38036</v>
+        <v>6.608230000000001</v>
       </c>
       <c r="G30">
         <v>0.013</v>
@@ -3729,28 +3729,28 @@
         <v>2.34</v>
       </c>
       <c r="M30">
-        <v>0.3464535480000001</v>
+        <v>0.358826889</v>
       </c>
       <c r="N30">
-        <v>1.993546452</v>
+        <v>1.981173111</v>
       </c>
       <c r="O30">
-        <v>0.498386613</v>
+        <v>0.49529327775</v>
       </c>
       <c r="P30">
-        <v>1.495159839</v>
+        <v>1.48587983325</v>
       </c>
       <c r="Q30">
-        <v>1.495159839</v>
+        <v>1.48587983325</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09805816553567384</v>
+        <v>0.09865173851995002</v>
       </c>
       <c r="T30">
-        <v>0.7604199831821568</v>
+        <v>0.7690571933500594</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.754152218986655</v>
+        <v>6.521250418331944</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08185298434916451</v>
+        <v>0.08170108951264385</v>
       </c>
       <c r="C31">
-        <v>17.56732859492864</v>
+        <v>17.38974264579491</v>
       </c>
       <c r="D31">
-        <v>24.16255859492864</v>
+        <v>24.2128426457949</v>
       </c>
       <c r="E31">
-        <v>5.821229999999999</v>
+        <v>6.049099999999999</v>
       </c>
       <c r="F31">
-        <v>6.608229999999999</v>
+        <v>6.836099999999999</v>
       </c>
       <c r="G31">
         <v>0.013</v>
@@ -3811,28 +3811,28 @@
         <v>2.34</v>
       </c>
       <c r="M31">
-        <v>0.3588268889999999</v>
+        <v>0.37120023</v>
       </c>
       <c r="N31">
-        <v>1.981173111</v>
+        <v>1.96879977</v>
       </c>
       <c r="O31">
-        <v>0.49529327775</v>
+        <v>0.4921999425</v>
       </c>
       <c r="P31">
-        <v>1.48587983325</v>
+        <v>1.4765998275</v>
       </c>
       <c r="Q31">
-        <v>1.48587983325</v>
+        <v>1.4765998275</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09865173851995002</v>
+        <v>0.09926227073234836</v>
       </c>
       <c r="T31">
-        <v>0.7690571933500594</v>
+        <v>0.7779411809513308</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.521250418331944</v>
+        <v>6.303875404387546</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08170108951264385</v>
+        <v>0.08178169467612317</v>
       </c>
       <c r="C32">
-        <v>17.38974264579491</v>
+        <v>17.13516266228955</v>
       </c>
       <c r="D32">
-        <v>24.2128426457949</v>
+        <v>24.18613266228954</v>
       </c>
       <c r="E32">
-        <v>6.049099999999999</v>
+        <v>6.276969999999999</v>
       </c>
       <c r="F32">
-        <v>6.836099999999999</v>
+        <v>7.063969999999999</v>
       </c>
       <c r="G32">
         <v>0.013</v>
@@ -3893,45 +3893,45 @@
         <v>2.34</v>
       </c>
       <c r="M32">
-        <v>0.37120023</v>
+        <v>0.390637541</v>
       </c>
       <c r="N32">
-        <v>1.96879977</v>
+        <v>1.949362459</v>
       </c>
       <c r="O32">
-        <v>0.4921999425</v>
+        <v>0.48734061475</v>
       </c>
       <c r="P32">
-        <v>1.4765998275</v>
+        <v>1.46202184425</v>
       </c>
       <c r="Q32">
-        <v>1.4765998275</v>
+        <v>1.46202184425</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09926227073234836</v>
+        <v>0.09989049953061331</v>
       </c>
       <c r="T32">
-        <v>0.7779411809513308</v>
+        <v>0.7870826754395955</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.303875404387546</v>
+        <v>5.990207684621893</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08178169467612317</v>
+        <v>0.08163729983960252</v>
       </c>
       <c r="C33">
-        <v>17.13516266228955</v>
+        <v>16.95518236541349</v>
       </c>
       <c r="D33">
-        <v>24.18613266228954</v>
+        <v>24.23402236541349</v>
       </c>
       <c r="E33">
-        <v>6.276969999999999</v>
+        <v>6.50484</v>
       </c>
       <c r="F33">
-        <v>7.063969999999999</v>
+        <v>7.29184</v>
       </c>
       <c r="G33">
         <v>0.013</v>
@@ -3975,28 +3975,28 @@
         <v>2.34</v>
       </c>
       <c r="M33">
-        <v>0.390637541</v>
+        <v>0.403238752</v>
       </c>
       <c r="N33">
-        <v>1.949362459</v>
+        <v>1.936761248</v>
       </c>
       <c r="O33">
-        <v>0.48734061475</v>
+        <v>0.484190312</v>
       </c>
       <c r="P33">
-        <v>1.46202184425</v>
+        <v>1.452570936</v>
       </c>
       <c r="Q33">
-        <v>1.46202184425</v>
+        <v>1.452570936</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09989049953061331</v>
+        <v>0.1005372056464743</v>
       </c>
       <c r="T33">
-        <v>0.7870826754395955</v>
+        <v>0.7964930374128093</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.990207684621893</v>
+        <v>5.80301369447746</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08163729983960252</v>
+        <v>0.08149290500308187</v>
       </c>
       <c r="C34">
-        <v>16.95518236541349</v>
+        <v>16.77539209261411</v>
       </c>
       <c r="D34">
-        <v>24.23402236541349</v>
+        <v>24.28210209261411</v>
       </c>
       <c r="E34">
-        <v>6.50484</v>
+        <v>6.73271</v>
       </c>
       <c r="F34">
-        <v>7.29184</v>
+        <v>7.51971</v>
       </c>
       <c r="G34">
         <v>0.013</v>
@@ -4057,28 +4057,28 @@
         <v>2.34</v>
       </c>
       <c r="M34">
-        <v>0.403238752</v>
+        <v>0.415839963</v>
       </c>
       <c r="N34">
-        <v>1.936761248</v>
+        <v>1.924160037</v>
       </c>
       <c r="O34">
-        <v>0.484190312</v>
+        <v>0.48104000925</v>
       </c>
       <c r="P34">
-        <v>1.452570936</v>
+        <v>1.44312002775</v>
       </c>
       <c r="Q34">
-        <v>1.452570936</v>
+        <v>1.44312002775</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1005372056464743</v>
+        <v>0.1012032164225103</v>
       </c>
       <c r="T34">
-        <v>0.7964930374128093</v>
+        <v>0.8061843057135817</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.80301369447746</v>
+        <v>5.627164794644808</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08149290500308187</v>
+        <v>0.08134851016656121</v>
       </c>
       <c r="C35">
-        <v>16.77539209261411</v>
+        <v>16.59579297714957</v>
       </c>
       <c r="D35">
-        <v>24.28210209261411</v>
+        <v>24.33037297714957</v>
       </c>
       <c r="E35">
-        <v>6.73271</v>
+        <v>6.96058</v>
       </c>
       <c r="F35">
-        <v>7.51971</v>
+        <v>7.74758</v>
       </c>
       <c r="G35">
         <v>0.013</v>
@@ -4139,28 +4139,28 @@
         <v>2.34</v>
       </c>
       <c r="M35">
-        <v>0.415839963</v>
+        <v>0.428441174</v>
       </c>
       <c r="N35">
-        <v>1.924160037</v>
+        <v>1.911558826</v>
       </c>
       <c r="O35">
-        <v>0.48104000925</v>
+        <v>0.4778897065</v>
       </c>
       <c r="P35">
-        <v>1.44312002775</v>
+        <v>1.4336691195</v>
       </c>
       <c r="Q35">
-        <v>1.44312002775</v>
+        <v>1.4336691195</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1012032164225103</v>
+        <v>0.1018894093432746</v>
       </c>
       <c r="T35">
-        <v>0.8061843057135817</v>
+        <v>0.8161692488113471</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.627164794644808</v>
+        <v>5.46165994774349</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08134851016656121</v>
+        <v>0.08120411533004054</v>
       </c>
       <c r="C36">
-        <v>16.59579297714957</v>
+        <v>16.41638616130731</v>
       </c>
       <c r="D36">
-        <v>24.33037297714957</v>
+        <v>24.37883616130731</v>
       </c>
       <c r="E36">
-        <v>6.96058</v>
+        <v>7.18845</v>
       </c>
       <c r="F36">
-        <v>7.74758</v>
+        <v>7.97545</v>
       </c>
       <c r="G36">
         <v>0.013</v>
@@ -4221,28 +4221,28 @@
         <v>2.34</v>
       </c>
       <c r="M36">
-        <v>0.428441174</v>
+        <v>0.441042385</v>
       </c>
       <c r="N36">
-        <v>1.911558826</v>
+        <v>1.898957615</v>
       </c>
       <c r="O36">
-        <v>0.4778897065</v>
+        <v>0.47473940375</v>
       </c>
       <c r="P36">
-        <v>1.4336691195</v>
+        <v>1.42421821125</v>
       </c>
       <c r="Q36">
-        <v>1.4336691195</v>
+        <v>1.42421821125</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1018894093432746</v>
+        <v>0.1025967158923701</v>
       </c>
       <c r="T36">
-        <v>0.8161692488113471</v>
+        <v>0.8264614209275054</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.46165994774349</v>
+        <v>5.305612520665105</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08120411533004054</v>
+        <v>0.08105972049351988</v>
       </c>
       <c r="C37">
-        <v>16.41638616130731</v>
+        <v>16.23717279649412</v>
       </c>
       <c r="D37">
-        <v>24.37883616130731</v>
+        <v>24.42749279649412</v>
       </c>
       <c r="E37">
-        <v>7.18845</v>
+        <v>7.416320000000002</v>
       </c>
       <c r="F37">
-        <v>7.97545</v>
+        <v>8.203320000000001</v>
       </c>
       <c r="G37">
         <v>0.013</v>
@@ -4303,28 +4303,28 @@
         <v>2.34</v>
       </c>
       <c r="M37">
-        <v>0.441042385</v>
+        <v>0.4536435960000001</v>
       </c>
       <c r="N37">
-        <v>1.898957615</v>
+        <v>1.886356404</v>
       </c>
       <c r="O37">
-        <v>0.47473940375</v>
+        <v>0.471589101</v>
       </c>
       <c r="P37">
-        <v>1.42421821125</v>
+        <v>1.414767303</v>
       </c>
       <c r="Q37">
-        <v>1.42421821125</v>
+        <v>1.414767303</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1025967158923701</v>
+        <v>0.1033261257711248</v>
       </c>
       <c r="T37">
-        <v>0.8264614209275054</v>
+        <v>0.8370752234222935</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.305612520665105</v>
+        <v>5.158234395091074</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08105972049351989</v>
+        <v>0.08091532565699924</v>
       </c>
       <c r="C38">
-        <v>16.23717279649411</v>
+        <v>16.05815404332736</v>
       </c>
       <c r="D38">
-        <v>24.42749279649411</v>
+        <v>24.47634404332736</v>
       </c>
       <c r="E38">
-        <v>7.41632</v>
+        <v>7.644189999999999</v>
       </c>
       <c r="F38">
-        <v>8.20332</v>
+        <v>8.431189999999999</v>
       </c>
       <c r="G38">
         <v>0.013</v>
@@ -4385,28 +4385,28 @@
         <v>2.34</v>
       </c>
       <c r="M38">
-        <v>0.453643596</v>
+        <v>0.466244807</v>
       </c>
       <c r="N38">
-        <v>1.886356404</v>
+        <v>1.873755193</v>
       </c>
       <c r="O38">
-        <v>0.471589101</v>
+        <v>0.46843879825</v>
       </c>
       <c r="P38">
-        <v>1.414767303</v>
+        <v>1.40531639475</v>
       </c>
       <c r="Q38">
-        <v>1.414767303</v>
+        <v>1.40531639475</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1033261257711248</v>
+        <v>0.1040786915190464</v>
       </c>
       <c r="T38">
-        <v>0.8370752234222935</v>
+        <v>0.8480259720280273</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.158234395091075</v>
+        <v>5.018822654683208</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08091532565699924</v>
+        <v>0.08077093082047856</v>
       </c>
       <c r="C39">
-        <v>16.05815404332736</v>
+        <v>15.87933107172721</v>
       </c>
       <c r="D39">
-        <v>24.47634404332736</v>
+        <v>24.52539107172721</v>
       </c>
       <c r="E39">
-        <v>7.644189999999999</v>
+        <v>7.87206</v>
       </c>
       <c r="F39">
-        <v>8.431189999999999</v>
+        <v>8.65906</v>
       </c>
       <c r="G39">
         <v>0.013</v>
@@ -4467,28 +4467,28 @@
         <v>2.34</v>
       </c>
       <c r="M39">
-        <v>0.466244807</v>
+        <v>0.478846018</v>
       </c>
       <c r="N39">
-        <v>1.873755193</v>
+        <v>1.861153982</v>
       </c>
       <c r="O39">
-        <v>0.46843879825</v>
+        <v>0.4652884955</v>
       </c>
       <c r="P39">
-        <v>1.40531639475</v>
+        <v>1.3958654865</v>
       </c>
       <c r="Q39">
-        <v>1.40531639475</v>
+        <v>1.3958654865</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1040786915190464</v>
+        <v>0.1048555335814171</v>
       </c>
       <c r="T39">
-        <v>0.8480259720280273</v>
+        <v>0.8593299705887848</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.018822654683208</v>
+        <v>4.886748374296808</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08077093082047856</v>
+        <v>0.08062653598395793</v>
       </c>
       <c r="C40">
-        <v>15.87933107172721</v>
+        <v>15.70070506101006</v>
       </c>
       <c r="D40">
-        <v>24.52539107172721</v>
+        <v>24.57463506101006</v>
       </c>
       <c r="E40">
-        <v>7.87206</v>
+        <v>8.099930000000001</v>
       </c>
       <c r="F40">
-        <v>8.65906</v>
+        <v>8.88693</v>
       </c>
       <c r="G40">
         <v>0.013</v>
@@ -4549,28 +4549,28 @@
         <v>2.34</v>
       </c>
       <c r="M40">
-        <v>0.478846018</v>
+        <v>0.491447229</v>
       </c>
       <c r="N40">
-        <v>1.861153982</v>
+        <v>1.848552771</v>
       </c>
       <c r="O40">
-        <v>0.4652884955</v>
+        <v>0.46213819275</v>
       </c>
       <c r="P40">
-        <v>1.3958654865</v>
+        <v>1.38641457825</v>
       </c>
       <c r="Q40">
-        <v>1.3958654865</v>
+        <v>1.38641457825</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1048555335814171</v>
+        <v>0.1056578458753409</v>
       </c>
       <c r="T40">
-        <v>0.8593299705887848</v>
+        <v>0.8710045920531737</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.886748374296808</v>
+        <v>4.761447133930223</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08062653598395793</v>
+        <v>0.08048214114743726</v>
       </c>
       <c r="C41">
-        <v>15.70070506101006</v>
+        <v>15.5222771999831</v>
       </c>
       <c r="D41">
-        <v>24.57463506101006</v>
+        <v>24.62407719998309</v>
       </c>
       <c r="E41">
-        <v>8.099930000000001</v>
+        <v>8.3278</v>
       </c>
       <c r="F41">
-        <v>8.88693</v>
+        <v>9.114800000000001</v>
       </c>
       <c r="G41">
         <v>0.013</v>
@@ -4631,28 +4631,28 @@
         <v>2.34</v>
       </c>
       <c r="M41">
-        <v>0.491447229</v>
+        <v>0.50404844</v>
       </c>
       <c r="N41">
-        <v>1.848552771</v>
+        <v>1.83595156</v>
       </c>
       <c r="O41">
-        <v>0.46213819275</v>
+        <v>0.45898789</v>
       </c>
       <c r="P41">
-        <v>1.38641457825</v>
+        <v>1.37696367</v>
       </c>
       <c r="Q41">
-        <v>1.38641457825</v>
+        <v>1.37696367</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1056578458753409</v>
+        <v>0.1064869019123954</v>
       </c>
       <c r="T41">
-        <v>0.8710045920531737</v>
+        <v>0.8830683675663755</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.761447133930223</v>
+        <v>4.642410955581967</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08048214114743726</v>
+        <v>0.0803377463109166</v>
       </c>
       <c r="C42">
-        <v>15.5222771999831</v>
+        <v>15.34404868703987</v>
       </c>
       <c r="D42">
-        <v>24.62407719998309</v>
+        <v>24.67371868703987</v>
       </c>
       <c r="E42">
-        <v>8.3278</v>
+        <v>8.555669999999999</v>
       </c>
       <c r="F42">
-        <v>9.114800000000001</v>
+        <v>9.34267</v>
       </c>
       <c r="G42">
         <v>0.013</v>
@@ -4713,28 +4713,28 @@
         <v>2.34</v>
       </c>
       <c r="M42">
-        <v>0.50404844</v>
+        <v>0.516649651</v>
       </c>
       <c r="N42">
-        <v>1.83595156</v>
+        <v>1.823350349</v>
       </c>
       <c r="O42">
-        <v>0.45898789</v>
+        <v>0.45583758725</v>
       </c>
       <c r="P42">
-        <v>1.37696367</v>
+        <v>1.36751276175</v>
       </c>
       <c r="Q42">
-        <v>1.37696367</v>
+        <v>1.36751276175</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1064869019123954</v>
+        <v>0.1073440615439265</v>
       </c>
       <c r="T42">
-        <v>0.8830683675663755</v>
+        <v>0.8955410846223979</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.642410955581967</v>
+        <v>4.529181420079968</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0803377463109166</v>
+        <v>0.08098085147439593</v>
       </c>
       <c r="C43">
-        <v>15.34404868703987</v>
+        <v>14.89661134353544</v>
       </c>
       <c r="D43">
-        <v>24.67371868703987</v>
+        <v>24.45415134353544</v>
       </c>
       <c r="E43">
-        <v>8.555669999999999</v>
+        <v>8.783540000000002</v>
       </c>
       <c r="F43">
-        <v>9.34267</v>
+        <v>9.570540000000001</v>
       </c>
       <c r="G43">
         <v>0.013</v>
@@ -4795,45 +4795,45 @@
         <v>2.34</v>
       </c>
       <c r="M43">
-        <v>0.516649651</v>
+        <v>0.5531772120000001</v>
       </c>
       <c r="N43">
-        <v>1.823350349</v>
+        <v>1.786822788</v>
       </c>
       <c r="O43">
-        <v>0.45583758725</v>
+        <v>0.446705697</v>
       </c>
       <c r="P43">
-        <v>1.36751276175</v>
+        <v>1.340117091</v>
       </c>
       <c r="Q43">
-        <v>1.36751276175</v>
+        <v>1.340117091</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1073440615439265</v>
+        <v>0.1082307784041309</v>
       </c>
       <c r="T43">
-        <v>0.8955410846223979</v>
+        <v>0.908443895370007</v>
       </c>
       <c r="U43">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.529181420079968</v>
+        <v>4.230109175213094</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08098085147439595</v>
+        <v>0.08085520663787528</v>
       </c>
       <c r="C44">
-        <v>14.89661134353543</v>
+        <v>14.71133099618286</v>
       </c>
       <c r="D44">
-        <v>24.45415134353543</v>
+        <v>24.49674099618285</v>
       </c>
       <c r="E44">
-        <v>8.783539999999999</v>
+        <v>9.011409999999998</v>
       </c>
       <c r="F44">
-        <v>9.570539999999999</v>
+        <v>9.798409999999999</v>
       </c>
       <c r="G44">
         <v>0.013</v>
@@ -4877,28 +4877,28 @@
         <v>2.34</v>
       </c>
       <c r="M44">
-        <v>0.553177212</v>
+        <v>0.566348098</v>
       </c>
       <c r="N44">
-        <v>1.786822788</v>
+        <v>1.773651902</v>
       </c>
       <c r="O44">
-        <v>0.446705697</v>
+        <v>0.4434129755</v>
       </c>
       <c r="P44">
-        <v>1.340117091</v>
+        <v>1.3302389265</v>
       </c>
       <c r="Q44">
-        <v>1.340117091</v>
+        <v>1.3302389265</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1082307784041309</v>
+        <v>0.1091486081366233</v>
       </c>
       <c r="T44">
-        <v>0.908443895370007</v>
+        <v>0.9217994363192866</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.230109175213096</v>
+        <v>4.131734543231396</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08085520663787528</v>
+        <v>0.08072956180135463</v>
       </c>
       <c r="C45">
-        <v>14.71133099618286</v>
+        <v>14.52619925698043</v>
       </c>
       <c r="D45">
-        <v>24.49674099618285</v>
+        <v>24.53947925698043</v>
       </c>
       <c r="E45">
-        <v>9.011409999999998</v>
+        <v>9.239280000000001</v>
       </c>
       <c r="F45">
-        <v>9.798409999999999</v>
+        <v>10.02628</v>
       </c>
       <c r="G45">
         <v>0.013</v>
@@ -4959,28 +4959,28 @@
         <v>2.34</v>
       </c>
       <c r="M45">
-        <v>0.566348098</v>
+        <v>0.579518984</v>
       </c>
       <c r="N45">
-        <v>1.773651902</v>
+        <v>1.760481016</v>
       </c>
       <c r="O45">
-        <v>0.4434129755</v>
+        <v>0.440120254</v>
       </c>
       <c r="P45">
-        <v>1.3302389265</v>
+        <v>1.320360762</v>
       </c>
       <c r="Q45">
-        <v>1.3302389265</v>
+        <v>1.320360762</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1091486081366233</v>
+        <v>0.110099217502419</v>
       </c>
       <c r="T45">
-        <v>0.9217994363192866</v>
+        <v>0.935631960873898</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.131734543231396</v>
+        <v>4.037831485430683</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08072956180135463</v>
+        <v>0.08178516696483397</v>
       </c>
       <c r="C46">
-        <v>14.52619925698043</v>
+        <v>13.94383338030592</v>
       </c>
       <c r="D46">
-        <v>24.53947925698043</v>
+        <v>24.18498338030592</v>
       </c>
       <c r="E46">
-        <v>9.239280000000001</v>
+        <v>9.46715</v>
       </c>
       <c r="F46">
-        <v>10.02628</v>
+        <v>10.25415</v>
       </c>
       <c r="G46">
         <v>0.013</v>
@@ -5041,45 +5041,45 @@
         <v>2.34</v>
       </c>
       <c r="M46">
-        <v>0.579518984</v>
+        <v>0.6285793949999999</v>
       </c>
       <c r="N46">
-        <v>1.760481016</v>
+        <v>1.711420605</v>
       </c>
       <c r="O46">
-        <v>0.440120254</v>
+        <v>0.42785515125</v>
       </c>
       <c r="P46">
-        <v>1.320360762</v>
+        <v>1.28356545375</v>
       </c>
       <c r="Q46">
-        <v>1.320360762</v>
+        <v>1.28356545375</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.110099217502419</v>
+        <v>0.1110843944815163</v>
       </c>
       <c r="T46">
-        <v>0.935631960873898</v>
+        <v>0.9499674863214039</v>
       </c>
       <c r="U46">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.037831485430683</v>
+        <v>3.722680091987425</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08178516696483397</v>
+        <v>0.08168577212831331</v>
       </c>
       <c r="C47">
-        <v>13.94383338030592</v>
+        <v>13.7489050109589</v>
       </c>
       <c r="D47">
-        <v>24.18498338030592</v>
+        <v>24.2179250109589</v>
       </c>
       <c r="E47">
-        <v>9.46715</v>
+        <v>9.69502</v>
       </c>
       <c r="F47">
-        <v>10.25415</v>
+        <v>10.48202</v>
       </c>
       <c r="G47">
         <v>0.013</v>
@@ -5123,28 +5123,28 @@
         <v>2.34</v>
       </c>
       <c r="M47">
-        <v>0.6285793949999999</v>
+        <v>0.642547826</v>
       </c>
       <c r="N47">
-        <v>1.711420605</v>
+        <v>1.697452174</v>
       </c>
       <c r="O47">
-        <v>0.42785515125</v>
+        <v>0.4243630435</v>
       </c>
       <c r="P47">
-        <v>1.28356545375</v>
+        <v>1.2730891305</v>
       </c>
       <c r="Q47">
-        <v>1.28356545375</v>
+        <v>1.2730891305</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1110843944815163</v>
+        <v>0.1121060594968765</v>
       </c>
       <c r="T47">
-        <v>0.9499674863214039</v>
+        <v>0.9648339571558547</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.722680091987425</v>
+        <v>3.641752263900742</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08168577212831331</v>
+        <v>0.08158637729179263</v>
       </c>
       <c r="C48">
-        <v>13.7489050109589</v>
+        <v>13.55406650159484</v>
       </c>
       <c r="D48">
-        <v>24.2179250109589</v>
+        <v>24.25095650159484</v>
       </c>
       <c r="E48">
-        <v>9.69502</v>
+        <v>9.922889999999999</v>
       </c>
       <c r="F48">
-        <v>10.48202</v>
+        <v>10.70989</v>
       </c>
       <c r="G48">
         <v>0.013</v>
@@ -5205,28 +5205,28 @@
         <v>2.34</v>
       </c>
       <c r="M48">
-        <v>0.642547826</v>
+        <v>0.6565162569999999</v>
       </c>
       <c r="N48">
-        <v>1.697452174</v>
+        <v>1.683483743</v>
       </c>
       <c r="O48">
-        <v>0.4243630435</v>
+        <v>0.42087093575</v>
       </c>
       <c r="P48">
-        <v>1.2730891305</v>
+        <v>1.26261280725</v>
       </c>
       <c r="Q48">
-        <v>1.2730891305</v>
+        <v>1.26261280725</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1121060594968765</v>
+        <v>0.1131662779090427</v>
       </c>
       <c r="T48">
-        <v>0.9648339571558547</v>
+        <v>0.9802614268897187</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.641752263900742</v>
+        <v>3.56426817317945</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08158637729179263</v>
+        <v>0.082494982455272</v>
       </c>
       <c r="C49">
-        <v>13.55406650159484</v>
+        <v>13.02755503162389</v>
       </c>
       <c r="D49">
-        <v>24.25095650159484</v>
+        <v>23.95231503162389</v>
       </c>
       <c r="E49">
-        <v>9.922889999999999</v>
+        <v>10.15076</v>
       </c>
       <c r="F49">
-        <v>10.70989</v>
+        <v>10.93776</v>
       </c>
       <c r="G49">
         <v>0.013</v>
@@ -5287,45 +5287,45 @@
         <v>2.34</v>
       </c>
       <c r="M49">
-        <v>0.6565162569999999</v>
+        <v>0.7011104160000001</v>
       </c>
       <c r="N49">
-        <v>1.683483743</v>
+        <v>1.638889584</v>
       </c>
       <c r="O49">
-        <v>0.42087093575</v>
+        <v>0.4097223959999999</v>
       </c>
       <c r="P49">
-        <v>1.26261280725</v>
+        <v>1.229167188</v>
       </c>
       <c r="Q49">
-        <v>1.26261280725</v>
+        <v>1.229167188</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1131662779090427</v>
+        <v>0.1142672739524461</v>
       </c>
       <c r="T49">
-        <v>0.9802614268897187</v>
+        <v>0.996282260844116</v>
       </c>
       <c r="U49">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.56426817317945</v>
+        <v>3.337562738477415</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.082494982455272</v>
+        <v>0.08241658761875131</v>
       </c>
       <c r="C50">
-        <v>13.02755503162389</v>
+        <v>12.82516170289597</v>
       </c>
       <c r="D50">
-        <v>23.95231503162389</v>
+        <v>23.97779170289596</v>
       </c>
       <c r="E50">
-        <v>10.15076</v>
+        <v>10.37863</v>
       </c>
       <c r="F50">
-        <v>10.93776</v>
+        <v>11.16563</v>
       </c>
       <c r="G50">
         <v>0.013</v>
@@ -5369,28 +5369,28 @@
         <v>2.34</v>
       </c>
       <c r="M50">
-        <v>0.701110416</v>
+        <v>0.715716883</v>
       </c>
       <c r="N50">
-        <v>1.638889584</v>
+        <v>1.624283117</v>
       </c>
       <c r="O50">
-        <v>0.4097223959999999</v>
+        <v>0.40607077925</v>
       </c>
       <c r="P50">
-        <v>1.229167188</v>
+        <v>1.21821233775</v>
       </c>
       <c r="Q50">
-        <v>1.229167188</v>
+        <v>1.21821233775</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1142672739524461</v>
+        <v>0.1154114463112771</v>
       </c>
       <c r="T50">
-        <v>0.996282260844116</v>
+        <v>1.012931362796725</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.337562738477415</v>
+        <v>3.269449213202366</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08241658761875131</v>
+        <v>0.08233819278223066</v>
       </c>
       <c r="C51">
-        <v>12.82516170289597</v>
+        <v>12.62282262795362</v>
       </c>
       <c r="D51">
-        <v>23.97779170289596</v>
+        <v>24.00332262795362</v>
       </c>
       <c r="E51">
-        <v>10.37863</v>
+        <v>10.6065</v>
       </c>
       <c r="F51">
-        <v>11.16563</v>
+        <v>11.3935</v>
       </c>
       <c r="G51">
         <v>0.013</v>
@@ -5451,28 +5451,28 @@
         <v>2.34</v>
       </c>
       <c r="M51">
-        <v>0.715716883</v>
+        <v>0.73032335</v>
       </c>
       <c r="N51">
-        <v>1.624283117</v>
+        <v>1.60967665</v>
       </c>
       <c r="O51">
-        <v>0.40607077925</v>
+        <v>0.4024191625</v>
       </c>
       <c r="P51">
-        <v>1.21821233775</v>
+        <v>1.2072574875</v>
       </c>
       <c r="Q51">
-        <v>1.21821233775</v>
+        <v>1.2072574875</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1154114463112771</v>
+        <v>0.1166013855644613</v>
       </c>
       <c r="T51">
-        <v>1.012931362796725</v>
+        <v>1.030246428827438</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.269449213202366</v>
+        <v>3.204060228938319</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08233819278223066</v>
+        <v>0.08225979794571002</v>
       </c>
       <c r="C52">
-        <v>12.62282262795362</v>
+        <v>12.42053798028562</v>
       </c>
       <c r="D52">
-        <v>24.00332262795362</v>
+        <v>24.02890798028562</v>
       </c>
       <c r="E52">
-        <v>10.6065</v>
+        <v>10.83437</v>
       </c>
       <c r="F52">
-        <v>11.3935</v>
+        <v>11.62137</v>
       </c>
       <c r="G52">
         <v>0.013</v>
@@ -5533,28 +5533,28 @@
         <v>2.34</v>
       </c>
       <c r="M52">
-        <v>0.73032335</v>
+        <v>0.7449298169999999</v>
       </c>
       <c r="N52">
-        <v>1.60967665</v>
+        <v>1.595070183</v>
       </c>
       <c r="O52">
-        <v>0.4024191625</v>
+        <v>0.39876754575</v>
       </c>
       <c r="P52">
-        <v>1.2072574875</v>
+        <v>1.19630263725</v>
       </c>
       <c r="Q52">
-        <v>1.2072574875</v>
+        <v>1.19630263725</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1166013855644613</v>
+        <v>0.1178398937667551</v>
       </c>
       <c r="T52">
-        <v>1.030246428827438</v>
+        <v>1.04826823224716</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.204060228938319</v>
+        <v>3.141235518566979</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08225979794571002</v>
+        <v>0.08218140310918935</v>
       </c>
       <c r="C53">
-        <v>12.42053798028562</v>
+        <v>12.21830793412122</v>
       </c>
       <c r="D53">
-        <v>24.02890798028562</v>
+        <v>24.05454793412121</v>
       </c>
       <c r="E53">
-        <v>10.83437</v>
+        <v>11.06224</v>
       </c>
       <c r="F53">
-        <v>11.62137</v>
+        <v>11.84924</v>
       </c>
       <c r="G53">
         <v>0.013</v>
@@ -5615,28 +5615,28 @@
         <v>2.34</v>
       </c>
       <c r="M53">
-        <v>0.7449298169999999</v>
+        <v>0.7595362840000001</v>
       </c>
       <c r="N53">
-        <v>1.595070183</v>
+        <v>1.580463716</v>
       </c>
       <c r="O53">
-        <v>0.39876754575</v>
+        <v>0.3951159289999999</v>
       </c>
       <c r="P53">
-        <v>1.19630263725</v>
+        <v>1.185347787</v>
       </c>
       <c r="Q53">
-        <v>1.19630263725</v>
+        <v>1.185347787</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1178398937667551</v>
+        <v>0.1191300064774778</v>
       </c>
       <c r="T53">
-        <v>1.04826823224716</v>
+        <v>1.067040944142704</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.141235518566979</v>
+        <v>3.080827143209921</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08218140310918935</v>
+        <v>0.0821030082726687</v>
       </c>
       <c r="C54">
-        <v>12.21830793412122</v>
+        <v>12.01613266443407</v>
       </c>
       <c r="D54">
-        <v>24.05454793412121</v>
+        <v>24.08024266443407</v>
       </c>
       <c r="E54">
-        <v>11.06224</v>
+        <v>11.29011</v>
       </c>
       <c r="F54">
-        <v>11.84924</v>
+        <v>12.07711</v>
       </c>
       <c r="G54">
         <v>0.013</v>
@@ -5697,28 +5697,28 @@
         <v>2.34</v>
       </c>
       <c r="M54">
-        <v>0.7595362840000001</v>
+        <v>0.774142751</v>
       </c>
       <c r="N54">
-        <v>1.580463716</v>
+        <v>1.565857249</v>
       </c>
       <c r="O54">
-        <v>0.3951159289999999</v>
+        <v>0.39146431225</v>
       </c>
       <c r="P54">
-        <v>1.185347787</v>
+        <v>1.17439293675</v>
       </c>
       <c r="Q54">
-        <v>1.185347787</v>
+        <v>1.17439293675</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1191300064774778</v>
+        <v>0.1204750176014228</v>
       </c>
       <c r="T54">
-        <v>1.067040944142704</v>
+        <v>1.086612494842313</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.080827143209921</v>
+        <v>3.022698329187093</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0821030082726687</v>
+        <v>0.08518361343614803</v>
       </c>
       <c r="C55">
-        <v>12.01613266443407</v>
+        <v>10.81820218061629</v>
       </c>
       <c r="D55">
-        <v>24.08024266443407</v>
+        <v>23.11018218061629</v>
       </c>
       <c r="E55">
-        <v>11.29011</v>
+        <v>11.51798</v>
       </c>
       <c r="F55">
-        <v>12.07711</v>
+        <v>12.30498</v>
       </c>
       <c r="G55">
         <v>0.013</v>
@@ -5779,45 +5779,45 @@
         <v>2.34</v>
       </c>
       <c r="M55">
-        <v>0.774142751</v>
+        <v>0.8847280620000001</v>
       </c>
       <c r="N55">
-        <v>1.565857249</v>
+        <v>1.455271938</v>
       </c>
       <c r="O55">
-        <v>0.39146431225</v>
+        <v>0.3638179844999999</v>
       </c>
       <c r="P55">
-        <v>1.17439293675</v>
+        <v>1.0914539535</v>
       </c>
       <c r="Q55">
-        <v>1.17439293675</v>
+        <v>1.0914539535</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1204750176014228</v>
+        <v>0.121878507469887</v>
       </c>
       <c r="T55">
-        <v>1.086612494842313</v>
+        <v>1.107034982528862</v>
       </c>
       <c r="U55">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.022698329187093</v>
+        <v>2.644880501145447</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08518361343614803</v>
+        <v>0.08516371859962737</v>
       </c>
       <c r="C56">
-        <v>10.81820218061629</v>
+        <v>10.5963461146575</v>
       </c>
       <c r="D56">
-        <v>23.11018218061629</v>
+        <v>23.11619611465749</v>
       </c>
       <c r="E56">
-        <v>11.51798</v>
+        <v>11.74585</v>
       </c>
       <c r="F56">
-        <v>12.30498</v>
+        <v>12.53285</v>
       </c>
       <c r="G56">
         <v>0.013</v>
@@ -5861,28 +5861,28 @@
         <v>2.34</v>
       </c>
       <c r="M56">
-        <v>0.8847280620000001</v>
+        <v>0.9011119150000001</v>
       </c>
       <c r="N56">
-        <v>1.455271938</v>
+        <v>1.438888085</v>
       </c>
       <c r="O56">
-        <v>0.3638179844999999</v>
+        <v>0.35972202125</v>
       </c>
       <c r="P56">
-        <v>1.0914539535</v>
+        <v>1.07916606375</v>
       </c>
       <c r="Q56">
-        <v>1.0914539535</v>
+        <v>1.07916606375</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.121878507469887</v>
+        <v>0.1233443746658386</v>
       </c>
       <c r="T56">
-        <v>1.107034982528862</v>
+        <v>1.128365136334813</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.644880501145447</v>
+        <v>2.596791764760984</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08516371859962737</v>
+        <v>0.0851438237631067</v>
       </c>
       <c r="C57">
-        <v>10.5963461146575</v>
+        <v>10.37449317951062</v>
       </c>
       <c r="D57">
-        <v>23.11619611465749</v>
+        <v>23.12221317951062</v>
       </c>
       <c r="E57">
-        <v>11.74585</v>
+        <v>11.97372</v>
       </c>
       <c r="F57">
-        <v>12.53285</v>
+        <v>12.76072</v>
       </c>
       <c r="G57">
         <v>0.013</v>
@@ -5943,28 +5943,28 @@
         <v>2.34</v>
       </c>
       <c r="M57">
-        <v>0.9011119150000001</v>
+        <v>0.9174957680000001</v>
       </c>
       <c r="N57">
-        <v>1.438888085</v>
+        <v>1.422504232</v>
       </c>
       <c r="O57">
-        <v>0.35972202125</v>
+        <v>0.3556260579999999</v>
       </c>
       <c r="P57">
-        <v>1.07916606375</v>
+        <v>1.066878174</v>
       </c>
       <c r="Q57">
-        <v>1.07916606375</v>
+        <v>1.066878174</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1233443746658386</v>
+        <v>0.1248768721888789</v>
       </c>
       <c r="T57">
-        <v>1.128365136334813</v>
+        <v>1.150664842586489</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.596791764760984</v>
+        <v>2.550420483247395</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0851438237631067</v>
+        <v>0.08512392892658606</v>
       </c>
       <c r="C58">
-        <v>10.37449317951062</v>
+        <v>10.15264337762112</v>
       </c>
       <c r="D58">
-        <v>23.12221317951062</v>
+        <v>23.12823337762112</v>
       </c>
       <c r="E58">
-        <v>11.97372</v>
+        <v>12.20159</v>
       </c>
       <c r="F58">
-        <v>12.76072</v>
+        <v>12.98859</v>
       </c>
       <c r="G58">
         <v>0.013</v>
@@ -6025,28 +6025,28 @@
         <v>2.34</v>
       </c>
       <c r="M58">
-        <v>0.9174957680000001</v>
+        <v>0.9338796210000001</v>
       </c>
       <c r="N58">
-        <v>1.422504232</v>
+        <v>1.406120379</v>
       </c>
       <c r="O58">
-        <v>0.3556260579999999</v>
+        <v>0.35153009475</v>
       </c>
       <c r="P58">
-        <v>1.066878174</v>
+        <v>1.05459028425</v>
       </c>
       <c r="Q58">
-        <v>1.066878174</v>
+        <v>1.05459028425</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1248768721888789</v>
+        <v>0.1264806486664792</v>
       </c>
       <c r="T58">
-        <v>1.150664842586489</v>
+        <v>1.174001744477778</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.550420483247395</v>
+        <v>2.505676264243054</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08512392892658606</v>
+        <v>0.0868005340900654</v>
       </c>
       <c r="C59">
-        <v>10.15264337762112</v>
+        <v>9.428194647028736</v>
       </c>
       <c r="D59">
-        <v>23.12823337762112</v>
+        <v>22.63165464702874</v>
       </c>
       <c r="E59">
-        <v>12.20159</v>
+        <v>12.42946</v>
       </c>
       <c r="F59">
-        <v>12.98859</v>
+        <v>13.21646</v>
       </c>
       <c r="G59">
         <v>0.013</v>
@@ -6107,45 +6107,45 @@
         <v>2.34</v>
       </c>
       <c r="M59">
-        <v>0.9338796210000001</v>
+        <v>1.001807668</v>
       </c>
       <c r="N59">
-        <v>1.406120379</v>
+        <v>1.338192332</v>
       </c>
       <c r="O59">
-        <v>0.35153009475</v>
+        <v>0.3345480829999999</v>
       </c>
       <c r="P59">
-        <v>1.05459028425</v>
+        <v>1.003644249</v>
       </c>
       <c r="Q59">
-        <v>1.05459028425</v>
+        <v>1.003644249</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1264806486664792</v>
+        <v>0.1281607954525367</v>
       </c>
       <c r="T59">
-        <v>1.174001744477778</v>
+        <v>1.19844992741151</v>
       </c>
       <c r="U59">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.505676264243054</v>
+        <v>2.335777689415729</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0868005340900654</v>
+        <v>0.08680988925354474</v>
       </c>
       <c r="C60">
-        <v>9.428194647028739</v>
+        <v>9.197613640799117</v>
       </c>
       <c r="D60">
-        <v>22.63165464702874</v>
+        <v>22.62894364079911</v>
       </c>
       <c r="E60">
-        <v>12.42946</v>
+        <v>12.65733</v>
       </c>
       <c r="F60">
-        <v>13.21646</v>
+        <v>13.44433</v>
       </c>
       <c r="G60">
         <v>0.013</v>
@@ -6189,28 +6189,28 @@
         <v>2.34</v>
       </c>
       <c r="M60">
-        <v>1.001807668</v>
+        <v>1.019080214</v>
       </c>
       <c r="N60">
-        <v>1.338192332</v>
+        <v>1.320919786</v>
       </c>
       <c r="O60">
-        <v>0.334548083</v>
+        <v>0.3302299465</v>
       </c>
       <c r="P60">
-        <v>1.003644249</v>
+        <v>0.9906898394999999</v>
       </c>
       <c r="Q60">
-        <v>1.003644249</v>
+        <v>0.9906898394999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1281607954525366</v>
+        <v>0.1299229006184018</v>
       </c>
       <c r="T60">
-        <v>1.198449927411509</v>
+        <v>1.224090704634691</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.335777689415729</v>
+        <v>2.296188237052751</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08680988925354474</v>
+        <v>0.08681924441702409</v>
       </c>
       <c r="C61">
-        <v>9.197613640799117</v>
+        <v>8.967033283985069</v>
       </c>
       <c r="D61">
-        <v>22.62894364079911</v>
+        <v>22.62623328398507</v>
       </c>
       <c r="E61">
-        <v>12.65733</v>
+        <v>12.8852</v>
       </c>
       <c r="F61">
-        <v>13.44433</v>
+        <v>13.6722</v>
       </c>
       <c r="G61">
         <v>0.013</v>
@@ -6271,28 +6271,28 @@
         <v>2.34</v>
       </c>
       <c r="M61">
-        <v>1.019080214</v>
+        <v>1.03635276</v>
       </c>
       <c r="N61">
-        <v>1.320919786</v>
+        <v>1.30364724</v>
       </c>
       <c r="O61">
-        <v>0.3302299465</v>
+        <v>0.32591181</v>
       </c>
       <c r="P61">
-        <v>0.9906898394999999</v>
+        <v>0.9777354299999998</v>
       </c>
       <c r="Q61">
-        <v>0.9906898394999999</v>
+        <v>0.9777354299999998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1299229006184018</v>
+        <v>0.1317731110425602</v>
       </c>
       <c r="T61">
-        <v>1.224090704634691</v>
+        <v>1.251013520719032</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.296188237052751</v>
+        <v>2.257918433101872</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08681924441702409</v>
+        <v>0.08682859958050343</v>
       </c>
       <c r="C62">
-        <v>8.967033283985069</v>
+        <v>8.736453576353274</v>
       </c>
       <c r="D62">
-        <v>22.62623328398507</v>
+        <v>22.62352357635327</v>
       </c>
       <c r="E62">
-        <v>12.8852</v>
+        <v>13.11307</v>
       </c>
       <c r="F62">
-        <v>13.6722</v>
+        <v>13.90007</v>
       </c>
       <c r="G62">
         <v>0.013</v>
@@ -6353,28 +6353,28 @@
         <v>2.34</v>
       </c>
       <c r="M62">
-        <v>1.03635276</v>
+        <v>1.053625306</v>
       </c>
       <c r="N62">
-        <v>1.30364724</v>
+        <v>1.286374694</v>
       </c>
       <c r="O62">
-        <v>0.32591181</v>
+        <v>0.3215936735</v>
       </c>
       <c r="P62">
-        <v>0.9777354299999998</v>
+        <v>0.9647810204999998</v>
       </c>
       <c r="Q62">
-        <v>0.9777354299999998</v>
+        <v>0.9647810204999998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1317731110425602</v>
+        <v>0.1337182040525729</v>
       </c>
       <c r="T62">
-        <v>1.251013520719032</v>
+        <v>1.279316994038467</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.257918433101872</v>
+        <v>2.220903376821513</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08682859958050343</v>
+        <v>0.08683795474398276</v>
       </c>
       <c r="C63">
-        <v>8.736453576353274</v>
+        <v>8.505874517670527</v>
       </c>
       <c r="D63">
-        <v>22.62352357635327</v>
+        <v>22.62081451767052</v>
       </c>
       <c r="E63">
-        <v>13.11307</v>
+        <v>13.34094</v>
       </c>
       <c r="F63">
-        <v>13.90007</v>
+        <v>14.12794</v>
       </c>
       <c r="G63">
         <v>0.013</v>
@@ -6435,28 +6435,28 @@
         <v>2.34</v>
       </c>
       <c r="M63">
-        <v>1.053625306</v>
+        <v>1.070897852</v>
       </c>
       <c r="N63">
-        <v>1.286374694</v>
+        <v>1.269102148</v>
       </c>
       <c r="O63">
-        <v>0.3215936735</v>
+        <v>0.3172755369999999</v>
       </c>
       <c r="P63">
-        <v>0.9647810204999998</v>
+        <v>0.9518266109999998</v>
       </c>
       <c r="Q63">
-        <v>0.9647810204999998</v>
+        <v>0.9518266109999998</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1337182040525729</v>
+        <v>0.135765670378902</v>
       </c>
       <c r="T63">
-        <v>1.279316994038467</v>
+        <v>1.309110123848399</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.220903376821513</v>
+        <v>2.185082354614714</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08683795474398276</v>
+        <v>0.08684730990746209</v>
       </c>
       <c r="C64">
-        <v>8.505874517670527</v>
+        <v>8.275296107703726</v>
       </c>
       <c r="D64">
-        <v>22.62081451767052</v>
+        <v>22.61810610770372</v>
       </c>
       <c r="E64">
-        <v>13.34094</v>
+        <v>13.56881</v>
       </c>
       <c r="F64">
-        <v>14.12794</v>
+        <v>14.35581</v>
       </c>
       <c r="G64">
         <v>0.013</v>
@@ -6517,28 +6517,28 @@
         <v>2.34</v>
       </c>
       <c r="M64">
-        <v>1.070897852</v>
+        <v>1.088170398</v>
       </c>
       <c r="N64">
-        <v>1.269102148</v>
+        <v>1.251829602</v>
       </c>
       <c r="O64">
-        <v>0.3172755369999999</v>
+        <v>0.3129574004999999</v>
       </c>
       <c r="P64">
-        <v>0.9518266109999998</v>
+        <v>0.9388722014999997</v>
       </c>
       <c r="Q64">
-        <v>0.9518266109999998</v>
+        <v>0.9388722014999997</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.135765670378902</v>
+        <v>0.1379238105607084</v>
       </c>
       <c r="T64">
-        <v>1.309110123848399</v>
+        <v>1.340513693107516</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.185082354614714</v>
+        <v>2.150398507716067</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08684730990746209</v>
+        <v>0.08685666507094145</v>
       </c>
       <c r="C65">
-        <v>8.275296107703726</v>
+        <v>8.044718346219872</v>
       </c>
       <c r="D65">
-        <v>22.61810610770372</v>
+        <v>22.61539834621987</v>
       </c>
       <c r="E65">
-        <v>13.56881</v>
+        <v>13.79668</v>
       </c>
       <c r="F65">
-        <v>14.35581</v>
+        <v>14.58368</v>
       </c>
       <c r="G65">
         <v>0.013</v>
@@ -6599,28 +6599,28 @@
         <v>2.34</v>
       </c>
       <c r="M65">
-        <v>1.088170398</v>
+        <v>1.105442944</v>
       </c>
       <c r="N65">
-        <v>1.251829602</v>
+        <v>1.234557056</v>
       </c>
       <c r="O65">
-        <v>0.3129574004999999</v>
+        <v>0.308639264</v>
       </c>
       <c r="P65">
-        <v>0.9388722014999997</v>
+        <v>0.9259177919999999</v>
       </c>
       <c r="Q65">
-        <v>0.9388722014999997</v>
+        <v>0.9259177919999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1379238105607084</v>
+        <v>0.1402018474192818</v>
       </c>
       <c r="T65">
-        <v>1.340513693107516</v>
+        <v>1.373661905103251</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.150398507716067</v>
+        <v>2.116798531033004</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08685666507094145</v>
+        <v>0.08686602023442078</v>
       </c>
       <c r="C66">
-        <v>8.044718346219872</v>
+        <v>7.814141232986113</v>
       </c>
       <c r="D66">
-        <v>22.61539834621987</v>
+        <v>22.61269123298611</v>
       </c>
       <c r="E66">
-        <v>13.79668</v>
+        <v>14.02455</v>
       </c>
       <c r="F66">
-        <v>14.58368</v>
+        <v>14.81155</v>
       </c>
       <c r="G66">
         <v>0.013</v>
@@ -6681,28 +6681,28 @@
         <v>2.34</v>
       </c>
       <c r="M66">
-        <v>1.105442944</v>
+        <v>1.12271549</v>
       </c>
       <c r="N66">
-        <v>1.234557056</v>
+        <v>1.21728451</v>
       </c>
       <c r="O66">
-        <v>0.308639264</v>
+        <v>0.3043211275</v>
       </c>
       <c r="P66">
-        <v>0.9259177919999999</v>
+        <v>0.9129633824999999</v>
       </c>
       <c r="Q66">
-        <v>0.9259177919999999</v>
+        <v>0.9129633824999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1402018474192818</v>
+        <v>0.1426100578126308</v>
       </c>
       <c r="T66">
-        <v>1.373661905103251</v>
+        <v>1.408704300641599</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.116798531033004</v>
+        <v>2.084232399786343</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08686602023442078</v>
+        <v>0.08687537539790013</v>
       </c>
       <c r="C67">
-        <v>7.814141232986113</v>
+        <v>7.583564767769673</v>
       </c>
       <c r="D67">
-        <v>22.61269123298611</v>
+        <v>22.60998476776967</v>
       </c>
       <c r="E67">
-        <v>14.02455</v>
+        <v>14.25242</v>
       </c>
       <c r="F67">
-        <v>14.81155</v>
+        <v>15.03942</v>
       </c>
       <c r="G67">
         <v>0.013</v>
@@ -6763,28 +6763,28 @@
         <v>2.34</v>
       </c>
       <c r="M67">
-        <v>1.12271549</v>
+        <v>1.139988036</v>
       </c>
       <c r="N67">
-        <v>1.21728451</v>
+        <v>1.200011964</v>
       </c>
       <c r="O67">
-        <v>0.3043211275</v>
+        <v>0.3000029909999999</v>
       </c>
       <c r="P67">
-        <v>0.9129633824999999</v>
+        <v>0.9000089729999998</v>
       </c>
       <c r="Q67">
-        <v>0.9129633824999999</v>
+        <v>0.9000089729999998</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1426100578126308</v>
+        <v>0.1451599276408827</v>
       </c>
       <c r="T67">
-        <v>1.408704300641599</v>
+        <v>1.445808013564556</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.084232399786343</v>
+        <v>2.052653121001701</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08687537539790013</v>
+        <v>0.08688473056137946</v>
       </c>
       <c r="C68">
-        <v>7.583564767769673</v>
+        <v>7.352988950337901</v>
       </c>
       <c r="D68">
-        <v>22.60998476776967</v>
+        <v>22.6072789503379</v>
       </c>
       <c r="E68">
-        <v>14.25242</v>
+        <v>14.48029</v>
       </c>
       <c r="F68">
-        <v>15.03942</v>
+        <v>15.26729</v>
       </c>
       <c r="G68">
         <v>0.013</v>
@@ -6845,28 +6845,28 @@
         <v>2.34</v>
       </c>
       <c r="M68">
-        <v>1.139988036</v>
+        <v>1.157260582</v>
       </c>
       <c r="N68">
-        <v>1.200011964</v>
+        <v>1.182739418</v>
       </c>
       <c r="O68">
-        <v>0.3000029909999999</v>
+        <v>0.2956848544999999</v>
       </c>
       <c r="P68">
-        <v>0.9000089729999998</v>
+        <v>0.8870545634999998</v>
       </c>
       <c r="Q68">
-        <v>0.9000089729999998</v>
+        <v>0.8870545634999998</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1451599276408827</v>
+        <v>0.1478643350344832</v>
       </c>
       <c r="T68">
-        <v>1.445808013564556</v>
+        <v>1.485160436361632</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.052653121001701</v>
+        <v>2.022016507255407</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08688473056137946</v>
+        <v>0.09413608572485881</v>
       </c>
       <c r="C69">
-        <v>7.352988950337901</v>
+        <v>5.206056657863742</v>
       </c>
       <c r="D69">
-        <v>22.6072789503379</v>
+        <v>20.68821665786374</v>
       </c>
       <c r="E69">
-        <v>14.48029</v>
+        <v>14.70816</v>
       </c>
       <c r="F69">
-        <v>15.26729</v>
+        <v>15.49516</v>
       </c>
       <c r="G69">
         <v>0.013</v>
@@ -6927,45 +6927,45 @@
         <v>2.34</v>
       </c>
       <c r="M69">
-        <v>1.157260582</v>
+        <v>1.3945644</v>
       </c>
       <c r="N69">
-        <v>1.182739418</v>
+        <v>0.9454355999999999</v>
       </c>
       <c r="O69">
-        <v>0.2956848544999999</v>
+        <v>0.2363589</v>
       </c>
       <c r="P69">
-        <v>0.8870545634999998</v>
+        <v>0.7090767</v>
       </c>
       <c r="Q69">
-        <v>0.8870545634999998</v>
+        <v>0.7090767</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1478643350344832</v>
+        <v>0.1507377678901838</v>
       </c>
       <c r="T69">
-        <v>1.485160436361632</v>
+        <v>1.526972385583525</v>
       </c>
       <c r="U69">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V69">
         <v>0.25</v>
       </c>
       <c r="W69">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.022016507255407</v>
+        <v>1.677943306167861</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09413608572485881</v>
+        <v>0.09425194088833815</v>
       </c>
       <c r="C70">
-        <v>5.206056657863742</v>
+        <v>4.950166444169199</v>
       </c>
       <c r="D70">
-        <v>20.68821665786374</v>
+        <v>20.6601964441692</v>
       </c>
       <c r="E70">
-        <v>14.70816</v>
+        <v>14.93603</v>
       </c>
       <c r="F70">
-        <v>15.49516</v>
+        <v>15.72303</v>
       </c>
       <c r="G70">
         <v>0.013</v>
@@ -7009,28 +7009,28 @@
         <v>2.34</v>
       </c>
       <c r="M70">
-        <v>1.3945644</v>
+        <v>1.4150727</v>
       </c>
       <c r="N70">
-        <v>0.9454355999999999</v>
+        <v>0.9249272999999998</v>
       </c>
       <c r="O70">
-        <v>0.2363589</v>
+        <v>0.2312318249999999</v>
       </c>
       <c r="P70">
-        <v>0.7090767</v>
+        <v>0.6936954749999998</v>
       </c>
       <c r="Q70">
-        <v>0.7090767</v>
+        <v>0.6936954749999998</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1507377678901838</v>
+        <v>0.1537965835107682</v>
       </c>
       <c r="T70">
-        <v>1.526972385583525</v>
+        <v>1.571481879916507</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.677943306167861</v>
+        <v>1.653625287237892</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09425194088833815</v>
+        <v>0.0943677960518175</v>
       </c>
       <c r="C71">
-        <v>4.950166444169199</v>
+        <v>4.694352029219417</v>
       </c>
       <c r="D71">
-        <v>20.6601964441692</v>
+        <v>20.63225202921942</v>
       </c>
       <c r="E71">
-        <v>14.93603</v>
+        <v>15.1639</v>
       </c>
       <c r="F71">
-        <v>15.72303</v>
+        <v>15.9509</v>
       </c>
       <c r="G71">
         <v>0.013</v>
@@ -7091,28 +7091,28 @@
         <v>2.34</v>
       </c>
       <c r="M71">
-        <v>1.4150727</v>
+        <v>1.435581</v>
       </c>
       <c r="N71">
-        <v>0.9249272999999998</v>
+        <v>0.9044189999999999</v>
       </c>
       <c r="O71">
-        <v>0.2312318249999999</v>
+        <v>0.22610475</v>
       </c>
       <c r="P71">
-        <v>0.6936954749999998</v>
+        <v>0.6783142499999999</v>
       </c>
       <c r="Q71">
-        <v>0.6936954749999998</v>
+        <v>0.6783142499999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1537965835107682</v>
+        <v>0.157059320172725</v>
       </c>
       <c r="T71">
-        <v>1.571481879916507</v>
+        <v>1.618958673871689</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.653625287237892</v>
+        <v>1.63000206884878</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0943677960518175</v>
+        <v>0.09448365121529684</v>
       </c>
       <c r="C72">
-        <v>4.694352029219417</v>
+        <v>4.438613105859933</v>
       </c>
       <c r="D72">
-        <v>20.63225202921942</v>
+        <v>20.60438310585993</v>
       </c>
       <c r="E72">
-        <v>15.1639</v>
+        <v>15.39177</v>
       </c>
       <c r="F72">
-        <v>15.9509</v>
+        <v>16.17877</v>
       </c>
       <c r="G72">
         <v>0.013</v>
@@ -7173,28 +7173,28 @@
         <v>2.34</v>
       </c>
       <c r="M72">
-        <v>1.435581</v>
+        <v>1.4560893</v>
       </c>
       <c r="N72">
-        <v>0.9044189999999999</v>
+        <v>0.8839106999999999</v>
       </c>
       <c r="O72">
-        <v>0.22610475</v>
+        <v>0.220977675</v>
       </c>
       <c r="P72">
-        <v>0.6783142499999999</v>
+        <v>0.662933025</v>
       </c>
       <c r="Q72">
-        <v>0.6783142499999999</v>
+        <v>0.662933025</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.157059320172725</v>
+        <v>0.160547073156196</v>
       </c>
       <c r="T72">
-        <v>1.618958673871689</v>
+        <v>1.669709729478952</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.63000206884878</v>
+        <v>1.607044293231191</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09448365121529684</v>
+        <v>0.09459950637877618</v>
       </c>
       <c r="C73">
-        <v>4.438613105859933</v>
+        <v>4.182949368593597</v>
       </c>
       <c r="D73">
-        <v>20.60438310585993</v>
+        <v>20.57658936859359</v>
       </c>
       <c r="E73">
-        <v>15.39177</v>
+        <v>15.61964</v>
       </c>
       <c r="F73">
-        <v>16.17877</v>
+        <v>16.40664</v>
       </c>
       <c r="G73">
         <v>0.013</v>
@@ -7255,28 +7255,28 @@
         <v>2.34</v>
       </c>
       <c r="M73">
-        <v>1.4560893</v>
+        <v>1.4765976</v>
       </c>
       <c r="N73">
-        <v>0.8839106999999999</v>
+        <v>0.8634024</v>
       </c>
       <c r="O73">
-        <v>0.220977675</v>
+        <v>0.2158506</v>
       </c>
       <c r="P73">
-        <v>0.662933025</v>
+        <v>0.6475518</v>
       </c>
       <c r="Q73">
-        <v>0.662933025</v>
+        <v>0.6475518</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.160547073156196</v>
+        <v>0.164283951352772</v>
       </c>
       <c r="T73">
-        <v>1.669709729478951</v>
+        <v>1.724085860486733</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.607044293231191</v>
+        <v>1.58472423360298</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09459950637877618</v>
+        <v>0.09471536154225552</v>
       </c>
       <c r="C74">
-        <v>4.182949368593597</v>
+        <v>3.927360513569415</v>
       </c>
       <c r="D74">
-        <v>20.57658936859359</v>
+        <v>20.54887051356941</v>
       </c>
       <c r="E74">
-        <v>15.61964</v>
+        <v>15.84751</v>
       </c>
       <c r="F74">
-        <v>16.40664</v>
+        <v>16.63451</v>
       </c>
       <c r="G74">
         <v>0.013</v>
@@ -7337,28 +7337,28 @@
         <v>2.34</v>
       </c>
       <c r="M74">
-        <v>1.4765976</v>
+        <v>1.4971059</v>
       </c>
       <c r="N74">
-        <v>0.8634024</v>
+        <v>0.8428941000000001</v>
       </c>
       <c r="O74">
-        <v>0.2158506</v>
+        <v>0.210723525</v>
       </c>
       <c r="P74">
-        <v>0.6475518</v>
+        <v>0.6321705750000001</v>
       </c>
       <c r="Q74">
-        <v>0.6475518</v>
+        <v>0.6321705750000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.164283951352772</v>
+        <v>0.1682976353416871</v>
       </c>
       <c r="T74">
-        <v>1.724085860486733</v>
+        <v>1.782489853050647</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.58472423360298</v>
+        <v>1.563015682457734</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09471536154225552</v>
+        <v>0.09483121670573486</v>
       </c>
       <c r="C75">
-        <v>3.927360513569415</v>
+        <v>3.671846238571458</v>
       </c>
       <c r="D75">
-        <v>20.54887051356941</v>
+        <v>20.52122623857145</v>
       </c>
       <c r="E75">
-        <v>15.84751</v>
+        <v>16.07538</v>
       </c>
       <c r="F75">
-        <v>16.63451</v>
+        <v>16.86238</v>
       </c>
       <c r="G75">
         <v>0.013</v>
@@ -7419,28 +7419,28 @@
         <v>2.34</v>
       </c>
       <c r="M75">
-        <v>1.4971059</v>
+        <v>1.5176142</v>
       </c>
       <c r="N75">
-        <v>0.8428941000000001</v>
+        <v>0.8223858000000002</v>
       </c>
       <c r="O75">
-        <v>0.210723525</v>
+        <v>0.20559645</v>
       </c>
       <c r="P75">
-        <v>0.6321705750000001</v>
+        <v>0.6167893500000001</v>
       </c>
       <c r="Q75">
-        <v>0.6321705750000001</v>
+        <v>0.6167893500000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1682976353416871</v>
+        <v>0.1726200642528263</v>
       </c>
       <c r="T75">
-        <v>1.782489853050647</v>
+        <v>1.845386460427169</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.563015682457734</v>
+        <v>1.541893848911008</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09483121670573486</v>
+        <v>0.09494707186921419</v>
       </c>
       <c r="C76">
-        <v>3.671846238571458</v>
+        <v>3.416406243007902</v>
       </c>
       <c r="D76">
-        <v>20.52122623857145</v>
+        <v>20.4936562430079</v>
       </c>
       <c r="E76">
-        <v>16.07538</v>
+        <v>16.30325</v>
       </c>
       <c r="F76">
-        <v>16.86238</v>
+        <v>17.09025</v>
       </c>
       <c r="G76">
         <v>0.013</v>
@@ -7501,28 +7501,28 @@
         <v>2.34</v>
       </c>
       <c r="M76">
-        <v>1.5176142</v>
+        <v>1.5381225</v>
       </c>
       <c r="N76">
-        <v>0.8223858000000002</v>
+        <v>0.8018775000000002</v>
       </c>
       <c r="O76">
-        <v>0.20559645</v>
+        <v>0.2004693750000001</v>
       </c>
       <c r="P76">
-        <v>0.6167893500000001</v>
+        <v>0.6014081250000002</v>
       </c>
       <c r="Q76">
-        <v>0.6167893500000001</v>
+        <v>0.6014081250000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1726200642528263</v>
+        <v>0.1772882874768568</v>
       </c>
       <c r="T76">
-        <v>1.845386460427169</v>
+        <v>1.913314796393814</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.541893848911008</v>
+        <v>1.521335264258861</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09494707186921419</v>
+        <v>0.09506292703269353</v>
       </c>
       <c r="C77">
-        <v>3.416406243007902</v>
+        <v>3.161040227900099</v>
       </c>
       <c r="D77">
-        <v>20.4936562430079</v>
+        <v>20.4661602279001</v>
       </c>
       <c r="E77">
-        <v>16.30325</v>
+        <v>16.53112</v>
       </c>
       <c r="F77">
-        <v>17.09025</v>
+        <v>17.31812</v>
       </c>
       <c r="G77">
         <v>0.013</v>
@@ -7583,28 +7583,28 @@
         <v>2.34</v>
       </c>
       <c r="M77">
-        <v>1.5381225</v>
+        <v>1.5586308</v>
       </c>
       <c r="N77">
-        <v>0.8018775000000002</v>
+        <v>0.7813691999999999</v>
       </c>
       <c r="O77">
-        <v>0.2004693750000001</v>
+        <v>0.1953423</v>
       </c>
       <c r="P77">
-        <v>0.6014081250000002</v>
+        <v>0.5860268999999999</v>
       </c>
       <c r="Q77">
-        <v>0.6014081250000002</v>
+        <v>0.5860268999999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1772882874768568</v>
+        <v>0.1823455293028897</v>
       </c>
       <c r="T77">
-        <v>1.913314796393814</v>
+        <v>1.986903827024345</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.521335264258861</v>
+        <v>1.501317694992297</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09506292703269353</v>
+        <v>0.1312800774698975</v>
       </c>
       <c r="C78">
-        <v>3.161040227900099</v>
+        <v>-3.11431235081745</v>
       </c>
       <c r="D78">
-        <v>20.4661602279001</v>
+        <v>14.41867764918255</v>
       </c>
       <c r="E78">
-        <v>16.53112</v>
+        <v>16.75899</v>
       </c>
       <c r="F78">
-        <v>17.31812</v>
+        <v>17.54599</v>
       </c>
       <c r="G78">
         <v>0.013</v>
@@ -7665,45 +7665,45 @@
         <v>2.34</v>
       </c>
       <c r="M78">
-        <v>1.5586308</v>
+        <v>2.575751332</v>
       </c>
       <c r="N78">
-        <v>0.7813691999999999</v>
+        <v>-0.2357513320000004</v>
       </c>
       <c r="O78">
-        <v>0.1953423</v>
+        <v>-0.05893783300000011</v>
       </c>
       <c r="P78">
-        <v>0.5860268999999999</v>
+        <v>-0.1768134990000003</v>
       </c>
       <c r="Q78">
-        <v>0.5860268999999999</v>
+        <v>-0.1768134990000003</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1823455293028897</v>
+        <v>0.1909417828446336</v>
       </c>
       <c r="T78">
-        <v>1.986903827024345</v>
+        <v>2.111989790273097</v>
       </c>
       <c r="U78">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.25</v>
+        <v>0.2271181976040224</v>
       </c>
       <c r="W78">
-        <v>0.0675</v>
+        <v>0.1134590485917295</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y78">
-        <v>1.501317694992297</v>
+        <v>0.9084727904160896</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1312800774698975</v>
+        <v>0.1322900774698975</v>
       </c>
       <c r="C79">
-        <v>-3.11431235081745</v>
+        <v>-3.460026144190833</v>
       </c>
       <c r="D79">
-        <v>14.41867764918255</v>
+        <v>14.30083385580917</v>
       </c>
       <c r="E79">
-        <v>16.75899</v>
+        <v>16.98686</v>
       </c>
       <c r="F79">
-        <v>17.54599</v>
+        <v>17.77386</v>
       </c>
       <c r="G79">
         <v>0.013</v>
@@ -7747,37 +7747,37 @@
         <v>2.34</v>
       </c>
       <c r="M79">
-        <v>2.575751332</v>
+        <v>2.609202648</v>
       </c>
       <c r="N79">
-        <v>-0.2357513320000004</v>
+        <v>-0.2692026480000003</v>
       </c>
       <c r="O79">
-        <v>-0.05893783300000011</v>
+        <v>-0.06730066200000007</v>
       </c>
       <c r="P79">
-        <v>-0.1768134990000003</v>
+        <v>-0.2019019860000002</v>
       </c>
       <c r="Q79">
-        <v>-0.1768134990000003</v>
+        <v>-0.2019019860000002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1909417828446336</v>
+        <v>0.1975391366102988</v>
       </c>
       <c r="T79">
-        <v>2.111989790273097</v>
+        <v>2.207989326194601</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2271181976040224</v>
+        <v>0.2242064258398683</v>
       </c>
       <c r="W79">
-        <v>0.1134590485917295</v>
+        <v>0.1138864966867073</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.9084727904160896</v>
+        <v>0.8968257033594731</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1322900774698975</v>
+        <v>0.1333000774698975</v>
       </c>
       <c r="C80">
-        <v>-3.460026144190833</v>
+        <v>-3.803829279682068</v>
       </c>
       <c r="D80">
-        <v>14.30083385580917</v>
+        <v>14.18490072031793</v>
       </c>
       <c r="E80">
-        <v>16.98686</v>
+        <v>17.21473</v>
       </c>
       <c r="F80">
-        <v>17.77386</v>
+        <v>18.00173</v>
       </c>
       <c r="G80">
         <v>0.013</v>
@@ -7829,37 +7829,37 @@
         <v>2.34</v>
       </c>
       <c r="M80">
-        <v>2.609202648</v>
+        <v>2.642653964</v>
       </c>
       <c r="N80">
-        <v>-0.2692026480000003</v>
+        <v>-0.3026539640000001</v>
       </c>
       <c r="O80">
-        <v>-0.06730066200000007</v>
+        <v>-0.07566349100000003</v>
       </c>
       <c r="P80">
-        <v>-0.2019019860000002</v>
+        <v>-0.2269904730000001</v>
       </c>
       <c r="Q80">
-        <v>-0.2019019860000002</v>
+        <v>-0.2269904730000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1975391366102988</v>
+        <v>0.2047648097822178</v>
       </c>
       <c r="T80">
-        <v>2.207989326194601</v>
+        <v>2.313131675061011</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2242064258398683</v>
+        <v>0.2213683698165788</v>
       </c>
       <c r="W80">
-        <v>0.1138864966867073</v>
+        <v>0.1143031233109262</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8968257033594731</v>
+        <v>0.8854734792663153</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1333000774698975</v>
+        <v>0.1343100774698975</v>
       </c>
       <c r="C81">
-        <v>-3.803829279682068</v>
+        <v>-4.145767851237034</v>
       </c>
       <c r="D81">
-        <v>14.18490072031793</v>
+        <v>14.07083214876297</v>
       </c>
       <c r="E81">
-        <v>17.21473</v>
+        <v>17.4426</v>
       </c>
       <c r="F81">
-        <v>18.00173</v>
+        <v>18.2296</v>
       </c>
       <c r="G81">
         <v>0.013</v>
@@ -7911,37 +7911,37 @@
         <v>2.34</v>
       </c>
       <c r="M81">
-        <v>2.642653964</v>
+        <v>2.67610528</v>
       </c>
       <c r="N81">
-        <v>-0.3026539640000001</v>
+        <v>-0.3361052800000004</v>
       </c>
       <c r="O81">
-        <v>-0.07566349100000003</v>
+        <v>-0.0840263200000001</v>
       </c>
       <c r="P81">
-        <v>-0.2269904730000001</v>
+        <v>-0.2520789600000003</v>
       </c>
       <c r="Q81">
-        <v>-0.2269904730000001</v>
+        <v>-0.2520789600000003</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2047648097822178</v>
+        <v>0.2127130502713288</v>
       </c>
       <c r="T81">
-        <v>2.313131675061011</v>
+        <v>2.428788258814062</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2213683698165788</v>
+        <v>0.2186012651938716</v>
       </c>
       <c r="W81">
-        <v>0.1143031233109262</v>
+        <v>0.1147093342695397</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8854734792663153</v>
+        <v>0.8744050607754863</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1343100774698975</v>
+        <v>0.1353200774698975</v>
       </c>
       <c r="C82">
-        <v>-4.145767851237034</v>
+        <v>-4.485886481962554</v>
       </c>
       <c r="D82">
-        <v>14.07083214876297</v>
+        <v>13.95858351803745</v>
       </c>
       <c r="E82">
-        <v>17.4426</v>
+        <v>17.67047</v>
       </c>
       <c r="F82">
-        <v>18.2296</v>
+        <v>18.45747</v>
       </c>
       <c r="G82">
         <v>0.013</v>
@@ -7993,37 +7993,37 @@
         <v>2.34</v>
       </c>
       <c r="M82">
-        <v>2.67610528</v>
+        <v>2.709556596000001</v>
       </c>
       <c r="N82">
-        <v>-0.3361052800000004</v>
+        <v>-0.3695565960000007</v>
       </c>
       <c r="O82">
-        <v>-0.0840263200000001</v>
+        <v>-0.09238914900000017</v>
       </c>
       <c r="P82">
-        <v>-0.2520789600000003</v>
+        <v>-0.2771674470000005</v>
       </c>
       <c r="Q82">
-        <v>-0.2520789600000003</v>
+        <v>-0.2771674470000005</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2127130502713288</v>
+        <v>0.2214979476540303</v>
       </c>
       <c r="T82">
-        <v>2.428788258814062</v>
+        <v>2.556619219804276</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2186012651938716</v>
+        <v>0.2159024841420953</v>
       </c>
       <c r="W82">
-        <v>0.1147093342695397</v>
+        <v>0.1151055153279404</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8744050607754863</v>
+        <v>0.8636099365683814</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1353200774698975</v>
+        <v>0.1363300774698975</v>
       </c>
       <c r="C83">
-        <v>-4.485886481962554</v>
+        <v>-4.824228382329464</v>
       </c>
       <c r="D83">
-        <v>13.95858351803745</v>
+        <v>13.84811161767054</v>
       </c>
       <c r="E83">
-        <v>17.67047</v>
+        <v>17.89834</v>
       </c>
       <c r="F83">
-        <v>18.45747</v>
+        <v>18.68534</v>
       </c>
       <c r="G83">
         <v>0.013</v>
@@ -8075,37 +8075,37 @@
         <v>2.34</v>
       </c>
       <c r="M83">
-        <v>2.709556596000001</v>
+        <v>2.743007912</v>
       </c>
       <c r="N83">
-        <v>-0.3695565960000007</v>
+        <v>-0.4030079120000005</v>
       </c>
       <c r="O83">
-        <v>-0.09238914900000017</v>
+        <v>-0.1007519780000001</v>
       </c>
       <c r="P83">
-        <v>-0.2771674470000005</v>
+        <v>-0.3022559340000004</v>
       </c>
       <c r="Q83">
-        <v>-0.2771674470000005</v>
+        <v>-0.3022559340000004</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2214979476540303</v>
+        <v>0.2312589447459208</v>
       </c>
       <c r="T83">
-        <v>2.556619219804276</v>
+        <v>2.698653620904513</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2159024841420953</v>
+        <v>0.2132695270184113</v>
       </c>
       <c r="W83">
-        <v>0.1151055153279404</v>
+        <v>0.1154920334336972</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8636099365683814</v>
+        <v>0.8530781080736451</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1363300774698975</v>
+        <v>0.1373400774698975</v>
       </c>
       <c r="C84">
-        <v>-4.824228382329464</v>
+        <v>-5.160835405633527</v>
       </c>
       <c r="D84">
-        <v>13.84811161767054</v>
+        <v>13.73937459436647</v>
       </c>
       <c r="E84">
-        <v>17.89834</v>
+        <v>18.12621</v>
       </c>
       <c r="F84">
-        <v>18.68534</v>
+        <v>18.91321</v>
       </c>
       <c r="G84">
         <v>0.013</v>
@@ -8157,37 +8157,37 @@
         <v>2.34</v>
       </c>
       <c r="M84">
-        <v>2.743007912</v>
+        <v>2.776459228</v>
       </c>
       <c r="N84">
-        <v>-0.4030079120000005</v>
+        <v>-0.4364592280000004</v>
       </c>
       <c r="O84">
-        <v>-0.1007519780000001</v>
+        <v>-0.1091148070000001</v>
       </c>
       <c r="P84">
-        <v>-0.3022559340000004</v>
+        <v>-0.3273444210000003</v>
       </c>
       <c r="Q84">
-        <v>-0.3022559340000004</v>
+        <v>-0.3273444210000003</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2312589447459208</v>
+        <v>0.2421682944368574</v>
       </c>
       <c r="T84">
-        <v>2.698653620904513</v>
+        <v>2.857397951545955</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2132695270184113</v>
+        <v>0.2107000146446955</v>
       </c>
       <c r="W84">
-        <v>0.1154920334336972</v>
+        <v>0.1158692378501587</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8530781080736451</v>
+        <v>0.8428000585787819</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1373400774698975</v>
+        <v>0.1383500774698975</v>
       </c>
       <c r="C85">
-        <v>-5.160835405633527</v>
+        <v>-5.495748100863798</v>
       </c>
       <c r="D85">
-        <v>13.73937459436647</v>
+        <v>13.6323318991362</v>
       </c>
       <c r="E85">
-        <v>18.12621</v>
+        <v>18.35408</v>
       </c>
       <c r="F85">
-        <v>18.91321</v>
+        <v>19.14108</v>
       </c>
       <c r="G85">
         <v>0.013</v>
@@ -8239,37 +8239,37 @@
         <v>2.34</v>
       </c>
       <c r="M85">
-        <v>2.776459228</v>
+        <v>2.809910544000001</v>
       </c>
       <c r="N85">
-        <v>-0.4364592280000004</v>
+        <v>-0.4699105440000007</v>
       </c>
       <c r="O85">
-        <v>-0.1091148070000001</v>
+        <v>-0.1174776360000002</v>
       </c>
       <c r="P85">
-        <v>-0.3273444210000003</v>
+        <v>-0.3524329080000005</v>
       </c>
       <c r="Q85">
-        <v>-0.3273444210000003</v>
+        <v>-0.3524329080000005</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2421682944368574</v>
+        <v>0.2544413128391609</v>
       </c>
       <c r="T85">
-        <v>2.857397951545955</v>
+        <v>3.035985323517578</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2107000146446955</v>
+        <v>0.2081916811370205</v>
       </c>
       <c r="W85">
-        <v>0.1158692378501587</v>
+        <v>0.1162374612090854</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8428000585787819</v>
+        <v>0.8327667245480821</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1383500774698975</v>
+        <v>0.1393600774698975</v>
       </c>
       <c r="C86">
-        <v>-5.495748100863795</v>
+        <v>-5.829005763118749</v>
       </c>
       <c r="D86">
-        <v>13.6323318991362</v>
+        <v>13.52694423688125</v>
       </c>
       <c r="E86">
-        <v>18.35408</v>
+        <v>18.58195</v>
       </c>
       <c r="F86">
-        <v>19.14108</v>
+        <v>19.36895</v>
       </c>
       <c r="G86">
         <v>0.013</v>
@@ -8321,37 +8321,37 @@
         <v>2.34</v>
       </c>
       <c r="M86">
-        <v>2.809910544</v>
+        <v>2.84336186</v>
       </c>
       <c r="N86">
-        <v>-0.4699105440000002</v>
+        <v>-0.50336186</v>
       </c>
       <c r="O86">
-        <v>-0.1174776360000001</v>
+        <v>-0.125840465</v>
       </c>
       <c r="P86">
-        <v>-0.3524329080000002</v>
+        <v>-0.377521395</v>
       </c>
       <c r="Q86">
-        <v>-0.3524329080000002</v>
+        <v>-0.377521395</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2544413128391608</v>
+        <v>0.2683507336951049</v>
       </c>
       <c r="T86">
-        <v>3.035985323517576</v>
+        <v>3.238384345085414</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2081916811370206</v>
+        <v>0.2057423672412909</v>
       </c>
       <c r="W86">
-        <v>0.1162374612090854</v>
+        <v>0.1165970204889785</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8327667245480822</v>
+        <v>0.8229694689651637</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1393600774698975</v>
+        <v>0.1403700774698975</v>
       </c>
       <c r="C87">
-        <v>-5.829005763118749</v>
+        <v>-6.160646481701802</v>
       </c>
       <c r="D87">
-        <v>13.52694423688125</v>
+        <v>13.4231735182982</v>
       </c>
       <c r="E87">
-        <v>18.58195</v>
+        <v>18.80982</v>
       </c>
       <c r="F87">
-        <v>19.36895</v>
+        <v>19.59682</v>
       </c>
       <c r="G87">
         <v>0.013</v>
@@ -8403,37 +8403,37 @@
         <v>2.34</v>
       </c>
       <c r="M87">
-        <v>2.84336186</v>
+        <v>2.876813176</v>
       </c>
       <c r="N87">
-        <v>-0.50336186</v>
+        <v>-0.5368131759999999</v>
       </c>
       <c r="O87">
-        <v>-0.125840465</v>
+        <v>-0.134203294</v>
       </c>
       <c r="P87">
-        <v>-0.377521395</v>
+        <v>-0.4026098819999999</v>
       </c>
       <c r="Q87">
-        <v>-0.377521395</v>
+        <v>-0.4026098819999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2683507336951049</v>
+        <v>0.2842472146733267</v>
       </c>
       <c r="T87">
-        <v>3.238384345085414</v>
+        <v>3.469697512591515</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2057423672412909</v>
+        <v>0.2033500141338341</v>
       </c>
       <c r="W87">
-        <v>0.1165970204889785</v>
+        <v>0.1169482179251532</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8229694689651637</v>
+        <v>0.8134000565353362</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1403700774698975</v>
+        <v>0.1413800774698975</v>
       </c>
       <c r="C88">
-        <v>-6.160646481701802</v>
+        <v>-6.490707186019952</v>
       </c>
       <c r="D88">
-        <v>13.4231735182982</v>
+        <v>13.32098281398005</v>
       </c>
       <c r="E88">
-        <v>18.80982</v>
+        <v>19.03769</v>
       </c>
       <c r="F88">
-        <v>19.59682</v>
+        <v>19.82469</v>
       </c>
       <c r="G88">
         <v>0.013</v>
@@ -8485,37 +8485,37 @@
         <v>2.34</v>
       </c>
       <c r="M88">
-        <v>2.876813176</v>
+        <v>2.910264492</v>
       </c>
       <c r="N88">
-        <v>-0.5368131759999999</v>
+        <v>-0.5702644920000006</v>
       </c>
       <c r="O88">
-        <v>-0.134203294</v>
+        <v>-0.1425661230000002</v>
       </c>
       <c r="P88">
-        <v>-0.4026098819999999</v>
+        <v>-0.4276983690000005</v>
       </c>
       <c r="Q88">
-        <v>-0.4026098819999999</v>
+        <v>-0.4276983690000005</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2842472146733267</v>
+        <v>0.3025893081097364</v>
       </c>
       <c r="T88">
-        <v>3.469697512591515</v>
+        <v>3.736597321252401</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2033500141338341</v>
+        <v>0.201012657649537</v>
       </c>
       <c r="W88">
-        <v>0.1169482179251532</v>
+        <v>0.117291341857048</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8134000565353362</v>
+        <v>0.8040506305981482</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1413800774698975</v>
+        <v>0.1918128041925861</v>
       </c>
       <c r="C89">
-        <v>-6.490707186019952</v>
+        <v>-10.38767569173741</v>
       </c>
       <c r="D89">
-        <v>13.32098281398005</v>
+        <v>9.651884308262588</v>
       </c>
       <c r="E89">
-        <v>19.03769</v>
+        <v>19.26556</v>
       </c>
       <c r="F89">
-        <v>19.82469</v>
+        <v>20.05256</v>
       </c>
       <c r="G89">
         <v>0.013</v>
@@ -8567,45 +8567,45 @@
         <v>2.34</v>
       </c>
       <c r="M89">
-        <v>2.910264492</v>
+        <v>4.026554048</v>
       </c>
       <c r="N89">
-        <v>-0.5702644920000006</v>
+        <v>-1.686554048000001</v>
       </c>
       <c r="O89">
-        <v>-0.1425661230000002</v>
+        <v>-0.4216385120000001</v>
       </c>
       <c r="P89">
-        <v>-0.4276983690000005</v>
+        <v>-1.264915536</v>
       </c>
       <c r="Q89">
-        <v>-0.4276983690000005</v>
+        <v>-1.264915536</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3025893081097364</v>
+        <v>0.3398444731412868</v>
       </c>
       <c r="T89">
-        <v>3.736597321252401</v>
+        <v>4.278705366499434</v>
       </c>
       <c r="U89">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.201012657649537</v>
+        <v>0.1452855203298639</v>
       </c>
       <c r="W89">
-        <v>0.117291341857048</v>
+        <v>0.1716266675177633</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.8040506305981482</v>
+        <v>0.5811420813194557</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1918128041925861</v>
+        <v>0.1933628041925861</v>
       </c>
       <c r="C90">
-        <v>-10.38767569173741</v>
+        <v>-10.69656592710833</v>
       </c>
       <c r="D90">
-        <v>9.651884308262588</v>
+        <v>9.570864072891666</v>
       </c>
       <c r="E90">
-        <v>19.26556</v>
+        <v>19.49343</v>
       </c>
       <c r="F90">
-        <v>20.05256</v>
+        <v>20.28043</v>
       </c>
       <c r="G90">
         <v>0.013</v>
@@ -8649,37 +8649,37 @@
         <v>2.34</v>
       </c>
       <c r="M90">
-        <v>4.026554048</v>
+        <v>4.072310344</v>
       </c>
       <c r="N90">
-        <v>-1.686554048000001</v>
+        <v>-1.732310344</v>
       </c>
       <c r="O90">
-        <v>-0.4216385120000001</v>
+        <v>-0.433077586</v>
       </c>
       <c r="P90">
-        <v>-1.264915536</v>
+        <v>-1.299232758</v>
       </c>
       <c r="Q90">
-        <v>-1.264915536</v>
+        <v>-1.299232758</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3398444731412868</v>
+        <v>0.3665757888814038</v>
       </c>
       <c r="T90">
-        <v>4.278705366499434</v>
+        <v>4.667678581635746</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1452855203298639</v>
+        <v>0.1436530987531239</v>
       </c>
       <c r="W90">
-        <v>0.1716266675177633</v>
+        <v>0.1719544577703727</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5811420813194557</v>
+        <v>0.5746123950124956</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1933628041925861</v>
+        <v>0.1949128041925862</v>
       </c>
       <c r="C91">
-        <v>-10.69656592710833</v>
+        <v>-11.00410727869845</v>
       </c>
       <c r="D91">
-        <v>9.570864072891666</v>
+        <v>9.491192721301553</v>
       </c>
       <c r="E91">
-        <v>19.49343</v>
+        <v>19.7213</v>
       </c>
       <c r="F91">
-        <v>20.28043</v>
+        <v>20.5083</v>
       </c>
       <c r="G91">
         <v>0.013</v>
@@ -8731,37 +8731,37 @@
         <v>2.34</v>
       </c>
       <c r="M91">
-        <v>4.072310344</v>
+        <v>4.118066639999999</v>
       </c>
       <c r="N91">
-        <v>-1.732310344</v>
+        <v>-1.77806664</v>
       </c>
       <c r="O91">
-        <v>-0.433077586</v>
+        <v>-0.4445166599999999</v>
       </c>
       <c r="P91">
-        <v>-1.299232758</v>
+        <v>-1.33354998</v>
       </c>
       <c r="Q91">
-        <v>-1.299232758</v>
+        <v>-1.33354998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3665757888814038</v>
+        <v>0.3986533677695441</v>
       </c>
       <c r="T91">
-        <v>4.667678581635746</v>
+        <v>5.13444643979932</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1436530987531239</v>
+        <v>0.1420569532114225</v>
       </c>
       <c r="W91">
-        <v>0.1719544577703727</v>
+        <v>0.1722749637951464</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5746123950124956</v>
+        <v>0.5682278128456901</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1949128041925862</v>
+        <v>0.1964628041925861</v>
       </c>
       <c r="C92">
-        <v>-11.00410727869845</v>
+        <v>-11.31033315420666</v>
       </c>
       <c r="D92">
-        <v>9.491192721301553</v>
+        <v>9.412836845793342</v>
       </c>
       <c r="E92">
-        <v>19.7213</v>
+        <v>19.94917</v>
       </c>
       <c r="F92">
-        <v>20.5083</v>
+        <v>20.73617</v>
       </c>
       <c r="G92">
         <v>0.013</v>
@@ -8813,37 +8813,37 @@
         <v>2.34</v>
       </c>
       <c r="M92">
-        <v>4.118066639999999</v>
+        <v>4.163822936000001</v>
       </c>
       <c r="N92">
-        <v>-1.77806664</v>
+        <v>-1.823822936000001</v>
       </c>
       <c r="O92">
-        <v>-0.4445166599999999</v>
+        <v>-0.4559557340000002</v>
       </c>
       <c r="P92">
-        <v>-1.33354998</v>
+        <v>-1.367867202000001</v>
       </c>
       <c r="Q92">
-        <v>-1.33354998</v>
+        <v>-1.367867202000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3986533677695441</v>
+        <v>0.4378592975217158</v>
       </c>
       <c r="T92">
-        <v>5.13444643979932</v>
+        <v>5.704940488665914</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1420569532114225</v>
+        <v>0.1404958877915168</v>
       </c>
       <c r="W92">
-        <v>0.1722749637951464</v>
+        <v>0.1725884257314634</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5682278128456901</v>
+        <v>0.561983551166067</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1964628041925861</v>
+        <v>0.1980128041925862</v>
       </c>
       <c r="C93">
-        <v>-11.31033315420666</v>
+        <v>-11.61527586715719</v>
       </c>
       <c r="D93">
-        <v>9.412836845793342</v>
+        <v>9.335764132842806</v>
       </c>
       <c r="E93">
-        <v>19.94917</v>
+        <v>20.17704</v>
       </c>
       <c r="F93">
-        <v>20.73617</v>
+        <v>20.96404</v>
       </c>
       <c r="G93">
         <v>0.013</v>
@@ -8895,37 +8895,37 @@
         <v>2.34</v>
       </c>
       <c r="M93">
-        <v>4.163822936000001</v>
+        <v>4.209579232</v>
       </c>
       <c r="N93">
-        <v>-1.823822936000001</v>
+        <v>-1.869579232</v>
       </c>
       <c r="O93">
-        <v>-0.4559557340000002</v>
+        <v>-0.4673948080000001</v>
       </c>
       <c r="P93">
-        <v>-1.367867202000001</v>
+        <v>-1.402184424</v>
       </c>
       <c r="Q93">
-        <v>-1.367867202000001</v>
+        <v>-1.402184424</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4378592975217158</v>
+        <v>0.4868667097119304</v>
       </c>
       <c r="T93">
-        <v>5.704940488665914</v>
+        <v>6.418058049749154</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1404958877915168</v>
+        <v>0.1389687585763916</v>
       </c>
       <c r="W93">
-        <v>0.1725884257314634</v>
+        <v>0.1728950732778606</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.561983551166067</v>
+        <v>0.5558750343055663</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1980128041925862</v>
+        <v>0.1995628041925861</v>
       </c>
       <c r="C94">
-        <v>-11.61527586715719</v>
+        <v>-11.9189666813315</v>
       </c>
       <c r="D94">
-        <v>9.335764132842806</v>
+        <v>9.259943318668503</v>
       </c>
       <c r="E94">
-        <v>20.17704</v>
+        <v>20.40491</v>
       </c>
       <c r="F94">
-        <v>20.96404</v>
+        <v>21.19191</v>
       </c>
       <c r="G94">
         <v>0.013</v>
@@ -8977,37 +8977,37 @@
         <v>2.34</v>
       </c>
       <c r="M94">
-        <v>4.209579232</v>
+        <v>4.255335528</v>
       </c>
       <c r="N94">
-        <v>-1.869579232</v>
+        <v>-1.915335528</v>
       </c>
       <c r="O94">
-        <v>-0.4673948080000001</v>
+        <v>-0.478833882</v>
       </c>
       <c r="P94">
-        <v>-1.402184424</v>
+        <v>-1.436501646</v>
       </c>
       <c r="Q94">
-        <v>-1.402184424</v>
+        <v>-1.436501646</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4868667097119304</v>
+        <v>0.5498762396707776</v>
       </c>
       <c r="T94">
-        <v>6.418058049749154</v>
+        <v>7.334923485427606</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1389687585763916</v>
+        <v>0.1374744708497637</v>
       </c>
       <c r="W94">
-        <v>0.1728950732778606</v>
+        <v>0.1731951262533674</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5558750343055663</v>
+        <v>0.5498978833990549</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1995628041925861</v>
+        <v>0.2011128041925861</v>
       </c>
       <c r="C95">
-        <v>-11.9189666813315</v>
+        <v>-12.2214358530525</v>
       </c>
       <c r="D95">
-        <v>9.259943318668503</v>
+        <v>9.185344146947495</v>
       </c>
       <c r="E95">
-        <v>20.40491</v>
+        <v>20.63278</v>
       </c>
       <c r="F95">
-        <v>21.19191</v>
+        <v>21.41978</v>
       </c>
       <c r="G95">
         <v>0.013</v>
@@ -9059,37 +9059,37 @@
         <v>2.34</v>
       </c>
       <c r="M95">
-        <v>4.255335528</v>
+        <v>4.301091824</v>
       </c>
       <c r="N95">
-        <v>-1.915335528</v>
+        <v>-1.961091824</v>
       </c>
       <c r="O95">
-        <v>-0.478833882</v>
+        <v>-0.4902729560000001</v>
       </c>
       <c r="P95">
-        <v>-1.436501646</v>
+        <v>-1.470818868</v>
       </c>
       <c r="Q95">
-        <v>-1.436501646</v>
+        <v>-1.470818868</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5498762396707776</v>
+        <v>0.633888946282574</v>
       </c>
       <c r="T95">
-        <v>7.334923485427606</v>
+        <v>8.557410732998875</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1374744708497637</v>
+        <v>0.1360119764790216</v>
       </c>
       <c r="W95">
-        <v>0.1731951262533674</v>
+        <v>0.1734887951230125</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5498978833990549</v>
+        <v>0.5440479059160863</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2011128041925861</v>
+        <v>0.2026628041925862</v>
       </c>
       <c r="C96">
-        <v>-12.2214358530525</v>
+        <v>-12.52271267144132</v>
       </c>
       <c r="D96">
-        <v>9.185344146947495</v>
+        <v>9.11193732855868</v>
       </c>
       <c r="E96">
-        <v>20.63278</v>
+        <v>20.86065</v>
       </c>
       <c r="F96">
-        <v>21.41978</v>
+        <v>21.64765</v>
       </c>
       <c r="G96">
         <v>0.013</v>
@@ -9141,37 +9141,37 @@
         <v>2.34</v>
       </c>
       <c r="M96">
-        <v>4.301091824</v>
+        <v>4.346848120000001</v>
       </c>
       <c r="N96">
-        <v>-1.961091824</v>
+        <v>-2.006848120000001</v>
       </c>
       <c r="O96">
-        <v>-0.4902729560000001</v>
+        <v>-0.5017120300000002</v>
       </c>
       <c r="P96">
-        <v>-1.470818868</v>
+        <v>-1.505136090000001</v>
       </c>
       <c r="Q96">
-        <v>-1.470818868</v>
+        <v>-1.505136090000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.633888946282574</v>
+        <v>0.7515067355390893</v>
       </c>
       <c r="T96">
-        <v>8.557410732998875</v>
+        <v>10.26889287959866</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1360119764790216</v>
+        <v>0.1345802714634529</v>
       </c>
       <c r="W96">
-        <v>0.1734887951230125</v>
+        <v>0.1737762814901387</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5440479059160863</v>
+        <v>0.5383210858538117</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2026628041925862</v>
+        <v>0.2042128041925861</v>
       </c>
       <c r="C97">
-        <v>-12.52271267144132</v>
+        <v>-12.8228254967589</v>
       </c>
       <c r="D97">
-        <v>9.11193732855868</v>
+        <v>9.039694503241103</v>
       </c>
       <c r="E97">
-        <v>20.86065</v>
+        <v>21.08852</v>
       </c>
       <c r="F97">
-        <v>21.64765</v>
+        <v>21.87552</v>
       </c>
       <c r="G97">
         <v>0.013</v>
@@ -9223,37 +9223,37 @@
         <v>2.34</v>
       </c>
       <c r="M97">
-        <v>4.346848120000001</v>
+        <v>4.392604416</v>
       </c>
       <c r="N97">
-        <v>-2.006848120000001</v>
+        <v>-2.052604416</v>
       </c>
       <c r="O97">
-        <v>-0.5017120300000002</v>
+        <v>-0.5131511040000001</v>
       </c>
       <c r="P97">
-        <v>-1.505136090000001</v>
+        <v>-1.539453312</v>
       </c>
       <c r="Q97">
-        <v>-1.505136090000001</v>
+        <v>-1.539453312</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7515067355390893</v>
+        <v>0.9279334194238619</v>
       </c>
       <c r="T97">
-        <v>10.26889287959866</v>
+        <v>12.83611609949832</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1345802714634529</v>
+        <v>0.1331783936357086</v>
       </c>
       <c r="W97">
-        <v>0.1737762814901387</v>
+        <v>0.1740577785579497</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5383210858538117</v>
+        <v>0.5327135745428344</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2042128041925861</v>
+        <v>0.2057628041925862</v>
       </c>
       <c r="C98">
-        <v>-12.8228254967589</v>
+        <v>-13.12180179693816</v>
       </c>
       <c r="D98">
-        <v>9.039694503241103</v>
+        <v>8.968588203061842</v>
       </c>
       <c r="E98">
-        <v>21.08852</v>
+        <v>21.31639</v>
       </c>
       <c r="F98">
-        <v>21.87552</v>
+        <v>22.10339</v>
       </c>
       <c r="G98">
         <v>0.013</v>
@@ -9305,37 +9305,37 @@
         <v>2.34</v>
       </c>
       <c r="M98">
-        <v>4.392604416</v>
+        <v>4.438360712</v>
       </c>
       <c r="N98">
-        <v>-2.052604416</v>
+        <v>-2.098360712</v>
       </c>
       <c r="O98">
-        <v>-0.5131511040000001</v>
+        <v>-0.524590178</v>
       </c>
       <c r="P98">
-        <v>-1.539453312</v>
+        <v>-1.573770534</v>
       </c>
       <c r="Q98">
-        <v>-1.539453312</v>
+        <v>-1.573770534</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9279334194238594</v>
+        <v>1.221977892565146</v>
       </c>
       <c r="T98">
-        <v>12.83611609949829</v>
+        <v>17.11482146599772</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1331783936357086</v>
+        <v>0.1318054205054436</v>
       </c>
       <c r="W98">
-        <v>0.1740577785579497</v>
+        <v>0.1743334715625069</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5327135745428344</v>
+        <v>0.5272216820217743</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2057628041925862</v>
+        <v>0.2073128041925862</v>
       </c>
       <c r="C99">
-        <v>-13.12180179693816</v>
+        <v>-13.41966818240536</v>
       </c>
       <c r="D99">
-        <v>8.968588203061842</v>
+        <v>8.898591817594644</v>
       </c>
       <c r="E99">
-        <v>21.31639</v>
+        <v>21.54426</v>
       </c>
       <c r="F99">
-        <v>22.10339</v>
+        <v>22.33126</v>
       </c>
       <c r="G99">
         <v>0.013</v>
@@ -9387,37 +9387,37 @@
         <v>2.34</v>
       </c>
       <c r="M99">
-        <v>4.438360712</v>
+        <v>4.484117008</v>
       </c>
       <c r="N99">
-        <v>-2.098360712</v>
+        <v>-2.144117008</v>
       </c>
       <c r="O99">
-        <v>-0.524590178</v>
+        <v>-0.5360292520000001</v>
       </c>
       <c r="P99">
-        <v>-1.573770534</v>
+        <v>-1.608087756</v>
       </c>
       <c r="Q99">
-        <v>-1.573770534</v>
+        <v>-1.608087756</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.221977892565146</v>
+        <v>1.810066838847719</v>
       </c>
       <c r="T99">
-        <v>17.11482146599772</v>
+        <v>25.67223219899658</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1318054205054436</v>
+        <v>0.1304604672349799</v>
       </c>
       <c r="W99">
-        <v>0.1743334715625069</v>
+        <v>0.1746035381792161</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5272216820217743</v>
+        <v>0.5218418689399195</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2073128041925862</v>
+        <v>0.2088628041925861</v>
       </c>
       <c r="C100">
-        <v>-13.41966818240536</v>
+        <v>-13.71645043928351</v>
       </c>
       <c r="D100">
-        <v>8.898591817594644</v>
+        <v>8.829679560716492</v>
       </c>
       <c r="E100">
-        <v>21.54426</v>
+        <v>21.77213</v>
       </c>
       <c r="F100">
-        <v>22.33126</v>
+        <v>22.55913</v>
       </c>
       <c r="G100">
         <v>0.013</v>
@@ -9469,37 +9469,37 @@
         <v>2.34</v>
       </c>
       <c r="M100">
-        <v>4.484117008</v>
+        <v>4.529873304</v>
       </c>
       <c r="N100">
-        <v>-2.144117008</v>
+        <v>-2.189873304</v>
       </c>
       <c r="O100">
-        <v>-0.5360292520000001</v>
+        <v>-0.5474683259999999</v>
       </c>
       <c r="P100">
-        <v>-1.608087756</v>
+        <v>-1.642404978</v>
       </c>
       <c r="Q100">
-        <v>-1.608087756</v>
+        <v>-1.642404978</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.810066838847719</v>
+        <v>3.574333677695438</v>
       </c>
       <c r="T100">
-        <v>25.67223219899658</v>
+        <v>51.34446439799316</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1304604672349799</v>
+        <v>0.1291426847376569</v>
       </c>
       <c r="W100">
-        <v>0.1746035381792161</v>
+        <v>0.1748681489046785</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5218418689399195</v>
+        <v>0.5165707389506273</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2088628041925861</v>
-      </c>
-      <c r="C101">
-        <v>-13.71645043928351</v>
-      </c>
-      <c r="D101">
-        <v>8.829679560716492</v>
-      </c>
-      <c r="E101">
-        <v>21.77213</v>
-      </c>
-      <c r="F101">
-        <v>22.55913</v>
-      </c>
-      <c r="G101">
-        <v>0.013</v>
-      </c>
-      <c r="H101">
-        <v>22</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.34</v>
-      </c>
-      <c r="K101">
-        <v>0</v>
-      </c>
-      <c r="L101">
-        <v>2.34</v>
-      </c>
-      <c r="M101">
-        <v>4.529873304</v>
-      </c>
-      <c r="N101">
-        <v>-2.189873304</v>
-      </c>
-      <c r="O101">
-        <v>-0.5474683259999999</v>
-      </c>
-      <c r="P101">
-        <v>-1.642404978</v>
-      </c>
-      <c r="Q101">
-        <v>-1.642404978</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.574333677695438</v>
-      </c>
-      <c r="T101">
-        <v>51.34446439799316</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1291426847376569</v>
-      </c>
-      <c r="W101">
-        <v>0.1748681489046785</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5165707389506273</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
